--- a/Briefing/Briefing.xlsx
+++ b/Briefing/Briefing.xlsx
@@ -1397,7 +1397,7 @@
       <c r="C4" s="40" t="n"/>
       <c r="D4" s="61" t="inlineStr">
         <is>
-          <t>23-Jul</t>
+          <t>24-Jul</t>
         </is>
       </c>
       <c r="E4" s="25" t="n"/>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="B5" s="30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C5" s="38" t="n"/>
@@ -1469,12 +1469,12 @@
       </c>
       <c r="E5" s="30" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F5" s="30" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>95</t>
         </is>
       </c>
       <c r="G5" s="38" t="n"/>
@@ -1500,52 +1500,52 @@
       </c>
       <c r="M5" s="37" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>92</t>
         </is>
       </c>
       <c r="N5" s="37" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>107</t>
         </is>
       </c>
       <c r="O5" s="37" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P5" s="37" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>129</t>
         </is>
       </c>
       <c r="Q5" s="37" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>55</t>
         </is>
       </c>
       <c r="R5" s="37" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>65</t>
         </is>
       </c>
       <c r="S5" s="37" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>143</t>
         </is>
       </c>
       <c r="T5" s="37" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>157</t>
         </is>
       </c>
       <c r="U5" s="37" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>48</t>
         </is>
       </c>
       <c r="V5" s="37" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>55</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,10 @@
           <t>AVC</t>
         </is>
       </c>
-      <c r="E6" s="30" t="n"/>
+      <c r="E6" s="30">
+        <f>F5-E5</f>
+        <v/>
+      </c>
       <c r="F6" s="39" t="n"/>
       <c r="G6" s="40" t="n"/>
       <c r="H6" s="35" t="n"/>
@@ -1570,15 +1573,30 @@
           <t>AVC</t>
         </is>
       </c>
-      <c r="M6" s="37" t="n"/>
+      <c r="M6" s="37">
+        <f>N5-M5</f>
+        <v/>
+      </c>
       <c r="N6" s="35" t="n"/>
-      <c r="O6" s="37" t="n"/>
+      <c r="O6" s="37">
+        <f>P5-O5</f>
+        <v/>
+      </c>
       <c r="P6" s="35" t="n"/>
-      <c r="Q6" s="37" t="n"/>
+      <c r="Q6" s="37">
+        <f>R5-Q5</f>
+        <v/>
+      </c>
       <c r="R6" s="35" t="n"/>
-      <c r="S6" s="37" t="n"/>
+      <c r="S6" s="37">
+        <f>T5-S5</f>
+        <v/>
+      </c>
       <c r="T6" s="35" t="n"/>
-      <c r="U6" s="37" t="n"/>
+      <c r="U6" s="37">
+        <f>V5-U5</f>
+        <v/>
+      </c>
       <c r="V6" s="35" t="n"/>
     </row>
     <row r="7" ht="55.5" customHeight="1">
@@ -1589,7 +1607,7 @@
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C7" s="38" t="n"/>
@@ -1600,12 +1618,12 @@
       </c>
       <c r="E7" s="30" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F7" s="30" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>49</t>
         </is>
       </c>
       <c r="G7" s="38" t="n"/>
@@ -1630,52 +1648,52 @@
       </c>
       <c r="M7" s="37" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>74</t>
         </is>
       </c>
       <c r="N7" s="37" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>84</t>
         </is>
       </c>
       <c r="O7" s="37" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="P7" s="37" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="Q7" s="37" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="R7" s="37" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="S7" s="37" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="T7" s="37" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="P7" s="37" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="Q7" s="37" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="R7" s="37" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="S7" s="37" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="T7" s="37" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="U7" s="37" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>117</t>
         </is>
       </c>
       <c r="V7" s="37" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>127</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1706,10 @@
           <t>AVC</t>
         </is>
       </c>
-      <c r="E8" s="30" t="n"/>
+      <c r="E8" s="30">
+        <f>F7-E7</f>
+        <v/>
+      </c>
       <c r="F8" s="39" t="n"/>
       <c r="G8" s="40" t="n"/>
       <c r="H8" s="35" t="n"/>
@@ -1700,15 +1721,30 @@
           <t>AVC</t>
         </is>
       </c>
-      <c r="M8" s="37" t="n"/>
+      <c r="M8" s="37">
+        <f>N7-M7</f>
+        <v/>
+      </c>
       <c r="N8" s="35" t="n"/>
-      <c r="O8" s="37" t="n"/>
+      <c r="O8" s="37">
+        <f>P7-O7</f>
+        <v/>
+      </c>
       <c r="P8" s="35" t="n"/>
-      <c r="Q8" s="37" t="n"/>
+      <c r="Q8" s="37">
+        <f>R7-Q7</f>
+        <v/>
+      </c>
       <c r="R8" s="35" t="n"/>
-      <c r="S8" s="37" t="n"/>
+      <c r="S8" s="37">
+        <f>T7-S7</f>
+        <v/>
+      </c>
       <c r="T8" s="35" t="n"/>
-      <c r="U8" s="37" t="n"/>
+      <c r="U8" s="37">
+        <f>V7-U7</f>
+        <v/>
+      </c>
       <c r="V8" s="35" t="n"/>
     </row>
     <row r="9" ht="57" customHeight="1">
@@ -1730,7 +1766,7 @@
       </c>
       <c r="E9" s="30" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>191</t>
         </is>
       </c>
       <c r="F9" s="50" t="n"/>
@@ -1757,31 +1793,31 @@
       </c>
       <c r="M9" s="37" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>214</t>
         </is>
       </c>
       <c r="N9" s="38" t="n"/>
       <c r="O9" s="37" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>273</t>
         </is>
       </c>
       <c r="P9" s="38" t="n"/>
       <c r="Q9" s="37" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>222</t>
         </is>
       </c>
       <c r="R9" s="38" t="n"/>
       <c r="S9" s="37" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>290</t>
         </is>
       </c>
       <c r="T9" s="38" t="n"/>
       <c r="U9" s="37" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>218</t>
         </is>
       </c>
       <c r="V9" s="38" t="n"/>
@@ -1817,7 +1853,7 @@
         </is>
       </c>
       <c r="B11" s="85" t="n">
-        <v>3077.72</v>
+        <v>4321.59</v>
       </c>
       <c r="C11" s="22" t="n"/>
       <c r="D11" s="42" t="inlineStr">
@@ -1826,7 +1862,7 @@
         </is>
       </c>
       <c r="E11" s="86" t="n">
-        <v>51.46</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="F11" s="25" t="n"/>
       <c r="G11" s="22" t="n"/>
@@ -1840,23 +1876,23 @@
         </is>
       </c>
       <c r="M11" s="87" t="n">
-        <v>78.47</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="N11" s="22" t="n"/>
       <c r="O11" s="87" t="n">
-        <v>52.92</v>
+        <v>99.64</v>
       </c>
       <c r="P11" s="22" t="n"/>
       <c r="Q11" s="87" t="n">
-        <v>65.33</v>
+        <v>81.02</v>
       </c>
       <c r="R11" s="22" t="n"/>
       <c r="S11" s="87" t="n">
-        <v>72.26000000000001</v>
+        <v>105.84</v>
       </c>
       <c r="T11" s="22" t="n"/>
       <c r="U11" s="87" t="n">
-        <v>94.53</v>
+        <v>79.56</v>
       </c>
       <c r="V11" s="22" t="n"/>
     </row>
@@ -1867,7 +1903,7 @@
         </is>
       </c>
       <c r="B12" s="88" t="n">
-        <v>59.56</v>
+        <v>46.32</v>
       </c>
       <c r="C12" s="38" t="n"/>
       <c r="D12" s="42" t="inlineStr">
@@ -1876,15 +1912,18 @@
 House</t>
         </is>
       </c>
-      <c r="E12" s="34" t="n"/>
-      <c r="F12" s="34" t="inlineStr">
-        <is>
-          <t>344</t>
-        </is>
+      <c r="E12" s="34" t="inlineStr">
+        <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="F12" s="34">
+        <f>E12+E13</f>
+        <v/>
       </c>
       <c r="G12" s="34" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>530</t>
         </is>
       </c>
       <c r="H12" s="28" t="inlineStr">
@@ -1909,31 +1948,31 @@
       </c>
       <c r="M12" s="37" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>625</t>
         </is>
       </c>
       <c r="N12" s="38" t="n"/>
       <c r="O12" s="37" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>753</t>
         </is>
       </c>
       <c r="P12" s="38" t="n"/>
       <c r="Q12" s="37" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>655</t>
         </is>
       </c>
       <c r="R12" s="38" t="n"/>
       <c r="S12" s="37" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>779</t>
         </is>
       </c>
       <c r="T12" s="38" t="n"/>
       <c r="U12" s="37" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>624</t>
         </is>
       </c>
       <c r="V12" s="38" t="n"/>
@@ -1943,7 +1982,11 @@
       <c r="B13" s="39" t="n"/>
       <c r="C13" s="40" t="n"/>
       <c r="D13" s="35" t="n"/>
-      <c r="E13" s="34" t="n"/>
+      <c r="E13" s="34" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
       <c r="F13" s="35" t="n"/>
       <c r="G13" s="35" t="n"/>
       <c r="H13" s="35" t="n"/>

--- a/Briefing/Briefing.xlsx
+++ b/Briefing/Briefing.xlsx
@@ -17,11 +17,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm;@"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="#.##&quot;%&quot;"/>
     <numFmt numFmtId="167" formatCode="#,###.##"/>
+    <numFmt numFmtId="168" formatCode="#,###.00"/>
+    <numFmt numFmtId="169" formatCode="#,###"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -422,7 +424,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
@@ -664,6 +666,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1458,7 +1475,7 @@
       </c>
       <c r="B5" s="30" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C5" s="38" t="n"/>
@@ -1484,7 +1501,11 @@
 Upselling</t>
         </is>
       </c>
-      <c r="I5" s="41" t="n"/>
+      <c r="I5" s="91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J5" s="41" t="inlineStr">
         <is>
           <t>-</t>
@@ -1632,7 +1653,9 @@
           <t>Late C/O</t>
         </is>
       </c>
-      <c r="I7" s="41" t="n"/>
+      <c r="I7" s="41" t="n">
+        <v>2881.21</v>
+      </c>
       <c r="J7" s="41" t="inlineStr">
         <is>
           <t>-</t>
@@ -1777,7 +1800,11 @@
 Comm. target</t>
         </is>
       </c>
-      <c r="I9" s="41" t="n"/>
+      <c r="I9" s="94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J9" s="41" t="inlineStr">
         <is>
           <t>-</t>
@@ -1861,8 +1888,9 @@
           <t>Occ %</t>
         </is>
       </c>
-      <c r="E11" s="86" t="n">
-        <v>69.70999999999999</v>
+      <c r="E11" s="86">
+        <f>E9-B5:B7/327*100</f>
+        <v/>
       </c>
       <c r="F11" s="25" t="n"/>
       <c r="G11" s="22" t="n"/>
@@ -1876,23 +1904,23 @@
         </is>
       </c>
       <c r="M11" s="87" t="n">
-        <v>78.09999999999999</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="N11" s="22" t="n"/>
       <c r="O11" s="87" t="n">
-        <v>99.64</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="P11" s="22" t="n"/>
       <c r="Q11" s="87" t="n">
-        <v>81.02</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="R11" s="22" t="n"/>
       <c r="S11" s="87" t="n">
-        <v>105.84</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="T11" s="22" t="n"/>
       <c r="U11" s="87" t="n">
-        <v>79.56</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="V11" s="22" t="n"/>
     </row>
@@ -1903,7 +1931,7 @@
         </is>
       </c>
       <c r="B12" s="88" t="n">
-        <v>46.32</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="C12" s="38" t="n"/>
       <c r="D12" s="42" t="inlineStr">
@@ -1931,7 +1959,9 @@
           <t>Gallery</t>
         </is>
       </c>
-      <c r="I12" s="78" t="n"/>
+      <c r="I12" s="78" t="n">
+        <v>2738.33</v>
+      </c>
       <c r="J12" s="41" t="inlineStr">
         <is>
           <t>-</t>

--- a/Briefing/Briefing.xlsx
+++ b/Briefing/Briefing.xlsx
@@ -1473,10 +1473,8 @@
           <t>COMP.</t>
         </is>
       </c>
-      <c r="B5" s="30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="B5" s="30" t="n">
+        <v>0</v>
       </c>
       <c r="C5" s="38" t="n"/>
       <c r="D5" s="77" t="inlineStr">
@@ -1626,10 +1624,8 @@
           <t>HOU</t>
         </is>
       </c>
-      <c r="B7" s="30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="B7" s="30" t="n">
+        <v>2</v>
       </c>
       <c r="C7" s="38" t="n"/>
       <c r="D7" s="77" t="inlineStr">
@@ -1888,9 +1884,8 @@
           <t>Occ %</t>
         </is>
       </c>
-      <c r="E11" s="86">
-        <f>E9-B5:B7/327*100</f>
-        <v/>
+      <c r="E11" s="86" t="n">
+        <v>2</v>
       </c>
       <c r="F11" s="25" t="n"/>
       <c r="G11" s="22" t="n"/>

--- a/Briefing/Briefing.xlsx
+++ b/Briefing/Briefing.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="34770" yWindow="4815" windowWidth="18660" windowHeight="16125" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="570" yWindow="1080" windowWidth="18660" windowHeight="16125" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Ori Format" sheetId="1" state="visible" r:id="rId1"/>
@@ -17,13 +17,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm;@"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="#.##&quot;%&quot;"/>
-    <numFmt numFmtId="167" formatCode="#,###.##"/>
-    <numFmt numFmtId="168" formatCode="#,###.00"/>
-    <numFmt numFmtId="169" formatCode="#,###"/>
+    <numFmt numFmtId="166" formatCode="#,###.##"/>
+    <numFmt numFmtId="167" formatCode="#.##&quot;%&quot;"/>
+    <numFmt numFmtId="168" formatCode="#.#0&quot;%&quot;"/>
+    <numFmt numFmtId="169" formatCode="#.##%"/>
+    <numFmt numFmtId="170" formatCode="#.###&quot;%&quot;"/>
+    <numFmt numFmtId="171" formatCode="0.00&quot;%&quot;"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -424,7 +426,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
@@ -434,12 +436,6 @@
     <xf numFmtId="164" fontId="4" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="9" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="10" fontId="9" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -456,26 +452,32 @@
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -556,6 +558,9 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -572,7 +577,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -599,13 +604,13 @@
     <xf numFmtId="49" fontId="6" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="167" fontId="13" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="12" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
+    <xf numFmtId="167" fontId="10" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -623,7 +628,7 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
+    <xf numFmtId="166" fontId="10" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -650,37 +655,37 @@
     <xf numFmtId="0" fontId="16" fillId="10" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="167" fontId="10" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="9" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="168" fontId="13" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="13" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="13" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="13" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="13" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1250,7 +1255,7 @@
     <col width="22.140625" customWidth="1" style="1" min="6" max="7"/>
     <col width="38.7109375" customWidth="1" style="1" min="8" max="8"/>
     <col width="43.85546875" customWidth="1" style="1" min="9" max="9"/>
-    <col width="43.85546875" customWidth="1" style="14" min="10" max="10"/>
+    <col width="43.85546875" customWidth="1" style="11" min="10" max="10"/>
     <col width="44.7109375" customWidth="1" style="1" min="11" max="11"/>
     <col width="41.28515625" customWidth="1" style="1" min="12" max="12"/>
     <col width="29.28515625" customWidth="1" style="1" min="13" max="13"/>
@@ -1263,15 +1268,15 @@
     <col width="28.7109375" customWidth="1" style="1" min="20" max="20"/>
     <col width="29.28515625" customWidth="1" style="1" min="21" max="21"/>
     <col width="110.7109375" customWidth="1" style="1" min="22" max="22"/>
-    <col width="10.42578125" customWidth="1" style="1" min="23" max="23"/>
-    <col width="10.42578125" customWidth="1" style="1" min="24" max="16384"/>
+    <col width="10.42578125" customWidth="1" style="1" min="23" max="24"/>
+    <col width="10.42578125" customWidth="1" style="1" min="25" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="336" customHeight="1">
-      <c r="A1" s="80" t="n"/>
+      <c r="A1" s="81" t="n"/>
       <c r="B1" s="50" t="n"/>
       <c r="C1" s="38" t="n"/>
-      <c r="D1" s="72" t="inlineStr">
+      <c r="D1" s="73" t="inlineStr">
         <is>
           <t xml:space="preserve">
 YTD GRI 
@@ -1282,7 +1287,7 @@
       <c r="E1" s="50" t="n"/>
       <c r="F1" s="50" t="n"/>
       <c r="G1" s="38" t="n"/>
-      <c r="H1" s="72" t="inlineStr">
+      <c r="H1" s="73" t="inlineStr">
         <is>
           <t xml:space="preserve">
 YTD NPS
@@ -1291,7 +1296,7 @@
         </is>
       </c>
       <c r="I1" s="38" t="n"/>
-      <c r="J1" s="72" t="inlineStr">
+      <c r="J1" s="73" t="inlineStr">
         <is>
           <t xml:space="preserve">
 MTD GRI
@@ -1301,7 +1306,7 @@
         </is>
       </c>
       <c r="K1" s="38" t="n"/>
-      <c r="L1" s="72" t="inlineStr">
+      <c r="L1" s="73" t="inlineStr">
         <is>
           <t xml:space="preserve">
 MTD NPS
@@ -1334,7 +1339,7 @@
       </c>
       <c r="T1" s="50" t="n"/>
       <c r="U1" s="38" t="n"/>
-      <c r="V1" s="67" t="inlineStr">
+      <c r="V1" s="68" t="inlineStr">
         <is>
           <t>Show Room
 -
@@ -1344,7 +1349,7 @@
       </c>
     </row>
     <row r="2" ht="306.6" customHeight="1">
-      <c r="A2" s="82" t="inlineStr">
+      <c r="A2" s="83" t="inlineStr">
         <is>
           <t>Daily Briefing
 ( Day ) July ( Date ), 2026</t>
@@ -1373,14 +1378,14 @@
       <c r="V2" s="35" t="n"/>
     </row>
     <row r="3" ht="99" customFormat="1" customHeight="1" s="2">
-      <c r="A3" s="57" t="inlineStr">
+      <c r="A3" s="58" t="inlineStr">
         <is>
           <t>Yesterday</t>
         </is>
       </c>
       <c r="B3" s="50" t="n"/>
       <c r="C3" s="38" t="n"/>
-      <c r="D3" s="57" t="inlineStr">
+      <c r="D3" s="58" t="inlineStr">
         <is>
           <t>TODAY</t>
         </is>
@@ -1392,7 +1397,7 @@
       <c r="I3" s="25" t="n"/>
       <c r="J3" s="25" t="n"/>
       <c r="K3" s="22" t="n"/>
-      <c r="L3" s="57" t="inlineStr">
+      <c r="L3" s="58" t="inlineStr">
         <is>
           <t>Next 5 days</t>
         </is>
@@ -1412,7 +1417,7 @@
       <c r="A4" s="39" t="n"/>
       <c r="B4" s="52" t="n"/>
       <c r="C4" s="40" t="n"/>
-      <c r="D4" s="61" t="inlineStr">
+      <c r="D4" s="62" t="inlineStr">
         <is>
           <t>24-Jul</t>
         </is>
@@ -1473,11 +1478,13 @@
           <t>COMP.</t>
         </is>
       </c>
-      <c r="B5" s="30" t="n">
-        <v>0</v>
+      <c r="B5" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C5" s="38" t="n"/>
-      <c r="D5" s="77" t="inlineStr">
+      <c r="D5" s="78" t="inlineStr">
         <is>
           <t>ARR.</t>
         </is>
@@ -1499,7 +1506,7 @@
 Upselling</t>
         </is>
       </c>
-      <c r="I5" s="91" t="inlineStr">
+      <c r="I5" s="53" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1509,10 +1516,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K5" s="69" t="n">
+      <c r="K5" s="70" t="n">
         <v>205427.65</v>
       </c>
-      <c r="L5" s="77" t="inlineStr">
+      <c r="L5" s="78" t="inlineStr">
         <is>
           <t>ARR.</t>
         </is>
@@ -1572,7 +1579,7 @@
       <c r="A6" s="35" t="n"/>
       <c r="B6" s="39" t="n"/>
       <c r="C6" s="40" t="n"/>
-      <c r="D6" s="77" t="inlineStr">
+      <c r="D6" s="78" t="inlineStr">
         <is>
           <t>AVC</t>
         </is>
@@ -1587,7 +1594,7 @@
       <c r="I6" s="35" t="n"/>
       <c r="J6" s="35" t="n"/>
       <c r="K6" s="35" t="n"/>
-      <c r="L6" s="77" t="inlineStr">
+      <c r="L6" s="78" t="inlineStr">
         <is>
           <t>AVC</t>
         </is>
@@ -1624,11 +1631,13 @@
           <t>HOU</t>
         </is>
       </c>
-      <c r="B7" s="30" t="n">
-        <v>2</v>
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="C7" s="38" t="n"/>
-      <c r="D7" s="77" t="inlineStr">
+      <c r="D7" s="78" t="inlineStr">
         <is>
           <t>DEP.</t>
         </is>
@@ -1657,10 +1666,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K7" s="69" t="n">
+      <c r="K7" s="70" t="n">
         <v>29000</v>
       </c>
-      <c r="L7" s="77" t="inlineStr">
+      <c r="L7" s="78" t="inlineStr">
         <is>
           <t>DEP.</t>
         </is>
@@ -1720,7 +1729,7 @@
       <c r="A8" s="35" t="n"/>
       <c r="B8" s="39" t="n"/>
       <c r="C8" s="40" t="n"/>
-      <c r="D8" s="77" t="inlineStr">
+      <c r="D8" s="78" t="inlineStr">
         <is>
           <t>AVC</t>
         </is>
@@ -1735,7 +1744,7 @@
       <c r="I8" s="35" t="n"/>
       <c r="J8" s="35" t="n"/>
       <c r="K8" s="35" t="n"/>
-      <c r="L8" s="77" t="inlineStr">
+      <c r="L8" s="78" t="inlineStr">
         <is>
           <t>AVC</t>
         </is>
@@ -1796,7 +1805,7 @@
 Comm. target</t>
         </is>
       </c>
-      <c r="I9" s="94" t="inlineStr">
+      <c r="I9" s="86" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1806,7 +1815,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K9" s="69" t="n">
+      <c r="K9" s="70" t="n">
         <v>160368</v>
       </c>
       <c r="L9" s="46" t="inlineStr">
@@ -1875,7 +1884,7 @@
           <t>ADR</t>
         </is>
       </c>
-      <c r="B11" s="85" t="n">
+      <c r="B11" s="77" t="n">
         <v>4321.59</v>
       </c>
       <c r="C11" s="22" t="n"/>
@@ -1884,8 +1893,8 @@
           <t>Occ %</t>
         </is>
       </c>
-      <c r="E11" s="86" t="n">
-        <v>2</v>
+      <c r="E11" s="87" t="n">
+        <v>57.8</v>
       </c>
       <c r="F11" s="25" t="n"/>
       <c r="G11" s="22" t="n"/>
@@ -1893,28 +1902,28 @@
       <c r="I11" s="35" t="n"/>
       <c r="J11" s="35" t="n"/>
       <c r="K11" s="35" t="n"/>
-      <c r="L11" s="7" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>OCC %</t>
         </is>
       </c>
-      <c r="M11" s="87" t="n">
+      <c r="M11" s="88" t="n">
         <v>69.70999999999999</v>
       </c>
       <c r="N11" s="22" t="n"/>
-      <c r="O11" s="87" t="n">
+      <c r="O11" s="88" t="n">
         <v>69.70999999999999</v>
       </c>
       <c r="P11" s="22" t="n"/>
-      <c r="Q11" s="87" t="n">
+      <c r="Q11" s="88" t="n">
         <v>69.70999999999999</v>
       </c>
       <c r="R11" s="22" t="n"/>
-      <c r="S11" s="87" t="n">
+      <c r="S11" s="88" t="n">
         <v>69.70999999999999</v>
       </c>
       <c r="T11" s="22" t="n"/>
-      <c r="U11" s="87" t="n">
+      <c r="U11" s="88" t="n">
         <v>69.70999999999999</v>
       </c>
       <c r="V11" s="22" t="n"/>
@@ -1925,7 +1934,7 @@
           <t>Occ%</t>
         </is>
       </c>
-      <c r="B12" s="88" t="n">
+      <c r="B12" s="89" t="n">
         <v>69.70999999999999</v>
       </c>
       <c r="C12" s="38" t="n"/>
@@ -1954,7 +1963,7 @@
           <t>Gallery</t>
         </is>
       </c>
-      <c r="I12" s="78" t="n">
+      <c r="I12" s="79" t="n">
         <v>2738.33</v>
       </c>
       <c r="J12" s="41" t="inlineStr">
@@ -1962,10 +1971,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K12" s="79" t="n">
+      <c r="K12" s="80" t="n">
         <v>180414</v>
       </c>
-      <c r="L12" s="54" t="inlineStr">
+      <c r="L12" s="55" t="inlineStr">
         <is>
           <t>Guest In 
 House</t>
@@ -2018,7 +2027,7 @@
       <c r="I13" s="47" t="n"/>
       <c r="J13" s="35" t="n"/>
       <c r="K13" s="47" t="n"/>
-      <c r="L13" s="55" t="n"/>
+      <c r="L13" s="56" t="n"/>
       <c r="M13" s="39" t="n"/>
       <c r="N13" s="40" t="n"/>
       <c r="O13" s="39" t="n"/>
@@ -2031,7 +2040,7 @@
       <c r="V13" s="40" t="n"/>
     </row>
     <row r="14" ht="99" customFormat="1" customHeight="1" s="2">
-      <c r="A14" s="89" t="inlineStr">
+      <c r="A14" s="90" t="inlineStr">
         <is>
           <t>VIP ARRIVAL</t>
         </is>
@@ -2092,12 +2101,12 @@
           <t xml:space="preserve">ARR </t>
         </is>
       </c>
-      <c r="J15" s="8" t="inlineStr">
+      <c r="J15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">DEP </t>
         </is>
       </c>
-      <c r="K15" s="8" t="inlineStr">
+      <c r="K15" s="6" t="inlineStr">
         <is>
           <t>Flight</t>
         </is>
@@ -2129,20 +2138,20 @@
     <row r="16" ht="114" customHeight="1">
       <c r="A16" s="31" t="n"/>
       <c r="B16" s="22" t="n"/>
-      <c r="C16" s="9" t="n"/>
+      <c r="C16" s="7" t="n"/>
       <c r="D16" s="23" t="n"/>
       <c r="E16" s="22" t="n"/>
       <c r="F16" s="23" t="n"/>
       <c r="G16" s="22" t="n"/>
-      <c r="H16" s="10" t="n"/>
-      <c r="I16" s="11" t="n"/>
-      <c r="J16" s="11" t="n"/>
-      <c r="K16" s="10" t="n"/>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="9" t="n"/>
+      <c r="J16" s="9" t="n"/>
+      <c r="K16" s="8" t="n"/>
       <c r="L16" s="29" t="n"/>
       <c r="M16" s="22" t="n"/>
       <c r="N16" s="30" t="n"/>
       <c r="O16" s="22" t="n"/>
-      <c r="P16" s="83" t="n"/>
+      <c r="P16" s="84" t="n"/>
       <c r="Q16" s="25" t="n"/>
       <c r="R16" s="25" t="n"/>
       <c r="S16" s="25" t="n"/>
@@ -2153,15 +2162,15 @@
     <row r="17" ht="114" customHeight="1">
       <c r="A17" s="31" t="n"/>
       <c r="B17" s="22" t="n"/>
-      <c r="C17" s="9" t="n"/>
+      <c r="C17" s="7" t="n"/>
       <c r="D17" s="23" t="n"/>
       <c r="E17" s="22" t="n"/>
       <c r="F17" s="23" t="n"/>
       <c r="G17" s="22" t="n"/>
-      <c r="H17" s="10" t="n"/>
-      <c r="I17" s="11" t="n"/>
-      <c r="J17" s="11" t="n"/>
-      <c r="K17" s="10" t="n"/>
+      <c r="H17" s="8" t="n"/>
+      <c r="I17" s="9" t="n"/>
+      <c r="J17" s="9" t="n"/>
+      <c r="K17" s="8" t="n"/>
       <c r="L17" s="29" t="n"/>
       <c r="M17" s="22" t="n"/>
       <c r="N17" s="30" t="n"/>
@@ -2177,15 +2186,15 @@
     <row r="18" ht="114" customHeight="1">
       <c r="A18" s="31" t="n"/>
       <c r="B18" s="22" t="n"/>
-      <c r="C18" s="9" t="n"/>
+      <c r="C18" s="7" t="n"/>
       <c r="D18" s="23" t="n"/>
       <c r="E18" s="22" t="n"/>
       <c r="F18" s="23" t="n"/>
       <c r="G18" s="22" t="n"/>
-      <c r="H18" s="10" t="n"/>
-      <c r="I18" s="11" t="n"/>
-      <c r="J18" s="11" t="n"/>
-      <c r="K18" s="10" t="n"/>
+      <c r="H18" s="8" t="n"/>
+      <c r="I18" s="9" t="n"/>
+      <c r="J18" s="9" t="n"/>
+      <c r="K18" s="8" t="n"/>
       <c r="L18" s="29" t="n"/>
       <c r="M18" s="22" t="n"/>
       <c r="N18" s="30" t="n"/>
@@ -2201,15 +2210,15 @@
     <row r="19" ht="114" customHeight="1">
       <c r="A19" s="31" t="n"/>
       <c r="B19" s="22" t="n"/>
-      <c r="C19" s="9" t="n"/>
+      <c r="C19" s="7" t="n"/>
       <c r="D19" s="23" t="n"/>
       <c r="E19" s="22" t="n"/>
       <c r="F19" s="23" t="n"/>
       <c r="G19" s="22" t="n"/>
-      <c r="H19" s="10" t="n"/>
-      <c r="I19" s="11" t="n"/>
-      <c r="J19" s="11" t="n"/>
-      <c r="K19" s="10" t="n"/>
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="9" t="n"/>
+      <c r="J19" s="9" t="n"/>
+      <c r="K19" s="8" t="n"/>
       <c r="L19" s="29" t="n"/>
       <c r="M19" s="22" t="n"/>
       <c r="N19" s="30" t="n"/>
@@ -2225,15 +2234,15 @@
     <row r="20" ht="114" customHeight="1">
       <c r="A20" s="31" t="n"/>
       <c r="B20" s="22" t="n"/>
-      <c r="C20" s="9" t="n"/>
+      <c r="C20" s="7" t="n"/>
       <c r="D20" s="23" t="n"/>
       <c r="E20" s="22" t="n"/>
       <c r="F20" s="23" t="n"/>
       <c r="G20" s="22" t="n"/>
-      <c r="H20" s="10" t="n"/>
-      <c r="I20" s="11" t="n"/>
-      <c r="J20" s="11" t="n"/>
-      <c r="K20" s="10" t="n"/>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="9" t="n"/>
+      <c r="J20" s="9" t="n"/>
+      <c r="K20" s="8" t="n"/>
       <c r="L20" s="29" t="n"/>
       <c r="M20" s="22" t="n"/>
       <c r="N20" s="30" t="n"/>
@@ -2249,15 +2258,15 @@
     <row r="21" ht="114" customHeight="1">
       <c r="A21" s="31" t="n"/>
       <c r="B21" s="22" t="n"/>
-      <c r="C21" s="9" t="n"/>
+      <c r="C21" s="7" t="n"/>
       <c r="D21" s="23" t="n"/>
       <c r="E21" s="22" t="n"/>
       <c r="F21" s="23" t="n"/>
       <c r="G21" s="22" t="n"/>
-      <c r="H21" s="10" t="n"/>
-      <c r="I21" s="11" t="n"/>
-      <c r="J21" s="11" t="n"/>
-      <c r="K21" s="10" t="n"/>
+      <c r="H21" s="8" t="n"/>
+      <c r="I21" s="9" t="n"/>
+      <c r="J21" s="9" t="n"/>
+      <c r="K21" s="8" t="n"/>
       <c r="L21" s="29" t="n"/>
       <c r="M21" s="22" t="n"/>
       <c r="N21" s="30" t="n"/>
@@ -2273,15 +2282,15 @@
     <row r="22" ht="114" customHeight="1">
       <c r="A22" s="31" t="n"/>
       <c r="B22" s="22" t="n"/>
-      <c r="C22" s="9" t="n"/>
+      <c r="C22" s="7" t="n"/>
       <c r="D22" s="23" t="n"/>
       <c r="E22" s="22" t="n"/>
       <c r="F22" s="23" t="n"/>
       <c r="G22" s="22" t="n"/>
-      <c r="H22" s="10" t="n"/>
-      <c r="I22" s="11" t="n"/>
-      <c r="J22" s="11" t="n"/>
-      <c r="K22" s="10" t="n"/>
+      <c r="H22" s="8" t="n"/>
+      <c r="I22" s="9" t="n"/>
+      <c r="J22" s="9" t="n"/>
+      <c r="K22" s="8" t="n"/>
       <c r="L22" s="29" t="n"/>
       <c r="M22" s="22" t="n"/>
       <c r="N22" s="30" t="n"/>
@@ -2297,15 +2306,15 @@
     <row r="23" ht="114" customHeight="1">
       <c r="A23" s="31" t="n"/>
       <c r="B23" s="22" t="n"/>
-      <c r="C23" s="9" t="n"/>
+      <c r="C23" s="7" t="n"/>
       <c r="D23" s="23" t="n"/>
       <c r="E23" s="22" t="n"/>
       <c r="F23" s="23" t="n"/>
       <c r="G23" s="22" t="n"/>
-      <c r="H23" s="10" t="n"/>
-      <c r="I23" s="11" t="n"/>
-      <c r="J23" s="11" t="n"/>
-      <c r="K23" s="10" t="n"/>
+      <c r="H23" s="8" t="n"/>
+      <c r="I23" s="9" t="n"/>
+      <c r="J23" s="9" t="n"/>
+      <c r="K23" s="8" t="n"/>
       <c r="L23" s="29" t="n"/>
       <c r="M23" s="22" t="n"/>
       <c r="N23" s="30" t="n"/>
@@ -2321,15 +2330,15 @@
     <row r="24" ht="114" customHeight="1">
       <c r="A24" s="31" t="n"/>
       <c r="B24" s="22" t="n"/>
-      <c r="C24" s="9" t="n"/>
+      <c r="C24" s="7" t="n"/>
       <c r="D24" s="23" t="n"/>
       <c r="E24" s="22" t="n"/>
       <c r="F24" s="23" t="n"/>
       <c r="G24" s="22" t="n"/>
-      <c r="H24" s="10" t="n"/>
-      <c r="I24" s="11" t="n"/>
-      <c r="J24" s="11" t="n"/>
-      <c r="K24" s="10" t="n"/>
+      <c r="H24" s="8" t="n"/>
+      <c r="I24" s="9" t="n"/>
+      <c r="J24" s="9" t="n"/>
+      <c r="K24" s="8" t="n"/>
       <c r="L24" s="29" t="n"/>
       <c r="M24" s="22" t="n"/>
       <c r="N24" s="30" t="n"/>
@@ -2345,15 +2354,15 @@
     <row r="25" ht="114" customHeight="1">
       <c r="A25" s="31" t="n"/>
       <c r="B25" s="22" t="n"/>
-      <c r="C25" s="9" t="n"/>
+      <c r="C25" s="7" t="n"/>
       <c r="D25" s="23" t="n"/>
       <c r="E25" s="22" t="n"/>
       <c r="F25" s="23" t="n"/>
       <c r="G25" s="22" t="n"/>
-      <c r="H25" s="10" t="n"/>
-      <c r="I25" s="11" t="n"/>
-      <c r="J25" s="11" t="n"/>
-      <c r="K25" s="10" t="n"/>
+      <c r="H25" s="8" t="n"/>
+      <c r="I25" s="9" t="n"/>
+      <c r="J25" s="9" t="n"/>
+      <c r="K25" s="8" t="n"/>
       <c r="L25" s="29" t="n"/>
       <c r="M25" s="22" t="n"/>
       <c r="N25" s="30" t="n"/>
@@ -2369,15 +2378,15 @@
     <row r="26" ht="114" customHeight="1">
       <c r="A26" s="31" t="n"/>
       <c r="B26" s="22" t="n"/>
-      <c r="C26" s="9" t="n"/>
+      <c r="C26" s="7" t="n"/>
       <c r="D26" s="23" t="n"/>
       <c r="E26" s="22" t="n"/>
       <c r="F26" s="23" t="n"/>
       <c r="G26" s="22" t="n"/>
-      <c r="H26" s="10" t="n"/>
-      <c r="I26" s="11" t="n"/>
-      <c r="J26" s="11" t="n"/>
-      <c r="K26" s="10" t="n"/>
+      <c r="H26" s="8" t="n"/>
+      <c r="I26" s="9" t="n"/>
+      <c r="J26" s="9" t="n"/>
+      <c r="K26" s="8" t="n"/>
       <c r="L26" s="29" t="n"/>
       <c r="M26" s="22" t="n"/>
       <c r="N26" s="30" t="n"/>
@@ -2393,15 +2402,15 @@
     <row r="27" ht="114" customHeight="1">
       <c r="A27" s="31" t="n"/>
       <c r="B27" s="22" t="n"/>
-      <c r="C27" s="9" t="n"/>
+      <c r="C27" s="7" t="n"/>
       <c r="D27" s="23" t="n"/>
       <c r="E27" s="22" t="n"/>
       <c r="F27" s="23" t="n"/>
       <c r="G27" s="22" t="n"/>
-      <c r="H27" s="10" t="n"/>
-      <c r="I27" s="11" t="n"/>
-      <c r="J27" s="11" t="n"/>
-      <c r="K27" s="10" t="n"/>
+      <c r="H27" s="8" t="n"/>
+      <c r="I27" s="9" t="n"/>
+      <c r="J27" s="9" t="n"/>
+      <c r="K27" s="8" t="n"/>
       <c r="L27" s="29" t="n"/>
       <c r="M27" s="22" t="n"/>
       <c r="N27" s="30" t="n"/>
@@ -2417,15 +2426,15 @@
     <row r="28" ht="114" customHeight="1">
       <c r="A28" s="31" t="n"/>
       <c r="B28" s="22" t="n"/>
-      <c r="C28" s="9" t="n"/>
+      <c r="C28" s="7" t="n"/>
       <c r="D28" s="23" t="n"/>
       <c r="E28" s="22" t="n"/>
       <c r="F28" s="23" t="n"/>
       <c r="G28" s="22" t="n"/>
-      <c r="H28" s="10" t="n"/>
-      <c r="I28" s="11" t="n"/>
-      <c r="J28" s="11" t="n"/>
-      <c r="K28" s="10" t="n"/>
+      <c r="H28" s="8" t="n"/>
+      <c r="I28" s="9" t="n"/>
+      <c r="J28" s="9" t="n"/>
+      <c r="K28" s="8" t="n"/>
       <c r="L28" s="29" t="n"/>
       <c r="M28" s="22" t="n"/>
       <c r="N28" s="30" t="n"/>
@@ -2441,15 +2450,15 @@
     <row r="29" ht="114" customHeight="1">
       <c r="A29" s="31" t="n"/>
       <c r="B29" s="22" t="n"/>
-      <c r="C29" s="9" t="n"/>
+      <c r="C29" s="7" t="n"/>
       <c r="D29" s="23" t="n"/>
       <c r="E29" s="22" t="n"/>
       <c r="F29" s="23" t="n"/>
       <c r="G29" s="22" t="n"/>
-      <c r="H29" s="10" t="n"/>
-      <c r="I29" s="11" t="n"/>
-      <c r="J29" s="11" t="n"/>
-      <c r="K29" s="10" t="n"/>
+      <c r="H29" s="8" t="n"/>
+      <c r="I29" s="9" t="n"/>
+      <c r="J29" s="9" t="n"/>
+      <c r="K29" s="8" t="n"/>
       <c r="L29" s="29" t="n"/>
       <c r="M29" s="22" t="n"/>
       <c r="N29" s="30" t="n"/>
@@ -2463,7 +2472,7 @@
       <c r="V29" s="22" t="n"/>
     </row>
     <row r="30" ht="99" customFormat="1" customHeight="1" s="2">
-      <c r="A30" s="90" t="inlineStr">
+      <c r="A30" s="91" t="inlineStr">
         <is>
           <t>VIP DEPARTURE</t>
         </is>
@@ -2524,12 +2533,12 @@
           <t xml:space="preserve">ARR </t>
         </is>
       </c>
-      <c r="J31" s="8" t="inlineStr">
+      <c r="J31" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">DEP </t>
         </is>
       </c>
-      <c r="K31" s="8" t="inlineStr">
+      <c r="K31" s="6" t="inlineStr">
         <is>
           <t>Flight</t>
         </is>
@@ -2561,15 +2570,15 @@
     <row r="32" ht="114" customHeight="1">
       <c r="A32" s="31" t="n"/>
       <c r="B32" s="22" t="n"/>
-      <c r="C32" s="9" t="n"/>
+      <c r="C32" s="7" t="n"/>
       <c r="D32" s="23" t="n"/>
       <c r="E32" s="22" t="n"/>
       <c r="F32" s="23" t="n"/>
       <c r="G32" s="22" t="n"/>
-      <c r="H32" s="10" t="n"/>
-      <c r="I32" s="11" t="n"/>
-      <c r="J32" s="11" t="n"/>
-      <c r="K32" s="10" t="n"/>
+      <c r="H32" s="8" t="n"/>
+      <c r="I32" s="9" t="n"/>
+      <c r="J32" s="9" t="n"/>
+      <c r="K32" s="8" t="n"/>
       <c r="L32" s="29" t="n"/>
       <c r="M32" s="22" t="n"/>
       <c r="N32" s="30" t="n"/>
@@ -2585,15 +2594,15 @@
     <row r="33" ht="114" customHeight="1">
       <c r="A33" s="31" t="n"/>
       <c r="B33" s="22" t="n"/>
-      <c r="C33" s="9" t="n"/>
+      <c r="C33" s="7" t="n"/>
       <c r="D33" s="23" t="n"/>
       <c r="E33" s="22" t="n"/>
       <c r="F33" s="23" t="n"/>
       <c r="G33" s="22" t="n"/>
-      <c r="H33" s="10" t="n"/>
-      <c r="I33" s="11" t="n"/>
-      <c r="J33" s="11" t="n"/>
-      <c r="K33" s="10" t="n"/>
+      <c r="H33" s="8" t="n"/>
+      <c r="I33" s="9" t="n"/>
+      <c r="J33" s="9" t="n"/>
+      <c r="K33" s="8" t="n"/>
       <c r="L33" s="29" t="n"/>
       <c r="M33" s="22" t="n"/>
       <c r="N33" s="30" t="n"/>
@@ -2609,15 +2618,15 @@
     <row r="34" ht="114" customHeight="1">
       <c r="A34" s="31" t="n"/>
       <c r="B34" s="22" t="n"/>
-      <c r="C34" s="9" t="n"/>
+      <c r="C34" s="7" t="n"/>
       <c r="D34" s="23" t="n"/>
       <c r="E34" s="22" t="n"/>
       <c r="F34" s="23" t="n"/>
       <c r="G34" s="22" t="n"/>
-      <c r="H34" s="10" t="n"/>
-      <c r="I34" s="11" t="n"/>
-      <c r="J34" s="11" t="n"/>
-      <c r="K34" s="10" t="n"/>
+      <c r="H34" s="8" t="n"/>
+      <c r="I34" s="9" t="n"/>
+      <c r="J34" s="9" t="n"/>
+      <c r="K34" s="8" t="n"/>
       <c r="L34" s="29" t="n"/>
       <c r="M34" s="22" t="n"/>
       <c r="N34" s="30" t="n"/>
@@ -2633,15 +2642,15 @@
     <row r="35" ht="114" customHeight="1">
       <c r="A35" s="31" t="n"/>
       <c r="B35" s="22" t="n"/>
-      <c r="C35" s="9" t="n"/>
+      <c r="C35" s="7" t="n"/>
       <c r="D35" s="23" t="n"/>
       <c r="E35" s="22" t="n"/>
       <c r="F35" s="23" t="n"/>
       <c r="G35" s="22" t="n"/>
-      <c r="H35" s="10" t="n"/>
-      <c r="I35" s="11" t="n"/>
-      <c r="J35" s="11" t="n"/>
-      <c r="K35" s="10" t="n"/>
+      <c r="H35" s="8" t="n"/>
+      <c r="I35" s="9" t="n"/>
+      <c r="J35" s="9" t="n"/>
+      <c r="K35" s="8" t="n"/>
       <c r="L35" s="29" t="n"/>
       <c r="M35" s="22" t="n"/>
       <c r="N35" s="30" t="n"/>
@@ -2657,15 +2666,15 @@
     <row r="36" ht="114" customHeight="1">
       <c r="A36" s="31" t="n"/>
       <c r="B36" s="22" t="n"/>
-      <c r="C36" s="9" t="n"/>
+      <c r="C36" s="7" t="n"/>
       <c r="D36" s="23" t="n"/>
       <c r="E36" s="22" t="n"/>
       <c r="F36" s="23" t="n"/>
       <c r="G36" s="22" t="n"/>
-      <c r="H36" s="10" t="n"/>
-      <c r="I36" s="11" t="n"/>
-      <c r="J36" s="11" t="n"/>
-      <c r="K36" s="10" t="n"/>
+      <c r="H36" s="8" t="n"/>
+      <c r="I36" s="9" t="n"/>
+      <c r="J36" s="9" t="n"/>
+      <c r="K36" s="8" t="n"/>
       <c r="L36" s="29" t="n"/>
       <c r="M36" s="22" t="n"/>
       <c r="N36" s="30" t="n"/>
@@ -2681,15 +2690,15 @@
     <row r="37" ht="114" customHeight="1">
       <c r="A37" s="31" t="n"/>
       <c r="B37" s="22" t="n"/>
-      <c r="C37" s="9" t="n"/>
+      <c r="C37" s="7" t="n"/>
       <c r="D37" s="23" t="n"/>
       <c r="E37" s="22" t="n"/>
       <c r="F37" s="23" t="n"/>
       <c r="G37" s="22" t="n"/>
-      <c r="H37" s="10" t="n"/>
-      <c r="I37" s="11" t="n"/>
-      <c r="J37" s="11" t="n"/>
-      <c r="K37" s="10" t="n"/>
+      <c r="H37" s="8" t="n"/>
+      <c r="I37" s="9" t="n"/>
+      <c r="J37" s="9" t="n"/>
+      <c r="K37" s="8" t="n"/>
       <c r="L37" s="29" t="n"/>
       <c r="M37" s="22" t="n"/>
       <c r="N37" s="30" t="n"/>
@@ -2705,15 +2714,15 @@
     <row r="38" ht="114" customHeight="1">
       <c r="A38" s="31" t="n"/>
       <c r="B38" s="22" t="n"/>
-      <c r="C38" s="9" t="n"/>
+      <c r="C38" s="7" t="n"/>
       <c r="D38" s="23" t="n"/>
       <c r="E38" s="22" t="n"/>
       <c r="F38" s="23" t="n"/>
       <c r="G38" s="22" t="n"/>
-      <c r="H38" s="10" t="n"/>
-      <c r="I38" s="11" t="n"/>
-      <c r="J38" s="11" t="n"/>
-      <c r="K38" s="10" t="n"/>
+      <c r="H38" s="8" t="n"/>
+      <c r="I38" s="9" t="n"/>
+      <c r="J38" s="9" t="n"/>
+      <c r="K38" s="8" t="n"/>
       <c r="L38" s="29" t="n"/>
       <c r="M38" s="22" t="n"/>
       <c r="N38" s="30" t="n"/>
@@ -2729,15 +2738,15 @@
     <row r="39" ht="114" customHeight="1">
       <c r="A39" s="31" t="n"/>
       <c r="B39" s="22" t="n"/>
-      <c r="C39" s="9" t="n"/>
+      <c r="C39" s="7" t="n"/>
       <c r="D39" s="23" t="n"/>
       <c r="E39" s="22" t="n"/>
       <c r="F39" s="23" t="n"/>
       <c r="G39" s="22" t="n"/>
-      <c r="H39" s="10" t="n"/>
-      <c r="I39" s="11" t="n"/>
-      <c r="J39" s="11" t="n"/>
-      <c r="K39" s="10" t="n"/>
+      <c r="H39" s="8" t="n"/>
+      <c r="I39" s="9" t="n"/>
+      <c r="J39" s="9" t="n"/>
+      <c r="K39" s="8" t="n"/>
       <c r="L39" s="29" t="n"/>
       <c r="M39" s="22" t="n"/>
       <c r="N39" s="30" t="n"/>
@@ -2753,15 +2762,15 @@
     <row r="40" ht="114" customHeight="1">
       <c r="A40" s="31" t="n"/>
       <c r="B40" s="22" t="n"/>
-      <c r="C40" s="9" t="n"/>
+      <c r="C40" s="7" t="n"/>
       <c r="D40" s="23" t="n"/>
       <c r="E40" s="22" t="n"/>
       <c r="F40" s="23" t="n"/>
       <c r="G40" s="22" t="n"/>
-      <c r="H40" s="10" t="n"/>
-      <c r="I40" s="11" t="n"/>
-      <c r="J40" s="11" t="n"/>
-      <c r="K40" s="10" t="n"/>
+      <c r="H40" s="8" t="n"/>
+      <c r="I40" s="9" t="n"/>
+      <c r="J40" s="9" t="n"/>
+      <c r="K40" s="8" t="n"/>
       <c r="L40" s="29" t="n"/>
       <c r="M40" s="22" t="n"/>
       <c r="N40" s="30" t="n"/>
@@ -2777,15 +2786,15 @@
     <row r="41" ht="114" customHeight="1">
       <c r="A41" s="31" t="n"/>
       <c r="B41" s="22" t="n"/>
-      <c r="C41" s="9" t="n"/>
+      <c r="C41" s="7" t="n"/>
       <c r="D41" s="23" t="n"/>
       <c r="E41" s="22" t="n"/>
       <c r="F41" s="23" t="n"/>
       <c r="G41" s="22" t="n"/>
-      <c r="H41" s="10" t="n"/>
-      <c r="I41" s="11" t="n"/>
-      <c r="J41" s="11" t="n"/>
-      <c r="K41" s="10" t="n"/>
+      <c r="H41" s="8" t="n"/>
+      <c r="I41" s="9" t="n"/>
+      <c r="J41" s="9" t="n"/>
+      <c r="K41" s="8" t="n"/>
       <c r="L41" s="29" t="n"/>
       <c r="M41" s="22" t="n"/>
       <c r="N41" s="30" t="n"/>
@@ -2801,15 +2810,15 @@
     <row r="42" ht="114" customHeight="1">
       <c r="A42" s="31" t="n"/>
       <c r="B42" s="22" t="n"/>
-      <c r="C42" s="9" t="n"/>
+      <c r="C42" s="7" t="n"/>
       <c r="D42" s="23" t="n"/>
       <c r="E42" s="22" t="n"/>
       <c r="F42" s="23" t="n"/>
       <c r="G42" s="22" t="n"/>
-      <c r="H42" s="10" t="n"/>
-      <c r="I42" s="11" t="n"/>
-      <c r="J42" s="11" t="n"/>
-      <c r="K42" s="10" t="n"/>
+      <c r="H42" s="8" t="n"/>
+      <c r="I42" s="9" t="n"/>
+      <c r="J42" s="9" t="n"/>
+      <c r="K42" s="8" t="n"/>
       <c r="L42" s="29" t="n"/>
       <c r="M42" s="22" t="n"/>
       <c r="N42" s="30" t="n"/>
@@ -2825,15 +2834,15 @@
     <row r="43" ht="114" customHeight="1">
       <c r="A43" s="31" t="n"/>
       <c r="B43" s="22" t="n"/>
-      <c r="C43" s="9" t="n"/>
+      <c r="C43" s="7" t="n"/>
       <c r="D43" s="23" t="n"/>
       <c r="E43" s="22" t="n"/>
       <c r="F43" s="23" t="n"/>
       <c r="G43" s="22" t="n"/>
-      <c r="H43" s="10" t="n"/>
-      <c r="I43" s="11" t="n"/>
-      <c r="J43" s="11" t="n"/>
-      <c r="K43" s="10" t="n"/>
+      <c r="H43" s="8" t="n"/>
+      <c r="I43" s="9" t="n"/>
+      <c r="J43" s="9" t="n"/>
+      <c r="K43" s="8" t="n"/>
       <c r="L43" s="29" t="n"/>
       <c r="M43" s="22" t="n"/>
       <c r="N43" s="30" t="n"/>
@@ -2849,15 +2858,15 @@
     <row r="44" ht="114" customHeight="1">
       <c r="A44" s="31" t="n"/>
       <c r="B44" s="22" t="n"/>
-      <c r="C44" s="9" t="n"/>
+      <c r="C44" s="7" t="n"/>
       <c r="D44" s="23" t="n"/>
       <c r="E44" s="22" t="n"/>
       <c r="F44" s="23" t="n"/>
       <c r="G44" s="22" t="n"/>
-      <c r="H44" s="10" t="n"/>
-      <c r="I44" s="11" t="n"/>
-      <c r="J44" s="11" t="n"/>
-      <c r="K44" s="10" t="n"/>
+      <c r="H44" s="8" t="n"/>
+      <c r="I44" s="9" t="n"/>
+      <c r="J44" s="9" t="n"/>
+      <c r="K44" s="8" t="n"/>
       <c r="L44" s="29" t="n"/>
       <c r="M44" s="22" t="n"/>
       <c r="N44" s="30" t="n"/>
@@ -2873,15 +2882,15 @@
     <row r="45" ht="114" customHeight="1">
       <c r="A45" s="31" t="n"/>
       <c r="B45" s="22" t="n"/>
-      <c r="C45" s="9" t="n"/>
+      <c r="C45" s="7" t="n"/>
       <c r="D45" s="23" t="n"/>
       <c r="E45" s="22" t="n"/>
       <c r="F45" s="23" t="n"/>
       <c r="G45" s="22" t="n"/>
-      <c r="H45" s="10" t="n"/>
-      <c r="I45" s="11" t="n"/>
-      <c r="J45" s="11" t="n"/>
-      <c r="K45" s="10" t="n"/>
+      <c r="H45" s="8" t="n"/>
+      <c r="I45" s="9" t="n"/>
+      <c r="J45" s="9" t="n"/>
+      <c r="K45" s="8" t="n"/>
       <c r="L45" s="29" t="n"/>
       <c r="M45" s="22" t="n"/>
       <c r="N45" s="30" t="n"/>
@@ -2895,7 +2904,7 @@
       <c r="V45" s="22" t="n"/>
     </row>
     <row r="46" ht="99" customFormat="1" customHeight="1" s="2">
-      <c r="A46" s="90" t="inlineStr">
+      <c r="A46" s="91" t="inlineStr">
         <is>
           <t>Priority Guest (Handicap In House)</t>
         </is>
@@ -2956,12 +2965,12 @@
           <t xml:space="preserve">ARR </t>
         </is>
       </c>
-      <c r="J47" s="8" t="inlineStr">
+      <c r="J47" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">DEP </t>
         </is>
       </c>
-      <c r="K47" s="8" t="inlineStr">
+      <c r="K47" s="6" t="inlineStr">
         <is>
           <t>Flight</t>
         </is>
@@ -2993,15 +3002,15 @@
     <row r="48" ht="114" customHeight="1">
       <c r="A48" s="31" t="n"/>
       <c r="B48" s="22" t="n"/>
-      <c r="C48" s="9" t="n"/>
+      <c r="C48" s="7" t="n"/>
       <c r="D48" s="23" t="n"/>
       <c r="E48" s="22" t="n"/>
       <c r="F48" s="23" t="n"/>
       <c r="G48" s="22" t="n"/>
-      <c r="H48" s="10" t="n"/>
-      <c r="I48" s="11" t="n"/>
-      <c r="J48" s="11" t="n"/>
-      <c r="K48" s="10" t="n"/>
+      <c r="H48" s="8" t="n"/>
+      <c r="I48" s="9" t="n"/>
+      <c r="J48" s="9" t="n"/>
+      <c r="K48" s="8" t="n"/>
       <c r="L48" s="29" t="n"/>
       <c r="M48" s="22" t="n"/>
       <c r="N48" s="30" t="n"/>
@@ -3090,7 +3099,7 @@
       <c r="M51" s="25" t="n"/>
       <c r="N51" s="25" t="n"/>
       <c r="O51" s="22" t="n"/>
-      <c r="P51" s="64" t="n"/>
+      <c r="P51" s="65" t="n"/>
       <c r="Q51" s="25" t="n"/>
       <c r="R51" s="25" t="n"/>
       <c r="S51" s="25" t="n"/>
@@ -3114,7 +3123,7 @@
       <c r="M52" s="25" t="n"/>
       <c r="N52" s="25" t="n"/>
       <c r="O52" s="22" t="n"/>
-      <c r="P52" s="64" t="n"/>
+      <c r="P52" s="65" t="n"/>
       <c r="Q52" s="25" t="n"/>
       <c r="R52" s="25" t="n"/>
       <c r="S52" s="25" t="n"/>
@@ -3138,7 +3147,7 @@
       <c r="M53" s="25" t="n"/>
       <c r="N53" s="25" t="n"/>
       <c r="O53" s="22" t="n"/>
-      <c r="P53" s="64" t="n"/>
+      <c r="P53" s="65" t="n"/>
       <c r="Q53" s="25" t="n"/>
       <c r="R53" s="25" t="n"/>
       <c r="S53" s="25" t="n"/>
@@ -3222,55 +3231,55 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="117" customFormat="1" customHeight="1" s="12">
-      <c r="A56" s="58" t="n"/>
+    <row r="56" ht="117" customFormat="1" customHeight="1" s="10">
+      <c r="A56" s="59" t="n"/>
       <c r="B56" s="25" t="n"/>
       <c r="C56" s="25" t="n"/>
       <c r="D56" s="22" t="n"/>
-      <c r="E56" s="58" t="n"/>
+      <c r="E56" s="59" t="n"/>
       <c r="F56" s="25" t="n"/>
       <c r="G56" s="25" t="n"/>
       <c r="H56" s="25" t="n"/>
       <c r="I56" s="25" t="n"/>
       <c r="J56" s="25" t="n"/>
       <c r="K56" s="22" t="n"/>
-      <c r="L56" s="58" t="n"/>
+      <c r="L56" s="59" t="n"/>
       <c r="M56" s="25" t="n"/>
       <c r="N56" s="25" t="n"/>
       <c r="O56" s="22" t="n"/>
-      <c r="P56" s="58" t="n"/>
+      <c r="P56" s="59" t="n"/>
       <c r="Q56" s="22" t="n"/>
-      <c r="R56" s="58" t="n"/>
+      <c r="R56" s="59" t="n"/>
       <c r="S56" s="25" t="n"/>
       <c r="T56" s="25" t="n"/>
       <c r="U56" s="22" t="n"/>
-      <c r="V56" s="58" t="n"/>
-    </row>
-    <row r="57" ht="117" customFormat="1" customHeight="1" s="12">
-      <c r="A57" s="58" t="n"/>
+      <c r="V56" s="59" t="n"/>
+    </row>
+    <row r="57" ht="117" customFormat="1" customHeight="1" s="10">
+      <c r="A57" s="59" t="n"/>
       <c r="B57" s="25" t="n"/>
       <c r="C57" s="25" t="n"/>
       <c r="D57" s="22" t="n"/>
-      <c r="E57" s="58" t="n"/>
+      <c r="E57" s="59" t="n"/>
       <c r="F57" s="25" t="n"/>
       <c r="G57" s="25" t="n"/>
       <c r="H57" s="25" t="n"/>
       <c r="I57" s="25" t="n"/>
       <c r="J57" s="25" t="n"/>
       <c r="K57" s="22" t="n"/>
-      <c r="L57" s="58" t="n"/>
+      <c r="L57" s="59" t="n"/>
       <c r="M57" s="25" t="n"/>
       <c r="N57" s="25" t="n"/>
       <c r="O57" s="22" t="n"/>
-      <c r="P57" s="58" t="n"/>
+      <c r="P57" s="59" t="n"/>
       <c r="Q57" s="22" t="n"/>
-      <c r="R57" s="58" t="n"/>
+      <c r="R57" s="59" t="n"/>
       <c r="S57" s="25" t="n"/>
       <c r="T57" s="25" t="n"/>
       <c r="U57" s="22" t="n"/>
-      <c r="V57" s="58" t="n"/>
-    </row>
-    <row r="58" ht="103.5" customFormat="1" customHeight="1" s="12">
+      <c r="V57" s="59" t="n"/>
+    </row>
+    <row r="58" ht="103.5" customFormat="1" customHeight="1" s="10">
       <c r="A58" s="27" t="inlineStr">
         <is>
           <t>GROUP</t>
@@ -3298,7 +3307,7 @@
       <c r="U58" s="25" t="n"/>
       <c r="V58" s="22" t="n"/>
     </row>
-    <row r="59" ht="87.75" customFormat="1" customHeight="1" s="12">
+    <row r="59" ht="87.75" customFormat="1" customHeight="1" s="10">
       <c r="A59" s="28" t="inlineStr">
         <is>
           <t>Group Name</t>
@@ -3342,7 +3351,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="114" customFormat="1" customHeight="1" s="12">
+    <row r="60" ht="114" customFormat="1" customHeight="1" s="10">
       <c r="A60" s="24" t="n"/>
       <c r="B60" s="25" t="n"/>
       <c r="C60" s="25" t="n"/>
@@ -3366,8 +3375,8 @@
       <c r="U60" s="22" t="n"/>
       <c r="V60" s="24" t="n"/>
     </row>
-    <row r="61" ht="93.75" customFormat="1" customHeight="1" s="12">
-      <c r="A61" s="77" t="inlineStr">
+    <row r="61" ht="93.75" customFormat="1" customHeight="1" s="10">
+      <c r="A61" s="78" t="inlineStr">
         <is>
           <t>Outlet</t>
         </is>
@@ -3407,14 +3416,14 @@
       <c r="V61" s="22" t="n"/>
     </row>
     <row r="62" ht="114" customHeight="1">
-      <c r="A62" s="62" t="inlineStr">
+      <c r="A62" s="63" t="inlineStr">
         <is>
           <t>Elements</t>
         </is>
       </c>
       <c r="B62" s="50" t="n"/>
       <c r="C62" s="50" t="n"/>
-      <c r="D62" s="71" t="inlineStr">
+      <c r="D62" s="72" t="inlineStr">
         <is>
           <t>Opening from 06.30 - 10.30 for breakfast</t>
         </is>
@@ -3434,7 +3443,7 @@
       <c r="M62" s="50" t="n"/>
       <c r="N62" s="50" t="n"/>
       <c r="O62" s="50" t="n"/>
-      <c r="P62" s="63" t="inlineStr">
+      <c r="P62" s="64" t="inlineStr">
         <is>
           <t>Opening from 12.00 - 20.00</t>
         </is>
@@ -3450,7 +3459,7 @@
       <c r="A63" s="39" t="n"/>
       <c r="B63" s="52" t="n"/>
       <c r="C63" s="52" t="n"/>
-      <c r="D63" s="65" t="inlineStr">
+      <c r="D63" s="66" t="inlineStr">
         <is>
           <t>Opening from 18.00 - 22.00 for dinner (only Friday to Sunday)</t>
         </is>
@@ -3461,7 +3470,7 @@
       <c r="H63" s="25" t="n"/>
       <c r="I63" s="25" t="n"/>
       <c r="J63" s="22" t="n"/>
-      <c r="K63" s="56" t="inlineStr">
+      <c r="K63" s="57" t="inlineStr">
         <is>
           <t>Coco Fire</t>
         </is>
@@ -3483,14 +3492,14 @@
       <c r="V63" s="22" t="n"/>
     </row>
     <row r="64" ht="114" customHeight="1">
-      <c r="A64" s="62" t="inlineStr">
+      <c r="A64" s="63" t="inlineStr">
         <is>
           <t>The Pantry</t>
         </is>
       </c>
       <c r="B64" s="25" t="n"/>
       <c r="C64" s="25" t="n"/>
-      <c r="D64" s="74" t="inlineStr">
+      <c r="D64" s="75" t="inlineStr">
         <is>
           <t>Opening from 07.00 - 19.00</t>
         </is>
@@ -3501,7 +3510,7 @@
       <c r="H64" s="52" t="n"/>
       <c r="I64" s="52" t="n"/>
       <c r="J64" s="52" t="n"/>
-      <c r="K64" s="56" t="inlineStr">
+      <c r="K64" s="57" t="inlineStr">
         <is>
           <t>Mizu Bar</t>
         </is>
@@ -3523,14 +3532,14 @@
       <c r="V64" s="22" t="n"/>
     </row>
     <row r="65" ht="114" customHeight="1">
-      <c r="A65" s="56" t="inlineStr">
+      <c r="A65" s="57" t="inlineStr">
         <is>
           <t>Mi Scusi</t>
         </is>
       </c>
       <c r="B65" s="25" t="n"/>
       <c r="C65" s="25" t="n"/>
-      <c r="D65" s="65" t="inlineStr">
+      <c r="D65" s="66" t="inlineStr">
         <is>
           <t>Monday to Thursday 11.00 - 21.00 | Friday to Sunday 11.00 - 18.00</t>
         </is>
@@ -3541,7 +3550,7 @@
       <c r="H65" s="25" t="n"/>
       <c r="I65" s="25" t="n"/>
       <c r="J65" s="22" t="n"/>
-      <c r="K65" s="56" t="inlineStr">
+      <c r="K65" s="57" t="inlineStr">
         <is>
           <t>AvaniSpa</t>
         </is>
@@ -3550,7 +3559,7 @@
       <c r="M65" s="25" t="n"/>
       <c r="N65" s="25" t="n"/>
       <c r="O65" s="25" t="n"/>
-      <c r="P65" s="71" t="inlineStr">
+      <c r="P65" s="72" t="inlineStr">
         <is>
           <t>Opening from 09.00 - 21.00</t>
         </is>
@@ -3563,7 +3572,7 @@
       <c r="V65" s="22" t="n"/>
     </row>
     <row r="66" ht="114" customHeight="1">
-      <c r="A66" s="62" t="inlineStr">
+      <c r="A66" s="63" t="inlineStr">
         <is>
           <t>Scoop It</t>
         </is>
@@ -3581,7 +3590,7 @@
       <c r="H66" s="25" t="n"/>
       <c r="I66" s="25" t="n"/>
       <c r="J66" s="22" t="n"/>
-      <c r="K66" s="53" t="inlineStr">
+      <c r="K66" s="54" t="inlineStr">
         <is>
           <t>Mini Golf</t>
         </is>
@@ -3590,7 +3599,7 @@
       <c r="M66" s="25" t="n"/>
       <c r="N66" s="25" t="n"/>
       <c r="O66" s="25" t="n"/>
-      <c r="P66" s="66" t="inlineStr">
+      <c r="P66" s="67" t="inlineStr">
         <is>
           <t>Opening from 09.00 - 20.00</t>
         </is>
@@ -3603,7 +3612,7 @@
       <c r="V66" s="22" t="n"/>
     </row>
     <row r="67" ht="114" customHeight="1">
-      <c r="A67" s="56" t="inlineStr">
+      <c r="A67" s="57" t="inlineStr">
         <is>
           <t>The Beach House</t>
         </is>
@@ -3621,7 +3630,7 @@
       <c r="H67" s="25" t="n"/>
       <c r="I67" s="25" t="n"/>
       <c r="J67" s="22" t="n"/>
-      <c r="K67" s="53" t="inlineStr">
+      <c r="K67" s="54" t="inlineStr">
         <is>
           <t>AvaniKids</t>
         </is>
@@ -3630,7 +3639,7 @@
       <c r="M67" s="25" t="n"/>
       <c r="N67" s="25" t="n"/>
       <c r="O67" s="25" t="n"/>
-      <c r="P67" s="66" t="inlineStr">
+      <c r="P67" s="67" t="inlineStr">
         <is>
           <t>Opening from 09.00 - 20.00</t>
         </is>
@@ -3643,7 +3652,7 @@
       <c r="V67" s="22" t="n"/>
     </row>
     <row r="68" ht="114" customHeight="1">
-      <c r="A68" s="56" t="inlineStr">
+      <c r="A68" s="57" t="inlineStr">
         <is>
           <t>The Beach Bar</t>
         </is>
@@ -3661,7 +3670,7 @@
       <c r="H68" s="25" t="n"/>
       <c r="I68" s="25" t="n"/>
       <c r="J68" s="22" t="n"/>
-      <c r="K68" s="53" t="inlineStr">
+      <c r="K68" s="54" t="inlineStr">
         <is>
           <t>Tennis Court</t>
         </is>
@@ -3670,7 +3679,7 @@
       <c r="M68" s="25" t="n"/>
       <c r="N68" s="25" t="n"/>
       <c r="O68" s="25" t="n"/>
-      <c r="P68" s="66" t="inlineStr">
+      <c r="P68" s="67" t="inlineStr">
         <is>
           <t>Opening from 06.00 - 22.00</t>
         </is>
@@ -3683,7 +3692,7 @@
       <c r="V68" s="22" t="n"/>
     </row>
     <row r="69" ht="99" customFormat="1" customHeight="1" s="2">
-      <c r="A69" s="75" t="inlineStr">
+      <c r="A69" s="76" t="inlineStr">
         <is>
           <t>Room Available for Upsell</t>
         </is>
@@ -3693,7 +3702,7 @@
       <c r="D69" s="25" t="n"/>
       <c r="E69" s="25" t="n"/>
       <c r="F69" s="22" t="n"/>
-      <c r="G69" s="84" t="inlineStr">
+      <c r="G69" s="85" t="inlineStr">
         <is>
           <t>Room Number</t>
         </is>
@@ -3706,7 +3715,7 @@
       <c r="M69" s="25" t="n"/>
       <c r="N69" s="25" t="n"/>
       <c r="O69" s="22" t="n"/>
-      <c r="P69" s="84" t="inlineStr">
+      <c r="P69" s="85" t="inlineStr">
         <is>
           <t>Available unit</t>
         </is>
@@ -3719,7 +3728,7 @@
       <c r="V69" s="22" t="n"/>
     </row>
     <row r="70" ht="114" customHeight="1">
-      <c r="A70" s="60" t="inlineStr">
+      <c r="A70" s="61" t="inlineStr">
         <is>
           <t>Suite</t>
         </is>
@@ -3738,7 +3747,7 @@
       <c r="M70" s="25" t="n"/>
       <c r="N70" s="25" t="n"/>
       <c r="O70" s="22" t="n"/>
-      <c r="P70" s="73" t="n"/>
+      <c r="P70" s="74" t="n"/>
       <c r="Q70" s="25" t="n"/>
       <c r="R70" s="25" t="n"/>
       <c r="S70" s="25" t="n"/>
@@ -3747,7 +3756,7 @@
       <c r="V70" s="22" t="n"/>
     </row>
     <row r="71" ht="114" customHeight="1">
-      <c r="A71" s="60" t="inlineStr">
+      <c r="A71" s="61" t="inlineStr">
         <is>
           <t>Pool Access</t>
         </is>
@@ -3757,7 +3766,7 @@
       <c r="D71" s="25" t="n"/>
       <c r="E71" s="25" t="n"/>
       <c r="F71" s="22" t="n"/>
-      <c r="G71" s="73" t="n"/>
+      <c r="G71" s="74" t="n"/>
       <c r="H71" s="25" t="n"/>
       <c r="I71" s="25" t="n"/>
       <c r="J71" s="25" t="n"/>
@@ -3766,7 +3775,7 @@
       <c r="M71" s="25" t="n"/>
       <c r="N71" s="25" t="n"/>
       <c r="O71" s="22" t="n"/>
-      <c r="P71" s="73" t="n"/>
+      <c r="P71" s="74" t="n"/>
       <c r="Q71" s="25" t="n"/>
       <c r="R71" s="25" t="n"/>
       <c r="S71" s="25" t="n"/>
@@ -3775,7 +3784,7 @@
       <c r="V71" s="22" t="n"/>
     </row>
     <row r="72" ht="99" customFormat="1" customHeight="1" s="2">
-      <c r="A72" s="75" t="inlineStr">
+      <c r="A72" s="76" t="inlineStr">
         <is>
           <t>ReviewPro</t>
         </is>
@@ -3803,7 +3812,7 @@
       <c r="V72" s="22" t="n"/>
     </row>
     <row r="633" ht="101.25" customHeight="1">
-      <c r="A633" s="75" t="inlineStr">
+      <c r="A633" s="76" t="inlineStr">
         <is>
           <t>ReviewPro Comment</t>
         </is>

--- a/Briefing/Briefing.xlsx
+++ b/Briefing/Briefing.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="570" yWindow="1080" windowWidth="18660" windowHeight="16125" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="570" yWindow="270" windowWidth="16170" windowHeight="12105" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Ori Format" sheetId="1" state="visible" r:id="rId1"/>
@@ -17,33 +17,29 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm;@"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="#,###.##"/>
-    <numFmt numFmtId="167" formatCode="#.##&quot;%&quot;"/>
-    <numFmt numFmtId="168" formatCode="#.#0&quot;%&quot;"/>
-    <numFmt numFmtId="169" formatCode="#.##%"/>
-    <numFmt numFmtId="170" formatCode="#.###&quot;%&quot;"/>
-    <numFmt numFmtId="171" formatCode="0.00&quot;%&quot;"/>
+    <numFmt numFmtId="166" formatCode="#.##&quot;%&quot;"/>
+    <numFmt numFmtId="167" formatCode="#,###.##"/>
   </numFmts>
   <fonts count="23">
     <font>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <color rgb="FF006100"/>
       <sz val="11"/>
@@ -82,7 +78,7 @@
       <sz val="30"/>
     </font>
     <font>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <b val="1"/>
       <color theme="1"/>
@@ -140,7 +136,7 @@
       <sz val="30"/>
     </font>
     <font>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="30"/>
@@ -426,7 +422,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
@@ -436,7 +432,28 @@
     <xf numFmtId="164" fontId="4" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="10" fontId="9" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="4" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -451,35 +468,14 @@
     <xf numFmtId="14" fontId="13" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="9" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -547,6 +543,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="9" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -558,9 +557,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -577,7 +573,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -604,13 +600,13 @@
     <xf numFmtId="49" fontId="6" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="166" fontId="13" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="12" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
+    <xf numFmtId="166" fontId="10" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -628,7 +624,7 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
+    <xf numFmtId="167" fontId="10" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -655,37 +651,22 @@
     <xf numFmtId="0" fontId="16" fillId="10" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="13" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="167" fontId="10" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="13" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="9" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="13" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="13" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="13" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="13" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="171" fontId="13" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -934,39 +915,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -999,26 +980,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1051,23 +1015,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1129,6 +1076,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -1137,13 +1091,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1208,31 +1155,11 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1255,7 +1182,7 @@
     <col width="22.140625" customWidth="1" style="1" min="6" max="7"/>
     <col width="38.7109375" customWidth="1" style="1" min="8" max="8"/>
     <col width="43.85546875" customWidth="1" style="1" min="9" max="9"/>
-    <col width="43.85546875" customWidth="1" style="11" min="10" max="10"/>
+    <col width="43.85546875" customWidth="1" style="20" min="10" max="10"/>
     <col width="44.7109375" customWidth="1" style="1" min="11" max="11"/>
     <col width="41.28515625" customWidth="1" style="1" min="12" max="12"/>
     <col width="29.28515625" customWidth="1" style="1" min="13" max="13"/>
@@ -1268,13 +1195,13 @@
     <col width="28.7109375" customWidth="1" style="1" min="20" max="20"/>
     <col width="29.28515625" customWidth="1" style="1" min="21" max="21"/>
     <col width="110.7109375" customWidth="1" style="1" min="22" max="22"/>
-    <col width="10.42578125" customWidth="1" style="1" min="23" max="24"/>
-    <col width="10.42578125" customWidth="1" style="1" min="25" max="16384"/>
+    <col width="10.42578125" customWidth="1" style="1" min="23" max="25"/>
+    <col width="10.42578125" customWidth="1" style="1" min="26" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="336" customHeight="1">
       <c r="A1" s="81" t="n"/>
-      <c r="B1" s="50" t="n"/>
+      <c r="B1" s="51" t="n"/>
       <c r="C1" s="38" t="n"/>
       <c r="D1" s="73" t="inlineStr">
         <is>
@@ -1284,8 +1211,8 @@
 by 31 Dec. 2026</t>
         </is>
       </c>
-      <c r="E1" s="50" t="n"/>
-      <c r="F1" s="50" t="n"/>
+      <c r="E1" s="51" t="n"/>
+      <c r="F1" s="51" t="n"/>
       <c r="G1" s="38" t="n"/>
       <c r="H1" s="73" t="inlineStr">
         <is>
@@ -1314,9 +1241,9 @@
 by 31 Dec. 2026</t>
         </is>
       </c>
-      <c r="M1" s="50" t="n"/>
+      <c r="M1" s="51" t="n"/>
       <c r="N1" s="38" t="n"/>
-      <c r="O1" s="51" t="inlineStr">
+      <c r="O1" s="52" t="inlineStr">
         <is>
           <t xml:space="preserve">
 Enrollment Done: -
@@ -1325,10 +1252,10 @@
 YTD = -</t>
         </is>
       </c>
-      <c r="P1" s="50" t="n"/>
-      <c r="Q1" s="50" t="n"/>
+      <c r="P1" s="51" t="n"/>
+      <c r="Q1" s="51" t="n"/>
       <c r="R1" s="38" t="n"/>
-      <c r="S1" s="51" t="inlineStr">
+      <c r="S1" s="52" t="inlineStr">
         <is>
           <t xml:space="preserve">
 Hotel in Khao Lak 
@@ -1337,7 +1264,7 @@
 Goal #1</t>
         </is>
       </c>
-      <c r="T1" s="50" t="n"/>
+      <c r="T1" s="51" t="n"/>
       <c r="U1" s="38" t="n"/>
       <c r="V1" s="68" t="inlineStr">
         <is>
@@ -1355,25 +1282,25 @@
 ( Day ) July ( Date ), 2026</t>
         </is>
       </c>
-      <c r="B2" s="52" t="n"/>
+      <c r="B2" s="53" t="n"/>
       <c r="C2" s="40" t="n"/>
       <c r="D2" s="39" t="n"/>
-      <c r="E2" s="52" t="n"/>
-      <c r="F2" s="52" t="n"/>
+      <c r="E2" s="53" t="n"/>
+      <c r="F2" s="53" t="n"/>
       <c r="G2" s="40" t="n"/>
       <c r="H2" s="39" t="n"/>
       <c r="I2" s="40" t="n"/>
       <c r="J2" s="39" t="n"/>
       <c r="K2" s="40" t="n"/>
       <c r="L2" s="39" t="n"/>
-      <c r="M2" s="52" t="n"/>
+      <c r="M2" s="53" t="n"/>
       <c r="N2" s="40" t="n"/>
       <c r="O2" s="39" t="n"/>
-      <c r="P2" s="52" t="n"/>
-      <c r="Q2" s="52" t="n"/>
+      <c r="P2" s="53" t="n"/>
+      <c r="Q2" s="53" t="n"/>
       <c r="R2" s="40" t="n"/>
       <c r="S2" s="39" t="n"/>
-      <c r="T2" s="52" t="n"/>
+      <c r="T2" s="53" t="n"/>
       <c r="U2" s="40" t="n"/>
       <c r="V2" s="35" t="n"/>
     </row>
@@ -1383,7 +1310,7 @@
           <t>Yesterday</t>
         </is>
       </c>
-      <c r="B3" s="50" t="n"/>
+      <c r="B3" s="51" t="n"/>
       <c r="C3" s="38" t="n"/>
       <c r="D3" s="58" t="inlineStr">
         <is>
@@ -1415,7 +1342,7 @@
     </row>
     <row r="4" ht="88.5" customHeight="1">
       <c r="A4" s="39" t="n"/>
-      <c r="B4" s="52" t="n"/>
+      <c r="B4" s="53" t="n"/>
       <c r="C4" s="40" t="n"/>
       <c r="D4" s="62" t="inlineStr">
         <is>
@@ -1480,7 +1407,7 @@
       </c>
       <c r="B5" s="30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C5" s="38" t="n"/>
@@ -1491,12 +1418,12 @@
       </c>
       <c r="E5" s="30" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F5" s="30" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>115</t>
         </is>
       </c>
       <c r="G5" s="38" t="n"/>
@@ -1506,15 +1433,11 @@
 Upselling</t>
         </is>
       </c>
-      <c r="I5" s="53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J5" s="41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I5" s="41" t="n">
+        <v>3875.32</v>
+      </c>
+      <c r="J5" s="41" t="n">
+        <v>79801.19</v>
       </c>
       <c r="K5" s="70" t="n">
         <v>205427.65</v>
@@ -1526,52 +1449,52 @@
       </c>
       <c r="M5" s="37" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>123</t>
         </is>
       </c>
       <c r="N5" s="37" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>132</t>
         </is>
       </c>
       <c r="O5" s="37" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>59</t>
         </is>
       </c>
       <c r="P5" s="37" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>70</t>
         </is>
       </c>
       <c r="Q5" s="37" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>134</t>
         </is>
       </c>
       <c r="R5" s="37" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>156</t>
         </is>
       </c>
       <c r="S5" s="37" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>50</t>
         </is>
       </c>
       <c r="T5" s="37" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>57</t>
         </is>
       </c>
       <c r="U5" s="37" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>63</t>
         </is>
       </c>
       <c r="V5" s="37" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>74</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1567,12 @@
       </c>
       <c r="E7" s="30" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F7" s="30" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>81</t>
         </is>
       </c>
       <c r="G7" s="38" t="n"/>
@@ -1658,13 +1581,13 @@
           <t>Late C/O</t>
         </is>
       </c>
-      <c r="I7" s="41" t="n">
-        <v>2881.21</v>
-      </c>
-      <c r="J7" s="41" t="inlineStr">
+      <c r="I7" s="41" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="J7" s="41" t="n">
+        <v>46773.37</v>
       </c>
       <c r="K7" s="70" t="n">
         <v>29000</v>
@@ -1676,52 +1599,52 @@
       </c>
       <c r="M7" s="37" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>65</t>
         </is>
       </c>
       <c r="N7" s="37" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>72</t>
         </is>
       </c>
       <c r="O7" s="37" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>108</t>
         </is>
       </c>
       <c r="P7" s="37" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>116</t>
         </is>
       </c>
       <c r="Q7" s="37" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>82</t>
         </is>
       </c>
       <c r="R7" s="37" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>96</t>
         </is>
       </c>
       <c r="S7" s="37" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>114</t>
         </is>
       </c>
       <c r="T7" s="37" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>132</t>
         </is>
       </c>
       <c r="U7" s="37" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>61</t>
         </is>
       </c>
       <c r="V7" s="37" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>68</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1706,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C9" s="38" t="n"/>
@@ -1794,10 +1717,10 @@
       </c>
       <c r="E9" s="30" t="inlineStr">
         <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="F9" s="50" t="n"/>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="F9" s="51" t="n"/>
       <c r="G9" s="38" t="n"/>
       <c r="H9" s="28" t="inlineStr">
         <is>
@@ -1805,15 +1728,11 @@
 Comm. target</t>
         </is>
       </c>
-      <c r="I9" s="86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J9" s="41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I9" s="48" t="n">
+        <v>1267</v>
+      </c>
+      <c r="J9" s="48" t="n">
+        <v>65214</v>
       </c>
       <c r="K9" s="70" t="n">
         <v>160368</v>
@@ -1825,31 +1744,31 @@
       </c>
       <c r="M9" s="37" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>281</t>
         </is>
       </c>
       <c r="N9" s="38" t="n"/>
       <c r="O9" s="37" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>235</t>
         </is>
       </c>
       <c r="P9" s="38" t="n"/>
       <c r="Q9" s="37" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>295</t>
         </is>
       </c>
       <c r="R9" s="38" t="n"/>
       <c r="S9" s="37" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>220</t>
         </is>
       </c>
       <c r="T9" s="38" t="n"/>
       <c r="U9" s="37" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>228</t>
         </is>
       </c>
       <c r="V9" s="38" t="n"/>
@@ -1860,7 +1779,7 @@
       <c r="C10" s="40" t="n"/>
       <c r="D10" s="35" t="n"/>
       <c r="E10" s="39" t="n"/>
-      <c r="F10" s="52" t="n"/>
+      <c r="F10" s="53" t="n"/>
       <c r="G10" s="40" t="n"/>
       <c r="H10" s="47" t="n"/>
       <c r="I10" s="47" t="n"/>
@@ -1884,8 +1803,8 @@
           <t>ADR</t>
         </is>
       </c>
-      <c r="B11" s="77" t="n">
-        <v>4321.59</v>
+      <c r="B11" s="86" t="n">
+        <v>3595.79</v>
       </c>
       <c r="C11" s="22" t="n"/>
       <c r="D11" s="42" t="inlineStr">
@@ -1894,7 +1813,7 @@
         </is>
       </c>
       <c r="E11" s="87" t="n">
-        <v>57.8</v>
+        <v>66.06</v>
       </c>
       <c r="F11" s="25" t="n"/>
       <c r="G11" s="22" t="n"/>
@@ -1902,29 +1821,29 @@
       <c r="I11" s="35" t="n"/>
       <c r="J11" s="35" t="n"/>
       <c r="K11" s="35" t="n"/>
-      <c r="L11" s="5" t="inlineStr">
+      <c r="L11" s="10" t="inlineStr">
         <is>
           <t>OCC %</t>
         </is>
       </c>
       <c r="M11" s="88" t="n">
-        <v>69.70999999999999</v>
+        <v>85.84615384615385</v>
       </c>
       <c r="N11" s="22" t="n"/>
       <c r="O11" s="88" t="n">
-        <v>69.70999999999999</v>
+        <v>71.69230769230769</v>
       </c>
       <c r="P11" s="22" t="n"/>
       <c r="Q11" s="88" t="n">
-        <v>69.70999999999999</v>
+        <v>90.15384615384615</v>
       </c>
       <c r="R11" s="22" t="n"/>
       <c r="S11" s="88" t="n">
-        <v>69.70999999999999</v>
+        <v>67.07692307692308</v>
       </c>
       <c r="T11" s="22" t="n"/>
       <c r="U11" s="88" t="n">
-        <v>69.70999999999999</v>
+        <v>69.53846153846153</v>
       </c>
       <c r="V11" s="22" t="n"/>
     </row>
@@ -1935,7 +1854,7 @@
         </is>
       </c>
       <c r="B12" s="89" t="n">
-        <v>69.70999999999999</v>
+        <v>71.53</v>
       </c>
       <c r="C12" s="38" t="n"/>
       <c r="D12" s="42" t="inlineStr">
@@ -1955,7 +1874,7 @@
       </c>
       <c r="G12" s="34" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>648</t>
         </is>
       </c>
       <c r="H12" s="28" t="inlineStr">
@@ -1964,12 +1883,10 @@
         </is>
       </c>
       <c r="I12" s="79" t="n">
-        <v>2738.33</v>
-      </c>
-      <c r="J12" s="41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3928.97</v>
+      </c>
+      <c r="J12" s="41" t="n">
+        <v>70219.72</v>
       </c>
       <c r="K12" s="80" t="n">
         <v>180414</v>
@@ -1982,31 +1899,31 @@
       </c>
       <c r="M12" s="37" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>780</t>
         </is>
       </c>
       <c r="N12" s="38" t="n"/>
       <c r="O12" s="37" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>693</t>
         </is>
       </c>
       <c r="P12" s="38" t="n"/>
       <c r="Q12" s="37" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>797</t>
         </is>
       </c>
       <c r="R12" s="38" t="n"/>
       <c r="S12" s="37" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>632</t>
         </is>
       </c>
       <c r="T12" s="38" t="n"/>
       <c r="U12" s="37" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>615</t>
         </is>
       </c>
       <c r="V12" s="38" t="n"/>
@@ -2045,26 +1962,26 @@
           <t>VIP ARRIVAL</t>
         </is>
       </c>
-      <c r="B14" s="50" t="n"/>
-      <c r="C14" s="50" t="n"/>
-      <c r="D14" s="50" t="n"/>
-      <c r="E14" s="50" t="n"/>
-      <c r="F14" s="50" t="n"/>
-      <c r="G14" s="50" t="n"/>
-      <c r="H14" s="50" t="n"/>
-      <c r="I14" s="50" t="n"/>
-      <c r="J14" s="50" t="n"/>
-      <c r="K14" s="50" t="n"/>
-      <c r="L14" s="50" t="n"/>
-      <c r="M14" s="50" t="n"/>
-      <c r="N14" s="50" t="n"/>
-      <c r="O14" s="50" t="n"/>
-      <c r="P14" s="50" t="n"/>
-      <c r="Q14" s="50" t="n"/>
-      <c r="R14" s="50" t="n"/>
-      <c r="S14" s="50" t="n"/>
-      <c r="T14" s="50" t="n"/>
-      <c r="U14" s="50" t="n"/>
+      <c r="B14" s="51" t="n"/>
+      <c r="C14" s="51" t="n"/>
+      <c r="D14" s="51" t="n"/>
+      <c r="E14" s="51" t="n"/>
+      <c r="F14" s="51" t="n"/>
+      <c r="G14" s="51" t="n"/>
+      <c r="H14" s="51" t="n"/>
+      <c r="I14" s="51" t="n"/>
+      <c r="J14" s="51" t="n"/>
+      <c r="K14" s="51" t="n"/>
+      <c r="L14" s="51" t="n"/>
+      <c r="M14" s="51" t="n"/>
+      <c r="N14" s="51" t="n"/>
+      <c r="O14" s="51" t="n"/>
+      <c r="P14" s="51" t="n"/>
+      <c r="Q14" s="51" t="n"/>
+      <c r="R14" s="51" t="n"/>
+      <c r="S14" s="51" t="n"/>
+      <c r="T14" s="51" t="n"/>
+      <c r="U14" s="51" t="n"/>
       <c r="V14" s="38" t="n"/>
     </row>
     <row r="15" ht="96" customHeight="1">
@@ -2101,12 +2018,12 @@
           <t xml:space="preserve">ARR </t>
         </is>
       </c>
-      <c r="J15" s="6" t="inlineStr">
+      <c r="J15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">DEP </t>
         </is>
       </c>
-      <c r="K15" s="6" t="inlineStr">
+      <c r="K15" s="13" t="inlineStr">
         <is>
           <t>Flight</t>
         </is>
@@ -2138,15 +2055,15 @@
     <row r="16" ht="114" customHeight="1">
       <c r="A16" s="31" t="n"/>
       <c r="B16" s="22" t="n"/>
-      <c r="C16" s="7" t="n"/>
+      <c r="C16" s="14" t="n"/>
       <c r="D16" s="23" t="n"/>
       <c r="E16" s="22" t="n"/>
       <c r="F16" s="23" t="n"/>
       <c r="G16" s="22" t="n"/>
-      <c r="H16" s="8" t="n"/>
-      <c r="I16" s="9" t="n"/>
-      <c r="J16" s="9" t="n"/>
-      <c r="K16" s="8" t="n"/>
+      <c r="H16" s="15" t="n"/>
+      <c r="I16" s="16" t="n"/>
+      <c r="J16" s="16" t="n"/>
+      <c r="K16" s="15" t="n"/>
       <c r="L16" s="29" t="n"/>
       <c r="M16" s="22" t="n"/>
       <c r="N16" s="30" t="n"/>
@@ -2162,15 +2079,15 @@
     <row r="17" ht="114" customHeight="1">
       <c r="A17" s="31" t="n"/>
       <c r="B17" s="22" t="n"/>
-      <c r="C17" s="7" t="n"/>
+      <c r="C17" s="14" t="n"/>
       <c r="D17" s="23" t="n"/>
       <c r="E17" s="22" t="n"/>
       <c r="F17" s="23" t="n"/>
       <c r="G17" s="22" t="n"/>
-      <c r="H17" s="8" t="n"/>
-      <c r="I17" s="9" t="n"/>
-      <c r="J17" s="9" t="n"/>
-      <c r="K17" s="8" t="n"/>
+      <c r="H17" s="15" t="n"/>
+      <c r="I17" s="16" t="n"/>
+      <c r="J17" s="16" t="n"/>
+      <c r="K17" s="15" t="n"/>
       <c r="L17" s="29" t="n"/>
       <c r="M17" s="22" t="n"/>
       <c r="N17" s="30" t="n"/>
@@ -2186,15 +2103,15 @@
     <row r="18" ht="114" customHeight="1">
       <c r="A18" s="31" t="n"/>
       <c r="B18" s="22" t="n"/>
-      <c r="C18" s="7" t="n"/>
+      <c r="C18" s="14" t="n"/>
       <c r="D18" s="23" t="n"/>
       <c r="E18" s="22" t="n"/>
       <c r="F18" s="23" t="n"/>
       <c r="G18" s="22" t="n"/>
-      <c r="H18" s="8" t="n"/>
-      <c r="I18" s="9" t="n"/>
-      <c r="J18" s="9" t="n"/>
-      <c r="K18" s="8" t="n"/>
+      <c r="H18" s="15" t="n"/>
+      <c r="I18" s="16" t="n"/>
+      <c r="J18" s="16" t="n"/>
+      <c r="K18" s="15" t="n"/>
       <c r="L18" s="29" t="n"/>
       <c r="M18" s="22" t="n"/>
       <c r="N18" s="30" t="n"/>
@@ -2210,15 +2127,15 @@
     <row r="19" ht="114" customHeight="1">
       <c r="A19" s="31" t="n"/>
       <c r="B19" s="22" t="n"/>
-      <c r="C19" s="7" t="n"/>
+      <c r="C19" s="14" t="n"/>
       <c r="D19" s="23" t="n"/>
       <c r="E19" s="22" t="n"/>
       <c r="F19" s="23" t="n"/>
       <c r="G19" s="22" t="n"/>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="9" t="n"/>
-      <c r="J19" s="9" t="n"/>
-      <c r="K19" s="8" t="n"/>
+      <c r="H19" s="15" t="n"/>
+      <c r="I19" s="16" t="n"/>
+      <c r="J19" s="16" t="n"/>
+      <c r="K19" s="15" t="n"/>
       <c r="L19" s="29" t="n"/>
       <c r="M19" s="22" t="n"/>
       <c r="N19" s="30" t="n"/>
@@ -2234,15 +2151,15 @@
     <row r="20" ht="114" customHeight="1">
       <c r="A20" s="31" t="n"/>
       <c r="B20" s="22" t="n"/>
-      <c r="C20" s="7" t="n"/>
+      <c r="C20" s="14" t="n"/>
       <c r="D20" s="23" t="n"/>
       <c r="E20" s="22" t="n"/>
       <c r="F20" s="23" t="n"/>
       <c r="G20" s="22" t="n"/>
-      <c r="H20" s="8" t="n"/>
-      <c r="I20" s="9" t="n"/>
-      <c r="J20" s="9" t="n"/>
-      <c r="K20" s="8" t="n"/>
+      <c r="H20" s="15" t="n"/>
+      <c r="I20" s="16" t="n"/>
+      <c r="J20" s="16" t="n"/>
+      <c r="K20" s="15" t="n"/>
       <c r="L20" s="29" t="n"/>
       <c r="M20" s="22" t="n"/>
       <c r="N20" s="30" t="n"/>
@@ -2258,15 +2175,15 @@
     <row r="21" ht="114" customHeight="1">
       <c r="A21" s="31" t="n"/>
       <c r="B21" s="22" t="n"/>
-      <c r="C21" s="7" t="n"/>
+      <c r="C21" s="14" t="n"/>
       <c r="D21" s="23" t="n"/>
       <c r="E21" s="22" t="n"/>
       <c r="F21" s="23" t="n"/>
       <c r="G21" s="22" t="n"/>
-      <c r="H21" s="8" t="n"/>
-      <c r="I21" s="9" t="n"/>
-      <c r="J21" s="9" t="n"/>
-      <c r="K21" s="8" t="n"/>
+      <c r="H21" s="15" t="n"/>
+      <c r="I21" s="16" t="n"/>
+      <c r="J21" s="16" t="n"/>
+      <c r="K21" s="15" t="n"/>
       <c r="L21" s="29" t="n"/>
       <c r="M21" s="22" t="n"/>
       <c r="N21" s="30" t="n"/>
@@ -2282,15 +2199,15 @@
     <row r="22" ht="114" customHeight="1">
       <c r="A22" s="31" t="n"/>
       <c r="B22" s="22" t="n"/>
-      <c r="C22" s="7" t="n"/>
+      <c r="C22" s="14" t="n"/>
       <c r="D22" s="23" t="n"/>
       <c r="E22" s="22" t="n"/>
       <c r="F22" s="23" t="n"/>
       <c r="G22" s="22" t="n"/>
-      <c r="H22" s="8" t="n"/>
-      <c r="I22" s="9" t="n"/>
-      <c r="J22" s="9" t="n"/>
-      <c r="K22" s="8" t="n"/>
+      <c r="H22" s="15" t="n"/>
+      <c r="I22" s="16" t="n"/>
+      <c r="J22" s="16" t="n"/>
+      <c r="K22" s="15" t="n"/>
       <c r="L22" s="29" t="n"/>
       <c r="M22" s="22" t="n"/>
       <c r="N22" s="30" t="n"/>
@@ -2306,15 +2223,15 @@
     <row r="23" ht="114" customHeight="1">
       <c r="A23" s="31" t="n"/>
       <c r="B23" s="22" t="n"/>
-      <c r="C23" s="7" t="n"/>
+      <c r="C23" s="14" t="n"/>
       <c r="D23" s="23" t="n"/>
       <c r="E23" s="22" t="n"/>
       <c r="F23" s="23" t="n"/>
       <c r="G23" s="22" t="n"/>
-      <c r="H23" s="8" t="n"/>
-      <c r="I23" s="9" t="n"/>
-      <c r="J23" s="9" t="n"/>
-      <c r="K23" s="8" t="n"/>
+      <c r="H23" s="15" t="n"/>
+      <c r="I23" s="16" t="n"/>
+      <c r="J23" s="16" t="n"/>
+      <c r="K23" s="15" t="n"/>
       <c r="L23" s="29" t="n"/>
       <c r="M23" s="22" t="n"/>
       <c r="N23" s="30" t="n"/>
@@ -2330,15 +2247,15 @@
     <row r="24" ht="114" customHeight="1">
       <c r="A24" s="31" t="n"/>
       <c r="B24" s="22" t="n"/>
-      <c r="C24" s="7" t="n"/>
+      <c r="C24" s="14" t="n"/>
       <c r="D24" s="23" t="n"/>
       <c r="E24" s="22" t="n"/>
       <c r="F24" s="23" t="n"/>
       <c r="G24" s="22" t="n"/>
-      <c r="H24" s="8" t="n"/>
-      <c r="I24" s="9" t="n"/>
-      <c r="J24" s="9" t="n"/>
-      <c r="K24" s="8" t="n"/>
+      <c r="H24" s="15" t="n"/>
+      <c r="I24" s="16" t="n"/>
+      <c r="J24" s="16" t="n"/>
+      <c r="K24" s="15" t="n"/>
       <c r="L24" s="29" t="n"/>
       <c r="M24" s="22" t="n"/>
       <c r="N24" s="30" t="n"/>
@@ -2354,15 +2271,15 @@
     <row r="25" ht="114" customHeight="1">
       <c r="A25" s="31" t="n"/>
       <c r="B25" s="22" t="n"/>
-      <c r="C25" s="7" t="n"/>
+      <c r="C25" s="14" t="n"/>
       <c r="D25" s="23" t="n"/>
       <c r="E25" s="22" t="n"/>
       <c r="F25" s="23" t="n"/>
       <c r="G25" s="22" t="n"/>
-      <c r="H25" s="8" t="n"/>
-      <c r="I25" s="9" t="n"/>
-      <c r="J25" s="9" t="n"/>
-      <c r="K25" s="8" t="n"/>
+      <c r="H25" s="15" t="n"/>
+      <c r="I25" s="16" t="n"/>
+      <c r="J25" s="16" t="n"/>
+      <c r="K25" s="15" t="n"/>
       <c r="L25" s="29" t="n"/>
       <c r="M25" s="22" t="n"/>
       <c r="N25" s="30" t="n"/>
@@ -2378,15 +2295,15 @@
     <row r="26" ht="114" customHeight="1">
       <c r="A26" s="31" t="n"/>
       <c r="B26" s="22" t="n"/>
-      <c r="C26" s="7" t="n"/>
+      <c r="C26" s="14" t="n"/>
       <c r="D26" s="23" t="n"/>
       <c r="E26" s="22" t="n"/>
       <c r="F26" s="23" t="n"/>
       <c r="G26" s="22" t="n"/>
-      <c r="H26" s="8" t="n"/>
-      <c r="I26" s="9" t="n"/>
-      <c r="J26" s="9" t="n"/>
-      <c r="K26" s="8" t="n"/>
+      <c r="H26" s="15" t="n"/>
+      <c r="I26" s="16" t="n"/>
+      <c r="J26" s="16" t="n"/>
+      <c r="K26" s="15" t="n"/>
       <c r="L26" s="29" t="n"/>
       <c r="M26" s="22" t="n"/>
       <c r="N26" s="30" t="n"/>
@@ -2402,15 +2319,15 @@
     <row r="27" ht="114" customHeight="1">
       <c r="A27" s="31" t="n"/>
       <c r="B27" s="22" t="n"/>
-      <c r="C27" s="7" t="n"/>
+      <c r="C27" s="14" t="n"/>
       <c r="D27" s="23" t="n"/>
       <c r="E27" s="22" t="n"/>
       <c r="F27" s="23" t="n"/>
       <c r="G27" s="22" t="n"/>
-      <c r="H27" s="8" t="n"/>
-      <c r="I27" s="9" t="n"/>
-      <c r="J27" s="9" t="n"/>
-      <c r="K27" s="8" t="n"/>
+      <c r="H27" s="15" t="n"/>
+      <c r="I27" s="16" t="n"/>
+      <c r="J27" s="16" t="n"/>
+      <c r="K27" s="15" t="n"/>
       <c r="L27" s="29" t="n"/>
       <c r="M27" s="22" t="n"/>
       <c r="N27" s="30" t="n"/>
@@ -2426,15 +2343,15 @@
     <row r="28" ht="114" customHeight="1">
       <c r="A28" s="31" t="n"/>
       <c r="B28" s="22" t="n"/>
-      <c r="C28" s="7" t="n"/>
+      <c r="C28" s="14" t="n"/>
       <c r="D28" s="23" t="n"/>
       <c r="E28" s="22" t="n"/>
       <c r="F28" s="23" t="n"/>
       <c r="G28" s="22" t="n"/>
-      <c r="H28" s="8" t="n"/>
-      <c r="I28" s="9" t="n"/>
-      <c r="J28" s="9" t="n"/>
-      <c r="K28" s="8" t="n"/>
+      <c r="H28" s="15" t="n"/>
+      <c r="I28" s="16" t="n"/>
+      <c r="J28" s="16" t="n"/>
+      <c r="K28" s="15" t="n"/>
       <c r="L28" s="29" t="n"/>
       <c r="M28" s="22" t="n"/>
       <c r="N28" s="30" t="n"/>
@@ -2450,15 +2367,15 @@
     <row r="29" ht="114" customHeight="1">
       <c r="A29" s="31" t="n"/>
       <c r="B29" s="22" t="n"/>
-      <c r="C29" s="7" t="n"/>
+      <c r="C29" s="14" t="n"/>
       <c r="D29" s="23" t="n"/>
       <c r="E29" s="22" t="n"/>
       <c r="F29" s="23" t="n"/>
       <c r="G29" s="22" t="n"/>
-      <c r="H29" s="8" t="n"/>
-      <c r="I29" s="9" t="n"/>
-      <c r="J29" s="9" t="n"/>
-      <c r="K29" s="8" t="n"/>
+      <c r="H29" s="15" t="n"/>
+      <c r="I29" s="16" t="n"/>
+      <c r="J29" s="16" t="n"/>
+      <c r="K29" s="15" t="n"/>
       <c r="L29" s="29" t="n"/>
       <c r="M29" s="22" t="n"/>
       <c r="N29" s="30" t="n"/>
@@ -2533,12 +2450,12 @@
           <t xml:space="preserve">ARR </t>
         </is>
       </c>
-      <c r="J31" s="6" t="inlineStr">
+      <c r="J31" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">DEP </t>
         </is>
       </c>
-      <c r="K31" s="6" t="inlineStr">
+      <c r="K31" s="13" t="inlineStr">
         <is>
           <t>Flight</t>
         </is>
@@ -2570,15 +2487,15 @@
     <row r="32" ht="114" customHeight="1">
       <c r="A32" s="31" t="n"/>
       <c r="B32" s="22" t="n"/>
-      <c r="C32" s="7" t="n"/>
+      <c r="C32" s="14" t="n"/>
       <c r="D32" s="23" t="n"/>
       <c r="E32" s="22" t="n"/>
       <c r="F32" s="23" t="n"/>
       <c r="G32" s="22" t="n"/>
-      <c r="H32" s="8" t="n"/>
-      <c r="I32" s="9" t="n"/>
-      <c r="J32" s="9" t="n"/>
-      <c r="K32" s="8" t="n"/>
+      <c r="H32" s="15" t="n"/>
+      <c r="I32" s="16" t="n"/>
+      <c r="J32" s="16" t="n"/>
+      <c r="K32" s="15" t="n"/>
       <c r="L32" s="29" t="n"/>
       <c r="M32" s="22" t="n"/>
       <c r="N32" s="30" t="n"/>
@@ -2594,15 +2511,15 @@
     <row r="33" ht="114" customHeight="1">
       <c r="A33" s="31" t="n"/>
       <c r="B33" s="22" t="n"/>
-      <c r="C33" s="7" t="n"/>
+      <c r="C33" s="14" t="n"/>
       <c r="D33" s="23" t="n"/>
       <c r="E33" s="22" t="n"/>
       <c r="F33" s="23" t="n"/>
       <c r="G33" s="22" t="n"/>
-      <c r="H33" s="8" t="n"/>
-      <c r="I33" s="9" t="n"/>
-      <c r="J33" s="9" t="n"/>
-      <c r="K33" s="8" t="n"/>
+      <c r="H33" s="15" t="n"/>
+      <c r="I33" s="16" t="n"/>
+      <c r="J33" s="16" t="n"/>
+      <c r="K33" s="15" t="n"/>
       <c r="L33" s="29" t="n"/>
       <c r="M33" s="22" t="n"/>
       <c r="N33" s="30" t="n"/>
@@ -2618,15 +2535,15 @@
     <row r="34" ht="114" customHeight="1">
       <c r="A34" s="31" t="n"/>
       <c r="B34" s="22" t="n"/>
-      <c r="C34" s="7" t="n"/>
+      <c r="C34" s="14" t="n"/>
       <c r="D34" s="23" t="n"/>
       <c r="E34" s="22" t="n"/>
       <c r="F34" s="23" t="n"/>
       <c r="G34" s="22" t="n"/>
-      <c r="H34" s="8" t="n"/>
-      <c r="I34" s="9" t="n"/>
-      <c r="J34" s="9" t="n"/>
-      <c r="K34" s="8" t="n"/>
+      <c r="H34" s="15" t="n"/>
+      <c r="I34" s="16" t="n"/>
+      <c r="J34" s="16" t="n"/>
+      <c r="K34" s="15" t="n"/>
       <c r="L34" s="29" t="n"/>
       <c r="M34" s="22" t="n"/>
       <c r="N34" s="30" t="n"/>
@@ -2642,15 +2559,15 @@
     <row r="35" ht="114" customHeight="1">
       <c r="A35" s="31" t="n"/>
       <c r="B35" s="22" t="n"/>
-      <c r="C35" s="7" t="n"/>
+      <c r="C35" s="14" t="n"/>
       <c r="D35" s="23" t="n"/>
       <c r="E35" s="22" t="n"/>
       <c r="F35" s="23" t="n"/>
       <c r="G35" s="22" t="n"/>
-      <c r="H35" s="8" t="n"/>
-      <c r="I35" s="9" t="n"/>
-      <c r="J35" s="9" t="n"/>
-      <c r="K35" s="8" t="n"/>
+      <c r="H35" s="15" t="n"/>
+      <c r="I35" s="16" t="n"/>
+      <c r="J35" s="16" t="n"/>
+      <c r="K35" s="15" t="n"/>
       <c r="L35" s="29" t="n"/>
       <c r="M35" s="22" t="n"/>
       <c r="N35" s="30" t="n"/>
@@ -2666,15 +2583,15 @@
     <row r="36" ht="114" customHeight="1">
       <c r="A36" s="31" t="n"/>
       <c r="B36" s="22" t="n"/>
-      <c r="C36" s="7" t="n"/>
+      <c r="C36" s="14" t="n"/>
       <c r="D36" s="23" t="n"/>
       <c r="E36" s="22" t="n"/>
       <c r="F36" s="23" t="n"/>
       <c r="G36" s="22" t="n"/>
-      <c r="H36" s="8" t="n"/>
-      <c r="I36" s="9" t="n"/>
-      <c r="J36" s="9" t="n"/>
-      <c r="K36" s="8" t="n"/>
+      <c r="H36" s="15" t="n"/>
+      <c r="I36" s="16" t="n"/>
+      <c r="J36" s="16" t="n"/>
+      <c r="K36" s="15" t="n"/>
       <c r="L36" s="29" t="n"/>
       <c r="M36" s="22" t="n"/>
       <c r="N36" s="30" t="n"/>
@@ -2690,15 +2607,15 @@
     <row r="37" ht="114" customHeight="1">
       <c r="A37" s="31" t="n"/>
       <c r="B37" s="22" t="n"/>
-      <c r="C37" s="7" t="n"/>
+      <c r="C37" s="14" t="n"/>
       <c r="D37" s="23" t="n"/>
       <c r="E37" s="22" t="n"/>
       <c r="F37" s="23" t="n"/>
       <c r="G37" s="22" t="n"/>
-      <c r="H37" s="8" t="n"/>
-      <c r="I37" s="9" t="n"/>
-      <c r="J37" s="9" t="n"/>
-      <c r="K37" s="8" t="n"/>
+      <c r="H37" s="15" t="n"/>
+      <c r="I37" s="16" t="n"/>
+      <c r="J37" s="16" t="n"/>
+      <c r="K37" s="15" t="n"/>
       <c r="L37" s="29" t="n"/>
       <c r="M37" s="22" t="n"/>
       <c r="N37" s="30" t="n"/>
@@ -2714,15 +2631,15 @@
     <row r="38" ht="114" customHeight="1">
       <c r="A38" s="31" t="n"/>
       <c r="B38" s="22" t="n"/>
-      <c r="C38" s="7" t="n"/>
+      <c r="C38" s="14" t="n"/>
       <c r="D38" s="23" t="n"/>
       <c r="E38" s="22" t="n"/>
       <c r="F38" s="23" t="n"/>
       <c r="G38" s="22" t="n"/>
-      <c r="H38" s="8" t="n"/>
-      <c r="I38" s="9" t="n"/>
-      <c r="J38" s="9" t="n"/>
-      <c r="K38" s="8" t="n"/>
+      <c r="H38" s="15" t="n"/>
+      <c r="I38" s="16" t="n"/>
+      <c r="J38" s="16" t="n"/>
+      <c r="K38" s="15" t="n"/>
       <c r="L38" s="29" t="n"/>
       <c r="M38" s="22" t="n"/>
       <c r="N38" s="30" t="n"/>
@@ -2738,15 +2655,15 @@
     <row r="39" ht="114" customHeight="1">
       <c r="A39" s="31" t="n"/>
       <c r="B39" s="22" t="n"/>
-      <c r="C39" s="7" t="n"/>
+      <c r="C39" s="14" t="n"/>
       <c r="D39" s="23" t="n"/>
       <c r="E39" s="22" t="n"/>
       <c r="F39" s="23" t="n"/>
       <c r="G39" s="22" t="n"/>
-      <c r="H39" s="8" t="n"/>
-      <c r="I39" s="9" t="n"/>
-      <c r="J39" s="9" t="n"/>
-      <c r="K39" s="8" t="n"/>
+      <c r="H39" s="15" t="n"/>
+      <c r="I39" s="16" t="n"/>
+      <c r="J39" s="16" t="n"/>
+      <c r="K39" s="15" t="n"/>
       <c r="L39" s="29" t="n"/>
       <c r="M39" s="22" t="n"/>
       <c r="N39" s="30" t="n"/>
@@ -2762,15 +2679,15 @@
     <row r="40" ht="114" customHeight="1">
       <c r="A40" s="31" t="n"/>
       <c r="B40" s="22" t="n"/>
-      <c r="C40" s="7" t="n"/>
+      <c r="C40" s="14" t="n"/>
       <c r="D40" s="23" t="n"/>
       <c r="E40" s="22" t="n"/>
       <c r="F40" s="23" t="n"/>
       <c r="G40" s="22" t="n"/>
-      <c r="H40" s="8" t="n"/>
-      <c r="I40" s="9" t="n"/>
-      <c r="J40" s="9" t="n"/>
-      <c r="K40" s="8" t="n"/>
+      <c r="H40" s="15" t="n"/>
+      <c r="I40" s="16" t="n"/>
+      <c r="J40" s="16" t="n"/>
+      <c r="K40" s="15" t="n"/>
       <c r="L40" s="29" t="n"/>
       <c r="M40" s="22" t="n"/>
       <c r="N40" s="30" t="n"/>
@@ -2786,15 +2703,15 @@
     <row r="41" ht="114" customHeight="1">
       <c r="A41" s="31" t="n"/>
       <c r="B41" s="22" t="n"/>
-      <c r="C41" s="7" t="n"/>
+      <c r="C41" s="14" t="n"/>
       <c r="D41" s="23" t="n"/>
       <c r="E41" s="22" t="n"/>
       <c r="F41" s="23" t="n"/>
       <c r="G41" s="22" t="n"/>
-      <c r="H41" s="8" t="n"/>
-      <c r="I41" s="9" t="n"/>
-      <c r="J41" s="9" t="n"/>
-      <c r="K41" s="8" t="n"/>
+      <c r="H41" s="15" t="n"/>
+      <c r="I41" s="16" t="n"/>
+      <c r="J41" s="16" t="n"/>
+      <c r="K41" s="15" t="n"/>
       <c r="L41" s="29" t="n"/>
       <c r="M41" s="22" t="n"/>
       <c r="N41" s="30" t="n"/>
@@ -2810,15 +2727,15 @@
     <row r="42" ht="114" customHeight="1">
       <c r="A42" s="31" t="n"/>
       <c r="B42" s="22" t="n"/>
-      <c r="C42" s="7" t="n"/>
+      <c r="C42" s="14" t="n"/>
       <c r="D42" s="23" t="n"/>
       <c r="E42" s="22" t="n"/>
       <c r="F42" s="23" t="n"/>
       <c r="G42" s="22" t="n"/>
-      <c r="H42" s="8" t="n"/>
-      <c r="I42" s="9" t="n"/>
-      <c r="J42" s="9" t="n"/>
-      <c r="K42" s="8" t="n"/>
+      <c r="H42" s="15" t="n"/>
+      <c r="I42" s="16" t="n"/>
+      <c r="J42" s="16" t="n"/>
+      <c r="K42" s="15" t="n"/>
       <c r="L42" s="29" t="n"/>
       <c r="M42" s="22" t="n"/>
       <c r="N42" s="30" t="n"/>
@@ -2834,15 +2751,15 @@
     <row r="43" ht="114" customHeight="1">
       <c r="A43" s="31" t="n"/>
       <c r="B43" s="22" t="n"/>
-      <c r="C43" s="7" t="n"/>
+      <c r="C43" s="14" t="n"/>
       <c r="D43" s="23" t="n"/>
       <c r="E43" s="22" t="n"/>
       <c r="F43" s="23" t="n"/>
       <c r="G43" s="22" t="n"/>
-      <c r="H43" s="8" t="n"/>
-      <c r="I43" s="9" t="n"/>
-      <c r="J43" s="9" t="n"/>
-      <c r="K43" s="8" t="n"/>
+      <c r="H43" s="15" t="n"/>
+      <c r="I43" s="16" t="n"/>
+      <c r="J43" s="16" t="n"/>
+      <c r="K43" s="15" t="n"/>
       <c r="L43" s="29" t="n"/>
       <c r="M43" s="22" t="n"/>
       <c r="N43" s="30" t="n"/>
@@ -2858,15 +2775,15 @@
     <row r="44" ht="114" customHeight="1">
       <c r="A44" s="31" t="n"/>
       <c r="B44" s="22" t="n"/>
-      <c r="C44" s="7" t="n"/>
+      <c r="C44" s="14" t="n"/>
       <c r="D44" s="23" t="n"/>
       <c r="E44" s="22" t="n"/>
       <c r="F44" s="23" t="n"/>
       <c r="G44" s="22" t="n"/>
-      <c r="H44" s="8" t="n"/>
-      <c r="I44" s="9" t="n"/>
-      <c r="J44" s="9" t="n"/>
-      <c r="K44" s="8" t="n"/>
+      <c r="H44" s="15" t="n"/>
+      <c r="I44" s="16" t="n"/>
+      <c r="J44" s="16" t="n"/>
+      <c r="K44" s="15" t="n"/>
       <c r="L44" s="29" t="n"/>
       <c r="M44" s="22" t="n"/>
       <c r="N44" s="30" t="n"/>
@@ -2882,15 +2799,15 @@
     <row r="45" ht="114" customHeight="1">
       <c r="A45" s="31" t="n"/>
       <c r="B45" s="22" t="n"/>
-      <c r="C45" s="7" t="n"/>
+      <c r="C45" s="14" t="n"/>
       <c r="D45" s="23" t="n"/>
       <c r="E45" s="22" t="n"/>
       <c r="F45" s="23" t="n"/>
       <c r="G45" s="22" t="n"/>
-      <c r="H45" s="8" t="n"/>
-      <c r="I45" s="9" t="n"/>
-      <c r="J45" s="9" t="n"/>
-      <c r="K45" s="8" t="n"/>
+      <c r="H45" s="15" t="n"/>
+      <c r="I45" s="16" t="n"/>
+      <c r="J45" s="16" t="n"/>
+      <c r="K45" s="15" t="n"/>
       <c r="L45" s="29" t="n"/>
       <c r="M45" s="22" t="n"/>
       <c r="N45" s="30" t="n"/>
@@ -2965,12 +2882,12 @@
           <t xml:space="preserve">ARR </t>
         </is>
       </c>
-      <c r="J47" s="6" t="inlineStr">
+      <c r="J47" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">DEP </t>
         </is>
       </c>
-      <c r="K47" s="6" t="inlineStr">
+      <c r="K47" s="13" t="inlineStr">
         <is>
           <t>Flight</t>
         </is>
@@ -3002,15 +2919,15 @@
     <row r="48" ht="114" customHeight="1">
       <c r="A48" s="31" t="n"/>
       <c r="B48" s="22" t="n"/>
-      <c r="C48" s="7" t="n"/>
+      <c r="C48" s="14" t="n"/>
       <c r="D48" s="23" t="n"/>
       <c r="E48" s="22" t="n"/>
       <c r="F48" s="23" t="n"/>
       <c r="G48" s="22" t="n"/>
-      <c r="H48" s="8" t="n"/>
-      <c r="I48" s="9" t="n"/>
-      <c r="J48" s="9" t="n"/>
-      <c r="K48" s="8" t="n"/>
+      <c r="H48" s="15" t="n"/>
+      <c r="I48" s="16" t="n"/>
+      <c r="J48" s="16" t="n"/>
+      <c r="K48" s="15" t="n"/>
       <c r="L48" s="29" t="n"/>
       <c r="M48" s="22" t="n"/>
       <c r="N48" s="30" t="n"/>
@@ -3231,7 +3148,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="117" customFormat="1" customHeight="1" s="10">
+    <row r="56" ht="117" customFormat="1" customHeight="1" s="18">
       <c r="A56" s="59" t="n"/>
       <c r="B56" s="25" t="n"/>
       <c r="C56" s="25" t="n"/>
@@ -3255,7 +3172,7 @@
       <c r="U56" s="22" t="n"/>
       <c r="V56" s="59" t="n"/>
     </row>
-    <row r="57" ht="117" customFormat="1" customHeight="1" s="10">
+    <row r="57" ht="117" customFormat="1" customHeight="1" s="18">
       <c r="A57" s="59" t="n"/>
       <c r="B57" s="25" t="n"/>
       <c r="C57" s="25" t="n"/>
@@ -3279,7 +3196,7 @@
       <c r="U57" s="22" t="n"/>
       <c r="V57" s="59" t="n"/>
     </row>
-    <row r="58" ht="103.5" customFormat="1" customHeight="1" s="10">
+    <row r="58" ht="103.5" customFormat="1" customHeight="1" s="18">
       <c r="A58" s="27" t="inlineStr">
         <is>
           <t>GROUP</t>
@@ -3307,7 +3224,7 @@
       <c r="U58" s="25" t="n"/>
       <c r="V58" s="22" t="n"/>
     </row>
-    <row r="59" ht="87.75" customFormat="1" customHeight="1" s="10">
+    <row r="59" ht="87.75" customFormat="1" customHeight="1" s="18">
       <c r="A59" s="28" t="inlineStr">
         <is>
           <t>Group Name</t>
@@ -3351,7 +3268,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="114" customFormat="1" customHeight="1" s="10">
+    <row r="60" ht="114" customFormat="1" customHeight="1" s="18">
       <c r="A60" s="24" t="n"/>
       <c r="B60" s="25" t="n"/>
       <c r="C60" s="25" t="n"/>
@@ -3375,7 +3292,7 @@
       <c r="U60" s="22" t="n"/>
       <c r="V60" s="24" t="n"/>
     </row>
-    <row r="61" ht="93.75" customFormat="1" customHeight="1" s="10">
+    <row r="61" ht="93.75" customFormat="1" customHeight="1" s="18">
       <c r="A61" s="78" t="inlineStr">
         <is>
           <t>Outlet</t>
@@ -3421,8 +3338,8 @@
           <t>Elements</t>
         </is>
       </c>
-      <c r="B62" s="50" t="n"/>
-      <c r="C62" s="50" t="n"/>
+      <c r="B62" s="51" t="n"/>
+      <c r="C62" s="51" t="n"/>
       <c r="D62" s="72" t="inlineStr">
         <is>
           <t>Opening from 06.30 - 10.30 for breakfast</t>
@@ -3434,31 +3351,31 @@
       <c r="H62" s="25" t="n"/>
       <c r="I62" s="25" t="n"/>
       <c r="J62" s="22" t="n"/>
-      <c r="K62" s="49" t="inlineStr">
+      <c r="K62" s="50" t="inlineStr">
         <is>
           <t xml:space="preserve">Burger N' Wing </t>
         </is>
       </c>
-      <c r="L62" s="50" t="n"/>
-      <c r="M62" s="50" t="n"/>
-      <c r="N62" s="50" t="n"/>
-      <c r="O62" s="50" t="n"/>
+      <c r="L62" s="51" t="n"/>
+      <c r="M62" s="51" t="n"/>
+      <c r="N62" s="51" t="n"/>
+      <c r="O62" s="51" t="n"/>
       <c r="P62" s="64" t="inlineStr">
         <is>
           <t>Opening from 12.00 - 20.00</t>
         </is>
       </c>
-      <c r="Q62" s="50" t="n"/>
-      <c r="R62" s="50" t="n"/>
-      <c r="S62" s="50" t="n"/>
-      <c r="T62" s="50" t="n"/>
-      <c r="U62" s="50" t="n"/>
+      <c r="Q62" s="51" t="n"/>
+      <c r="R62" s="51" t="n"/>
+      <c r="S62" s="51" t="n"/>
+      <c r="T62" s="51" t="n"/>
+      <c r="U62" s="51" t="n"/>
       <c r="V62" s="38" t="n"/>
     </row>
     <row r="63" ht="114" customHeight="1">
       <c r="A63" s="39" t="n"/>
-      <c r="B63" s="52" t="n"/>
-      <c r="C63" s="52" t="n"/>
+      <c r="B63" s="53" t="n"/>
+      <c r="C63" s="53" t="n"/>
       <c r="D63" s="66" t="inlineStr">
         <is>
           <t>Opening from 18.00 - 22.00 for dinner (only Friday to Sunday)</t>
@@ -3504,12 +3421,12 @@
           <t>Opening from 07.00 - 19.00</t>
         </is>
       </c>
-      <c r="E64" s="52" t="n"/>
-      <c r="F64" s="52" t="n"/>
-      <c r="G64" s="52" t="n"/>
-      <c r="H64" s="52" t="n"/>
-      <c r="I64" s="52" t="n"/>
-      <c r="J64" s="52" t="n"/>
+      <c r="E64" s="53" t="n"/>
+      <c r="F64" s="53" t="n"/>
+      <c r="G64" s="53" t="n"/>
+      <c r="H64" s="53" t="n"/>
+      <c r="I64" s="53" t="n"/>
+      <c r="J64" s="53" t="n"/>
       <c r="K64" s="57" t="inlineStr">
         <is>
           <t>Mizu Bar</t>
@@ -3862,8 +3779,8 @@
     <mergeCell ref="R55:U55"/>
     <mergeCell ref="N24:O24"/>
     <mergeCell ref="G12:G13"/>
+    <mergeCell ref="L55:O55"/>
     <mergeCell ref="A28:B28"/>
-    <mergeCell ref="L55:O55"/>
     <mergeCell ref="G70:O70"/>
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="N26:O26"/>
@@ -3874,14 +3791,14 @@
     <mergeCell ref="I7:I8"/>
     <mergeCell ref="L42:M42"/>
     <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F45:G45"/>
     <mergeCell ref="N42:O42"/>
-    <mergeCell ref="F45:G45"/>
     <mergeCell ref="F42:G42"/>
     <mergeCell ref="D12:D13"/>
     <mergeCell ref="F17:G17"/>
     <mergeCell ref="D47:E47"/>
+    <mergeCell ref="F47:G47"/>
     <mergeCell ref="N44:O44"/>
-    <mergeCell ref="F47:G47"/>
     <mergeCell ref="P27:V27"/>
     <mergeCell ref="F48:G48"/>
     <mergeCell ref="M4:N4"/>
@@ -3899,8 +3816,8 @@
     <mergeCell ref="P38:V38"/>
     <mergeCell ref="L9:L10"/>
     <mergeCell ref="P40:V40"/>
+    <mergeCell ref="D28:E28"/>
     <mergeCell ref="L25:M25"/>
-    <mergeCell ref="D28:E28"/>
     <mergeCell ref="K61:O61"/>
     <mergeCell ref="H9:H11"/>
     <mergeCell ref="J9:J11"/>
@@ -3926,9 +3843,9 @@
     <mergeCell ref="P48:V48"/>
     <mergeCell ref="F29:G29"/>
     <mergeCell ref="L12:L13"/>
-    <mergeCell ref="L28:M28"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="A50:O50"/>
+    <mergeCell ref="L28:M28"/>
     <mergeCell ref="K64:O64"/>
     <mergeCell ref="L3:V3"/>
     <mergeCell ref="D44:E44"/>
@@ -3938,22 +3855,22 @@
     <mergeCell ref="P34:V34"/>
     <mergeCell ref="P36:V36"/>
     <mergeCell ref="A56:D56"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="L21:M21"/>
     <mergeCell ref="O11:P11"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="D24:E24"/>
     <mergeCell ref="Q11:R11"/>
     <mergeCell ref="A70:F70"/>
     <mergeCell ref="D26:E26"/>
     <mergeCell ref="S4:T4"/>
+    <mergeCell ref="U4:V4"/>
     <mergeCell ref="D4:G4"/>
-    <mergeCell ref="U4:V4"/>
     <mergeCell ref="A66:C66"/>
+    <mergeCell ref="D19:E19"/>
     <mergeCell ref="L16:M16"/>
-    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="A62:C63"/>
+    <mergeCell ref="A45:B45"/>
     <mergeCell ref="N16:O16"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A62:C63"/>
     <mergeCell ref="B9:C10"/>
     <mergeCell ref="P62:V62"/>
     <mergeCell ref="F20:G20"/>
@@ -3971,10 +3888,10 @@
     <mergeCell ref="V1:V2"/>
     <mergeCell ref="A71:F71"/>
     <mergeCell ref="E11:G11"/>
+    <mergeCell ref="E56:K56"/>
     <mergeCell ref="A12:A13"/>
-    <mergeCell ref="E56:K56"/>
+    <mergeCell ref="D27:E27"/>
     <mergeCell ref="L24:M24"/>
-    <mergeCell ref="D27:E27"/>
     <mergeCell ref="L18:M18"/>
     <mergeCell ref="N18:O18"/>
     <mergeCell ref="K9:K11"/>
@@ -3983,19 +3900,19 @@
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="S12:T13"/>
     <mergeCell ref="A32:B32"/>
+    <mergeCell ref="F22:G22"/>
     <mergeCell ref="N19:O19"/>
-    <mergeCell ref="F22:G22"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="P5:P6"/>
     <mergeCell ref="B12:C13"/>
-    <mergeCell ref="H5:H6"/>
     <mergeCell ref="R5:R6"/>
     <mergeCell ref="P65:V65"/>
+    <mergeCell ref="H5:H6"/>
     <mergeCell ref="J5:J6"/>
+    <mergeCell ref="D40:E40"/>
     <mergeCell ref="L37:M37"/>
-    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
     <mergeCell ref="N37:O37"/>
-    <mergeCell ref="F40:G40"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="D41:E41"/>
     <mergeCell ref="A18:B18"/>
@@ -4013,29 +3930,29 @@
     <mergeCell ref="D61:J61"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="G71:O71"/>
+    <mergeCell ref="A44:B44"/>
     <mergeCell ref="L27:M27"/>
-    <mergeCell ref="A44:B44"/>
     <mergeCell ref="N27:O27"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="M60:U60"/>
     <mergeCell ref="D62:J62"/>
     <mergeCell ref="N20:O20"/>
+    <mergeCell ref="L56:O56"/>
     <mergeCell ref="F25:G25"/>
-    <mergeCell ref="L56:O56"/>
     <mergeCell ref="D64:J64"/>
     <mergeCell ref="D36:E36"/>
     <mergeCell ref="P15:V15"/>
+    <mergeCell ref="P71:V71"/>
     <mergeCell ref="N22:O22"/>
-    <mergeCell ref="P71:V71"/>
+    <mergeCell ref="D48:E48"/>
     <mergeCell ref="L45:M45"/>
-    <mergeCell ref="D48:E48"/>
     <mergeCell ref="L38:M38"/>
     <mergeCell ref="N38:O38"/>
     <mergeCell ref="A42:B42"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="L40:M40"/>
+    <mergeCell ref="F43:G43"/>
     <mergeCell ref="N40:O40"/>
-    <mergeCell ref="F43:G43"/>
     <mergeCell ref="N15:O15"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="D1:G2"/>
@@ -4045,8 +3962,8 @@
     <mergeCell ref="A72:V72"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B5:C6"/>
+    <mergeCell ref="A37:B37"/>
     <mergeCell ref="F33:G33"/>
-    <mergeCell ref="A37:B37"/>
     <mergeCell ref="A59:D59"/>
     <mergeCell ref="A30:V30"/>
     <mergeCell ref="L57:O57"/>
@@ -4054,9 +3971,9 @@
     <mergeCell ref="D65:J65"/>
     <mergeCell ref="H12:H13"/>
     <mergeCell ref="J12:J13"/>
-    <mergeCell ref="N28:O28"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="A67:C67"/>
+    <mergeCell ref="N28:O28"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="D39:E39"/>
     <mergeCell ref="A54:V54"/>
@@ -4068,13 +3985,13 @@
     <mergeCell ref="S9:T10"/>
     <mergeCell ref="N41:O41"/>
     <mergeCell ref="F21:G21"/>
+    <mergeCell ref="P56:Q56"/>
     <mergeCell ref="L43:M43"/>
-    <mergeCell ref="P56:Q56"/>
+    <mergeCell ref="N43:O43"/>
     <mergeCell ref="M11:N11"/>
-    <mergeCell ref="N43:O43"/>
     <mergeCell ref="P29:V29"/>
+    <mergeCell ref="D17:E17"/>
     <mergeCell ref="O4:P4"/>
-    <mergeCell ref="D17:E17"/>
     <mergeCell ref="Q4:R4"/>
     <mergeCell ref="P44:V44"/>
     <mergeCell ref="P31:V31"/>
@@ -4090,8 +4007,8 @@
     <mergeCell ref="K59:L59"/>
     <mergeCell ref="Q12:R13"/>
     <mergeCell ref="K7:K8"/>
+    <mergeCell ref="P57:Q57"/>
     <mergeCell ref="A3:C4"/>
-    <mergeCell ref="P57:Q57"/>
     <mergeCell ref="F37:G37"/>
     <mergeCell ref="L1:N2"/>
     <mergeCell ref="A1:C1"/>
@@ -4099,13 +4016,13 @@
     <mergeCell ref="P70:V70"/>
     <mergeCell ref="A65:C65"/>
     <mergeCell ref="P32:V32"/>
+    <mergeCell ref="D20:E20"/>
     <mergeCell ref="L17:M17"/>
-    <mergeCell ref="D20:E20"/>
     <mergeCell ref="P47:V47"/>
     <mergeCell ref="A14:V14"/>
     <mergeCell ref="A7:A8"/>
+    <mergeCell ref="D22:E22"/>
     <mergeCell ref="L19:M19"/>
-    <mergeCell ref="D22:E22"/>
     <mergeCell ref="E59:J59"/>
     <mergeCell ref="N5:N6"/>
     <mergeCell ref="F15:G15"/>
@@ -4118,16 +4035,16 @@
     <mergeCell ref="B7:C8"/>
     <mergeCell ref="T7:T8"/>
     <mergeCell ref="V7:V8"/>
+    <mergeCell ref="P52:V52"/>
     <mergeCell ref="E9:G10"/>
-    <mergeCell ref="P52:V52"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="K66:O66"/>
     <mergeCell ref="D35:E35"/>
     <mergeCell ref="K68:O68"/>
     <mergeCell ref="D34:E34"/>
+    <mergeCell ref="R56:U56"/>
     <mergeCell ref="F34:G34"/>
-    <mergeCell ref="R56:U56"/>
     <mergeCell ref="N25:O25"/>
     <mergeCell ref="A69:F69"/>
     <mergeCell ref="D9:D10"/>
@@ -4144,8 +4061,8 @@
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="K60:L60"/>
     <mergeCell ref="L33:M33"/>
+    <mergeCell ref="F36:G36"/>
     <mergeCell ref="N33:O33"/>
-    <mergeCell ref="F36:G36"/>
     <mergeCell ref="A53:O53"/>
     <mergeCell ref="R57:U57"/>
     <mergeCell ref="L35:M35"/>
@@ -4156,22 +4073,22 @@
     <mergeCell ref="P23:V23"/>
     <mergeCell ref="A57:D57"/>
     <mergeCell ref="T5:T6"/>
+    <mergeCell ref="P16:V16"/>
     <mergeCell ref="V5:V6"/>
-    <mergeCell ref="P16:V16"/>
     <mergeCell ref="S1:U2"/>
+    <mergeCell ref="P43:V43"/>
+    <mergeCell ref="P18:V18"/>
     <mergeCell ref="F12:F13"/>
-    <mergeCell ref="P18:V18"/>
-    <mergeCell ref="P43:V43"/>
     <mergeCell ref="G69:O69"/>
+    <mergeCell ref="F24:G24"/>
     <mergeCell ref="N21:O21"/>
-    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="A25:B25"/>
     <mergeCell ref="S11:T11"/>
-    <mergeCell ref="A25:B25"/>
     <mergeCell ref="U11:V11"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="H7:H8"/>
+    <mergeCell ref="F32:G32"/>
     <mergeCell ref="L23:M23"/>
-    <mergeCell ref="F32:G32"/>
     <mergeCell ref="J7:J8"/>
     <mergeCell ref="N23:O23"/>
     <mergeCell ref="F26:G26"/>
@@ -4185,15 +4102,123 @@
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="M59:U59"/>
     <mergeCell ref="L34:M34"/>
+    <mergeCell ref="D42:E42"/>
     <mergeCell ref="N34:O34"/>
-    <mergeCell ref="D42:E42"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="L36:M36"/>
     <mergeCell ref="N36:O36"/>
     <mergeCell ref="F44:G44"/>
   </mergeCells>
   <dataValidations count="30">
-    <dataValidation sqref="CX64465" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=65552.82_x000d__x000a_" type="textLength" errorStyle="information">
+    <dataValidation sqref="D64491:F64491 CS64464" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=9175.87085811385_x000d__x000a_" type="textLength" errorStyle="information">
+      <formula1>0</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation sqref="D64503:F64503 CS64476" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=1971.66180968562_x000d__x000a_" type="textLength" errorStyle="information">
+      <formula1>0</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation sqref="D64499:F64499 CS64472" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=654.21_x000d__x000a_" type="textLength" errorStyle="information">
+      <formula1>0</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation sqref="D64508:F64508 CS64481" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=3831.77570093458_x000d__x000a_" type="textLength" errorStyle="information">
+      <formula1>0</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation sqref="D64504:F64504 CS64477" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=969_x000d__x000a_" type="textLength" errorStyle="information">
+      <formula1>0</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation sqref="D64501:F64501 CS64474" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=29778.32_x000d__x000a_" type="textLength" errorStyle="information">
+      <formula1>0</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation sqref="D64496:F64496 CS64469" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=2730_x000d__x000a_" type="textLength" errorStyle="information">
+      <formula1>0</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation sqref="D64493:F64493 CS64466" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=140.186915887849_x000d__x000a_" type="textLength" errorStyle="information">
+      <formula1>0</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation sqref="D64497:F64497 CS64470" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=3495_x000d__x000a_" type="textLength" errorStyle="information">
+      <formula1>0</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation sqref="D64492:F64492 CS64465" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=76.46_x000d__x000a_" type="textLength" errorStyle="information">
+      <formula1>0</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation sqref="D64490:F64490 D64494:F64495 D64498:F64498 D64500:F64500 D64505:F64507 P64490:Q64490 P64494:Q64495 P64498:Q64498 P64500:Q64500 P64503:Q64503 P64505:Q64506 CS64471" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:2=0_x000d__x000a_" type="textLength" errorStyle="information">
+      <formula1>0</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation sqref="P64507:Q64507 DA64480" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=3124.44_x000d__x000a_" type="textLength" errorStyle="information">
+      <formula1>0</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation sqref="P64499:Q64499 DA64472" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=2947.48_x000d__x000a_" type="textLength" errorStyle="information">
+      <formula1>0</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation sqref="P64501:Q64501 DA64474" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=337579.47_x000d__x000a_" type="textLength" errorStyle="information">
+      <formula1>0</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation sqref="P64508:Q64508 DA64481" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=3041.07_x000d__x000a_" type="textLength" errorStyle="information">
+      <formula1>0</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation sqref="P64504:Q64504 DA64477" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=10387_x000d__x000a_" type="textLength" errorStyle="information">
+      <formula1>0</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation sqref="P64497:Q64497 DA64470" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=7600_x000d__x000a_" type="textLength" errorStyle="information">
+      <formula1>0</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation sqref="P64496:Q64496 DA64469" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=33859.1606542056_x000d__x000a_" type="textLength" errorStyle="information">
+      <formula1>0</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation sqref="P64492:Q64492 DA64465" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=108462.39_x000d__x000a_" type="textLength" errorStyle="information">
+      <formula1>0</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation sqref="P64493:Q64493 DA64466" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=1064.01962616822_x000d__x000a_" type="textLength" errorStyle="information">
+      <formula1>0</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation sqref="CX64476" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=16849.7162616821_x000d__x000a_" type="textLength" errorStyle="information">
+      <formula1>0</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation sqref="CX64472" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=116642.038971963_x000d__x000a_" type="textLength" errorStyle="information">
+      <formula1>0</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation sqref="CX64474" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=379048.61_x000d__x000a_" type="textLength" errorStyle="information">
+      <formula1>0</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation sqref="CX64466" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=1031.37196261682_x000d__x000a_" type="textLength" errorStyle="information">
+      <formula1>0</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation sqref="CX64464" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=57417.1622769754_x000d__x000a_" type="textLength" errorStyle="information">
+      <formula1>0</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation sqref="CX64470" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=78897.0664655905_x000d__x000a_" type="textLength" errorStyle="information">
+      <formula1>0</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation sqref="CX64481" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=812367.264112149_x000d__x000a_" type="textLength" errorStyle="information">
+      <formula1>0</formula1>
+      <formula2>300</formula2>
+    </dataValidation>
+    <dataValidation sqref="CX64477" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=7558.54_x000d__x000a_" type="textLength" errorStyle="information">
       <formula1>0</formula1>
       <formula2>300</formula2>
     </dataValidation>
@@ -4201,115 +4226,7 @@
       <formula1>0</formula1>
       <formula2>300</formula2>
     </dataValidation>
-    <dataValidation sqref="CX64477" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=7558.54_x000d__x000a_" type="textLength" errorStyle="information">
-      <formula1>0</formula1>
-      <formula2>300</formula2>
-    </dataValidation>
-    <dataValidation sqref="CX64481" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=812367.264112149_x000d__x000a_" type="textLength" errorStyle="information">
-      <formula1>0</formula1>
-      <formula2>300</formula2>
-    </dataValidation>
-    <dataValidation sqref="CX64470" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=78897.0664655905_x000d__x000a_" type="textLength" errorStyle="information">
-      <formula1>0</formula1>
-      <formula2>300</formula2>
-    </dataValidation>
-    <dataValidation sqref="CX64464" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=57417.1622769754_x000d__x000a_" type="textLength" errorStyle="information">
-      <formula1>0</formula1>
-      <formula2>300</formula2>
-    </dataValidation>
-    <dataValidation sqref="CX64466" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=1031.37196261682_x000d__x000a_" type="textLength" errorStyle="information">
-      <formula1>0</formula1>
-      <formula2>300</formula2>
-    </dataValidation>
-    <dataValidation sqref="CX64474" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=379048.61_x000d__x000a_" type="textLength" errorStyle="information">
-      <formula1>0</formula1>
-      <formula2>300</formula2>
-    </dataValidation>
-    <dataValidation sqref="CX64472" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=116642.038971963_x000d__x000a_" type="textLength" errorStyle="information">
-      <formula1>0</formula1>
-      <formula2>300</formula2>
-    </dataValidation>
-    <dataValidation sqref="CX64476" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=16849.7162616821_x000d__x000a_" type="textLength" errorStyle="information">
-      <formula1>0</formula1>
-      <formula2>300</formula2>
-    </dataValidation>
-    <dataValidation sqref="P64493:Q64493 DA64466" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=1064.01962616822_x000d__x000a_" type="textLength" errorStyle="information">
-      <formula1>0</formula1>
-      <formula2>300</formula2>
-    </dataValidation>
-    <dataValidation sqref="P64492:Q64492 DA64465" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=108462.39_x000d__x000a_" type="textLength" errorStyle="information">
-      <formula1>0</formula1>
-      <formula2>300</formula2>
-    </dataValidation>
-    <dataValidation sqref="P64496:Q64496 DA64469" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=33859.1606542056_x000d__x000a_" type="textLength" errorStyle="information">
-      <formula1>0</formula1>
-      <formula2>300</formula2>
-    </dataValidation>
-    <dataValidation sqref="P64497:Q64497 DA64470" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=7600_x000d__x000a_" type="textLength" errorStyle="information">
-      <formula1>0</formula1>
-      <formula2>300</formula2>
-    </dataValidation>
-    <dataValidation sqref="P64504:Q64504 DA64477" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=10387_x000d__x000a_" type="textLength" errorStyle="information">
-      <formula1>0</formula1>
-      <formula2>300</formula2>
-    </dataValidation>
-    <dataValidation sqref="P64508:Q64508 DA64481" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=3041.07_x000d__x000a_" type="textLength" errorStyle="information">
-      <formula1>0</formula1>
-      <formula2>300</formula2>
-    </dataValidation>
-    <dataValidation sqref="P64501:Q64501 DA64474" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=337579.47_x000d__x000a_" type="textLength" errorStyle="information">
-      <formula1>0</formula1>
-      <formula2>300</formula2>
-    </dataValidation>
-    <dataValidation sqref="P64499:Q64499 DA64472" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=2947.48_x000d__x000a_" type="textLength" errorStyle="information">
-      <formula1>0</formula1>
-      <formula2>300</formula2>
-    </dataValidation>
-    <dataValidation sqref="P64507:Q64507 DA64480" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=3124.44_x000d__x000a_" type="textLength" errorStyle="information">
-      <formula1>0</formula1>
-      <formula2>300</formula2>
-    </dataValidation>
-    <dataValidation sqref="D64490:F64490 D64494:F64495 D64498:F64498 D64500:F64500 D64505:F64507 P64490:Q64490 P64494:Q64495 P64498:Q64498 P64500:Q64500 P64503:Q64503 P64505:Q64506 CS64471" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:2=0_x000d__x000a_" type="textLength" errorStyle="information">
-      <formula1>0</formula1>
-      <formula2>300</formula2>
-    </dataValidation>
-    <dataValidation sqref="D64492:F64492 CS64465" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=76.46_x000d__x000a_" type="textLength" errorStyle="information">
-      <formula1>0</formula1>
-      <formula2>300</formula2>
-    </dataValidation>
-    <dataValidation sqref="D64497:F64497 CS64470" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=3495_x000d__x000a_" type="textLength" errorStyle="information">
-      <formula1>0</formula1>
-      <formula2>300</formula2>
-    </dataValidation>
-    <dataValidation sqref="D64493:F64493 CS64466" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=140.186915887849_x000d__x000a_" type="textLength" errorStyle="information">
-      <formula1>0</formula1>
-      <formula2>300</formula2>
-    </dataValidation>
-    <dataValidation sqref="D64496:F64496 CS64469" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=2730_x000d__x000a_" type="textLength" errorStyle="information">
-      <formula1>0</formula1>
-      <formula2>300</formula2>
-    </dataValidation>
-    <dataValidation sqref="D64501:F64501 CS64474" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=29778.32_x000d__x000a_" type="textLength" errorStyle="information">
-      <formula1>0</formula1>
-      <formula2>300</formula2>
-    </dataValidation>
-    <dataValidation sqref="D64504:F64504 CS64477" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=969_x000d__x000a_" type="textLength" errorStyle="information">
-      <formula1>0</formula1>
-      <formula2>300</formula2>
-    </dataValidation>
-    <dataValidation sqref="D64508:F64508 CS64481" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=3831.77570093458_x000d__x000a_" type="textLength" errorStyle="information">
-      <formula1>0</formula1>
-      <formula2>300</formula2>
-    </dataValidation>
-    <dataValidation sqref="D64499:F64499 CS64472" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=654.21_x000d__x000a_" type="textLength" errorStyle="information">
-      <formula1>0</formula1>
-      <formula2>300</formula2>
-    </dataValidation>
-    <dataValidation sqref="D64503:F64503 CS64476" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=1971.66180968562_x000d__x000a_" type="textLength" errorStyle="information">
-      <formula1>0</formula1>
-      <formula2>300</formula2>
-    </dataValidation>
-    <dataValidation sqref="D64491:F64491 CS64464" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=9175.87085811385_x000d__x000a_" type="textLength" errorStyle="information">
+    <dataValidation sqref="CX64465" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="XLBVal:5=65552.82_x000d__x000a_" type="textLength" errorStyle="information">
       <formula1>0</formula1>
       <formula2>300</formula2>
     </dataValidation>

--- a/Briefing/Briefing.xlsx
+++ b/Briefing/Briefing.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="570" yWindow="270" windowWidth="16170" windowHeight="12105" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="555" windowWidth="16170" windowHeight="12105" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Ori Format" sheetId="1" state="visible" r:id="rId1"/>
@@ -1195,8 +1195,8 @@
     <col width="28.7109375" customWidth="1" style="1" min="20" max="20"/>
     <col width="29.28515625" customWidth="1" style="1" min="21" max="21"/>
     <col width="110.7109375" customWidth="1" style="1" min="22" max="22"/>
-    <col width="10.42578125" customWidth="1" style="1" min="23" max="25"/>
-    <col width="10.42578125" customWidth="1" style="1" min="26" max="16384"/>
+    <col width="10.42578125" customWidth="1" style="1" min="23" max="26"/>
+    <col width="10.42578125" customWidth="1" style="1" min="27" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="336" customHeight="1">
@@ -1346,7 +1346,7 @@
       <c r="C4" s="40" t="n"/>
       <c r="D4" s="62" t="inlineStr">
         <is>
-          <t>24-Jul</t>
+          <t>25-Jul</t>
         </is>
       </c>
       <c r="E4" s="25" t="n"/>
@@ -1554,10 +1554,8 @@
           <t>HOU</t>
         </is>
       </c>
-      <c r="B7" s="30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="B7" s="30" t="n">
+        <v>2</v>
       </c>
       <c r="C7" s="38" t="n"/>
       <c r="D7" s="78" t="inlineStr">
@@ -1715,10 +1713,8 @@
           <t>RM Occ.</t>
         </is>
       </c>
-      <c r="E9" s="30" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
+      <c r="E9" s="30" t="n">
+        <v>221</v>
       </c>
       <c r="F9" s="51" t="n"/>
       <c r="G9" s="38" t="n"/>
@@ -1742,34 +1738,24 @@
           <t>RM Occ.</t>
         </is>
       </c>
-      <c r="M9" s="37" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
+      <c r="M9" s="37" t="n">
+        <v>281</v>
       </c>
       <c r="N9" s="38" t="n"/>
-      <c r="O9" s="37" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
+      <c r="O9" s="37" t="n">
+        <v>235</v>
       </c>
       <c r="P9" s="38" t="n"/>
-      <c r="Q9" s="37" t="inlineStr">
-        <is>
-          <t>295</t>
-        </is>
+      <c r="Q9" s="37" t="n">
+        <v>295</v>
       </c>
       <c r="R9" s="38" t="n"/>
-      <c r="S9" s="37" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
+      <c r="S9" s="37" t="n">
+        <v>220</v>
       </c>
       <c r="T9" s="38" t="n"/>
-      <c r="U9" s="37" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
+      <c r="U9" s="37" t="n">
+        <v>228</v>
       </c>
       <c r="V9" s="38" t="n"/>
     </row>
@@ -1839,7 +1825,7 @@
       </c>
       <c r="R11" s="22" t="n"/>
       <c r="S11" s="88" t="n">
-        <v>67.07692307692308</v>
+        <v>66.9753086419753</v>
       </c>
       <c r="T11" s="22" t="n"/>
       <c r="U11" s="88" t="n">

--- a/Briefing/Briefing.xlsx
+++ b/Briefing/Briefing.xlsx
@@ -17,11 +17,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm;@"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="#.##&quot;%&quot;"/>
-    <numFmt numFmtId="167" formatCode="#,###.##"/>
+    <numFmt numFmtId="166" formatCode="##.##"/>
+    <numFmt numFmtId="167" formatCode="#.##&quot;%&quot;"/>
+    <numFmt numFmtId="168" formatCode="#,###.##"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -171,7 +172,7 @@
       <sz val="34"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -229,6 +230,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF009999"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -416,7 +423,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
@@ -480,7 +487,7 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -496,7 +503,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="13" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
+    <xf numFmtId="166" fontId="13" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -536,11 +543,17 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="15" fontId="4" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="13" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -570,10 +583,7 @@
     <xf numFmtId="0" fontId="15" fillId="10" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -588,7 +598,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="167" fontId="13" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="12" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -597,7 +607,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
+    <xf numFmtId="167" fontId="10" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -609,13 +619,16 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
+    <xf numFmtId="168" fontId="10" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
@@ -645,20 +658,26 @@
     <xf numFmtId="15" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
+    <xf numFmtId="168" fontId="10" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="167" fontId="13" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
+    <xf numFmtId="167" fontId="10" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
@@ -1192,15 +1211,15 @@
     <col width="28.7109375" customWidth="1" style="1" min="20" max="20"/>
     <col width="29.28515625" customWidth="1" style="1" min="21" max="21"/>
     <col width="110.7109375" customWidth="1" style="1" min="22" max="22"/>
-    <col width="10.42578125" customWidth="1" style="1" min="23" max="47"/>
-    <col width="10.42578125" customWidth="1" style="1" min="48" max="16384"/>
+    <col width="10.42578125" customWidth="1" style="1" min="23" max="50"/>
+    <col width="10.42578125" customWidth="1" style="1" min="51" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="336" customHeight="1">
-      <c r="A1" s="82" t="n"/>
-      <c r="B1" s="54" t="n"/>
+      <c r="A1" s="84" t="n"/>
+      <c r="B1" s="56" t="n"/>
       <c r="C1" s="38" t="n"/>
-      <c r="D1" s="72" t="inlineStr">
+      <c r="D1" s="73" t="inlineStr">
         <is>
           <t xml:space="preserve">
 YTD GRI 
@@ -1208,10 +1227,10 @@
 by 31 Dec. 2026</t>
         </is>
       </c>
-      <c r="E1" s="54" t="n"/>
-      <c r="F1" s="54" t="n"/>
+      <c r="E1" s="56" t="n"/>
+      <c r="F1" s="56" t="n"/>
       <c r="G1" s="38" t="n"/>
-      <c r="H1" s="72" t="inlineStr">
+      <c r="H1" s="73" t="inlineStr">
         <is>
           <t xml:space="preserve">
 YTD NPS
@@ -1220,7 +1239,7 @@
         </is>
       </c>
       <c r="I1" s="38" t="n"/>
-      <c r="J1" s="72" t="inlineStr">
+      <c r="J1" s="73" t="inlineStr">
         <is>
           <t xml:space="preserve">
 MTD GRI
@@ -1230,7 +1249,7 @@
         </is>
       </c>
       <c r="K1" s="38" t="n"/>
-      <c r="L1" s="72" t="inlineStr">
+      <c r="L1" s="73" t="inlineStr">
         <is>
           <t xml:space="preserve">
 MTD NPS
@@ -1238,9 +1257,9 @@
 by 31 Dec. 2026</t>
         </is>
       </c>
-      <c r="M1" s="54" t="n"/>
+      <c r="M1" s="56" t="n"/>
       <c r="N1" s="38" t="n"/>
-      <c r="O1" s="53" t="inlineStr">
+      <c r="O1" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">
 Enrollment Done: -
@@ -1249,10 +1268,10 @@
 YTD = -</t>
         </is>
       </c>
-      <c r="P1" s="54" t="n"/>
-      <c r="Q1" s="54" t="n"/>
+      <c r="P1" s="56" t="n"/>
+      <c r="Q1" s="56" t="n"/>
       <c r="R1" s="38" t="n"/>
-      <c r="S1" s="53" t="inlineStr">
+      <c r="S1" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">
 Hotel in Khao Lak 
@@ -1261,9 +1280,9 @@
 Goal #1</t>
         </is>
       </c>
-      <c r="T1" s="54" t="n"/>
+      <c r="T1" s="56" t="n"/>
       <c r="U1" s="38" t="n"/>
-      <c r="V1" s="65" t="inlineStr">
+      <c r="V1" s="66" t="inlineStr">
         <is>
           <t>Show Room
 -
@@ -1273,43 +1292,43 @@
       </c>
     </row>
     <row r="2" ht="306.6" customHeight="1">
-      <c r="A2" s="85" t="inlineStr">
+      <c r="A2" s="87" t="inlineStr">
         <is>
           <t>Daily Briefing
 ( Day ) July ( Date ), 2026</t>
         </is>
       </c>
-      <c r="B2" s="55" t="n"/>
+      <c r="B2" s="57" t="n"/>
       <c r="C2" s="40" t="n"/>
       <c r="D2" s="39" t="n"/>
-      <c r="E2" s="55" t="n"/>
-      <c r="F2" s="55" t="n"/>
+      <c r="E2" s="57" t="n"/>
+      <c r="F2" s="57" t="n"/>
       <c r="G2" s="40" t="n"/>
       <c r="H2" s="39" t="n"/>
       <c r="I2" s="40" t="n"/>
       <c r="J2" s="39" t="n"/>
       <c r="K2" s="40" t="n"/>
       <c r="L2" s="39" t="n"/>
-      <c r="M2" s="55" t="n"/>
+      <c r="M2" s="57" t="n"/>
       <c r="N2" s="40" t="n"/>
       <c r="O2" s="39" t="n"/>
-      <c r="P2" s="55" t="n"/>
-      <c r="Q2" s="55" t="n"/>
+      <c r="P2" s="57" t="n"/>
+      <c r="Q2" s="57" t="n"/>
       <c r="R2" s="40" t="n"/>
       <c r="S2" s="39" t="n"/>
-      <c r="T2" s="55" t="n"/>
+      <c r="T2" s="57" t="n"/>
       <c r="U2" s="40" t="n"/>
       <c r="V2" s="34" t="n"/>
     </row>
     <row r="3" ht="99" customFormat="1" customHeight="1" s="2">
-      <c r="A3" s="59" t="inlineStr">
+      <c r="A3" s="61" t="inlineStr">
         <is>
           <t>Yesterday</t>
         </is>
       </c>
-      <c r="B3" s="54" t="n"/>
+      <c r="B3" s="56" t="n"/>
       <c r="C3" s="38" t="n"/>
-      <c r="D3" s="59" t="inlineStr">
+      <c r="D3" s="61" t="inlineStr">
         <is>
           <t>TODAY</t>
         </is>
@@ -1317,11 +1336,11 @@
       <c r="E3" s="28" t="n"/>
       <c r="F3" s="28" t="n"/>
       <c r="G3" s="23" t="n"/>
-      <c r="H3" s="48" t="n"/>
+      <c r="H3" s="49" t="n"/>
       <c r="I3" s="28" t="n"/>
       <c r="J3" s="28" t="n"/>
       <c r="K3" s="23" t="n"/>
-      <c r="L3" s="59" t="inlineStr">
+      <c r="L3" s="61" t="inlineStr">
         <is>
           <t>Next 5 days</t>
         </is>
@@ -1339,9 +1358,9 @@
     </row>
     <row r="4" ht="88.5" customHeight="1">
       <c r="A4" s="39" t="n"/>
-      <c r="B4" s="55" t="n"/>
+      <c r="B4" s="57" t="n"/>
       <c r="C4" s="40" t="n"/>
-      <c r="D4" s="63" t="inlineStr">
+      <c r="D4" s="64" t="inlineStr">
         <is>
           <t>25-Jul</t>
         </is>
@@ -1370,27 +1389,27 @@
         </is>
       </c>
       <c r="L4" s="4" t="n"/>
-      <c r="M4" s="62">
+      <c r="M4" s="47">
         <f>D4+1</f>
         <v/>
       </c>
       <c r="N4" s="38" t="n"/>
-      <c r="O4" s="62">
+      <c r="O4" s="47">
         <f>M4+1</f>
         <v/>
       </c>
       <c r="P4" s="38" t="n"/>
-      <c r="Q4" s="62">
+      <c r="Q4" s="47">
         <f>O4+1</f>
         <v/>
       </c>
       <c r="R4" s="38" t="n"/>
-      <c r="S4" s="62">
+      <c r="S4" s="47">
         <f>Q4+1</f>
         <v/>
       </c>
       <c r="T4" s="38" t="n"/>
-      <c r="U4" s="62">
+      <c r="U4" s="47">
         <f>S4+1</f>
         <v/>
       </c>
@@ -1408,7 +1427,7 @@
         </is>
       </c>
       <c r="C5" s="38" t="n"/>
-      <c r="D5" s="49" t="inlineStr">
+      <c r="D5" s="51" t="inlineStr">
         <is>
           <t>ARR.</t>
         </is>
@@ -1436,10 +1455,10 @@
       <c r="J5" s="41" t="n">
         <v>79801.19</v>
       </c>
-      <c r="K5" s="68" t="n">
+      <c r="K5" s="69" t="n">
         <v>205427.65</v>
       </c>
-      <c r="L5" s="49" t="inlineStr">
+      <c r="L5" s="51" t="inlineStr">
         <is>
           <t>ARR.</t>
         </is>
@@ -1499,7 +1518,7 @@
       <c r="A6" s="34" t="n"/>
       <c r="B6" s="39" t="n"/>
       <c r="C6" s="40" t="n"/>
-      <c r="D6" s="49" t="inlineStr">
+      <c r="D6" s="51" t="inlineStr">
         <is>
           <t>AVC</t>
         </is>
@@ -1514,7 +1533,7 @@
       <c r="I6" s="34" t="n"/>
       <c r="J6" s="34" t="n"/>
       <c r="K6" s="34" t="n"/>
-      <c r="L6" s="49" t="inlineStr">
+      <c r="L6" s="51" t="inlineStr">
         <is>
           <t>AVC</t>
         </is>
@@ -1555,7 +1574,7 @@
         <v>2</v>
       </c>
       <c r="C7" s="38" t="n"/>
-      <c r="D7" s="49" t="inlineStr">
+      <c r="D7" s="51" t="inlineStr">
         <is>
           <t>DEP.</t>
         </is>
@@ -1584,10 +1603,10 @@
       <c r="J7" s="41" t="n">
         <v>46773.37</v>
       </c>
-      <c r="K7" s="68" t="n">
+      <c r="K7" s="69" t="n">
         <v>29000</v>
       </c>
-      <c r="L7" s="49" t="inlineStr">
+      <c r="L7" s="51" t="inlineStr">
         <is>
           <t>DEP.</t>
         </is>
@@ -1647,7 +1666,7 @@
       <c r="A8" s="34" t="n"/>
       <c r="B8" s="39" t="n"/>
       <c r="C8" s="40" t="n"/>
-      <c r="D8" s="49" t="inlineStr">
+      <c r="D8" s="51" t="inlineStr">
         <is>
           <t>AVC</t>
         </is>
@@ -1662,7 +1681,7 @@
       <c r="I8" s="34" t="n"/>
       <c r="J8" s="34" t="n"/>
       <c r="K8" s="34" t="n"/>
-      <c r="L8" s="49" t="inlineStr">
+      <c r="L8" s="51" t="inlineStr">
         <is>
           <t>AVC</t>
         </is>
@@ -1705,7 +1724,7 @@
         </is>
       </c>
       <c r="C9" s="38" t="n"/>
-      <c r="D9" s="50" t="inlineStr">
+      <c r="D9" s="52" t="inlineStr">
         <is>
           <t>RM Occ.</t>
         </is>
@@ -1713,7 +1732,7 @@
       <c r="E9" s="22" t="n">
         <v>221</v>
       </c>
-      <c r="F9" s="54" t="n"/>
+      <c r="F9" s="56" t="n"/>
       <c r="G9" s="38" t="n"/>
       <c r="H9" s="35" t="inlineStr">
         <is>
@@ -1721,16 +1740,16 @@
 Comm. target</t>
         </is>
       </c>
-      <c r="I9" s="52" t="n">
+      <c r="I9" s="54" t="n">
         <v>1267</v>
       </c>
-      <c r="J9" s="52" t="n">
+      <c r="J9" s="54" t="n">
         <v>65214</v>
       </c>
-      <c r="K9" s="68" t="n">
+      <c r="K9" s="69" t="n">
         <v>160368</v>
       </c>
-      <c r="L9" s="50" t="inlineStr">
+      <c r="L9" s="52" t="inlineStr">
         <is>
           <t>RM Occ.</t>
         </is>
@@ -1762,12 +1781,12 @@
       <c r="C10" s="40" t="n"/>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="39" t="n"/>
-      <c r="F10" s="55" t="n"/>
+      <c r="F10" s="57" t="n"/>
       <c r="G10" s="40" t="n"/>
-      <c r="H10" s="51" t="n"/>
-      <c r="I10" s="51" t="n"/>
-      <c r="J10" s="51" t="n"/>
-      <c r="K10" s="51" t="n"/>
+      <c r="H10" s="53" t="n"/>
+      <c r="I10" s="53" t="n"/>
+      <c r="J10" s="53" t="n"/>
+      <c r="K10" s="53" t="n"/>
       <c r="L10" s="34" t="n"/>
       <c r="M10" s="39" t="n"/>
       <c r="N10" s="40" t="n"/>
@@ -1786,7 +1805,7 @@
           <t>ADR</t>
         </is>
       </c>
-      <c r="B11" s="86" t="n">
+      <c r="B11" s="88" t="n">
         <v>3595.79</v>
       </c>
       <c r="C11" s="23" t="n"/>
@@ -1795,7 +1814,7 @@
           <t>Occ %</t>
         </is>
       </c>
-      <c r="E11" s="87" t="n">
+      <c r="E11" s="89" t="n">
         <v>66.06</v>
       </c>
       <c r="F11" s="28" t="n"/>
@@ -1809,23 +1828,23 @@
           <t>OCC %</t>
         </is>
       </c>
-      <c r="M11" s="88" t="n">
+      <c r="M11" s="90" t="n">
         <v>85.84615384615385</v>
       </c>
       <c r="N11" s="23" t="n"/>
-      <c r="O11" s="88" t="n">
+      <c r="O11" s="90" t="n">
         <v>71.69230769230769</v>
       </c>
       <c r="P11" s="23" t="n"/>
-      <c r="Q11" s="88" t="n">
+      <c r="Q11" s="90" t="n">
         <v>90.15384615384615</v>
       </c>
       <c r="R11" s="23" t="n"/>
-      <c r="S11" s="88" t="n">
+      <c r="S11" s="90" t="n">
         <v>66.9753086419753</v>
       </c>
       <c r="T11" s="23" t="n"/>
-      <c r="U11" s="88" t="n">
+      <c r="U11" s="90" t="n">
         <v>69.53846153846153</v>
       </c>
       <c r="V11" s="23" t="n"/>
@@ -1836,7 +1855,7 @@
           <t>Occ%</t>
         </is>
       </c>
-      <c r="B12" s="89" t="n">
+      <c r="B12" s="91" t="n">
         <v>71.53</v>
       </c>
       <c r="C12" s="38" t="n"/>
@@ -1865,16 +1884,16 @@
           <t>Gallery</t>
         </is>
       </c>
-      <c r="I12" s="78" t="n">
+      <c r="I12" s="80" t="n">
         <v>3928.97</v>
       </c>
       <c r="J12" s="41" t="n">
         <v>70219.72</v>
       </c>
-      <c r="K12" s="79" t="n">
+      <c r="K12" s="81" t="n">
         <v>180414</v>
       </c>
-      <c r="L12" s="56" t="inlineStr">
+      <c r="L12" s="58" t="inlineStr">
         <is>
           <t>Guest In 
 House</t>
@@ -1924,10 +1943,10 @@
       <c r="F13" s="34" t="n"/>
       <c r="G13" s="34" t="n"/>
       <c r="H13" s="34" t="n"/>
-      <c r="I13" s="51" t="n"/>
+      <c r="I13" s="53" t="n"/>
       <c r="J13" s="34" t="n"/>
-      <c r="K13" s="51" t="n"/>
-      <c r="L13" s="57" t="n"/>
+      <c r="K13" s="53" t="n"/>
+      <c r="L13" s="59" t="n"/>
       <c r="M13" s="39" t="n"/>
       <c r="N13" s="40" t="n"/>
       <c r="O13" s="39" t="n"/>
@@ -1940,31 +1959,31 @@
       <c r="V13" s="40" t="n"/>
     </row>
     <row r="14" ht="99" customFormat="1" customHeight="1" s="2">
-      <c r="A14" s="90" t="inlineStr">
+      <c r="A14" s="92" t="inlineStr">
         <is>
           <t>VIP ARRIVAL</t>
         </is>
       </c>
-      <c r="B14" s="54" t="n"/>
-      <c r="C14" s="54" t="n"/>
-      <c r="D14" s="54" t="n"/>
-      <c r="E14" s="54" t="n"/>
-      <c r="F14" s="54" t="n"/>
-      <c r="G14" s="54" t="n"/>
-      <c r="H14" s="54" t="n"/>
-      <c r="I14" s="54" t="n"/>
-      <c r="J14" s="54" t="n"/>
-      <c r="K14" s="54" t="n"/>
-      <c r="L14" s="54" t="n"/>
-      <c r="M14" s="54" t="n"/>
-      <c r="N14" s="54" t="n"/>
-      <c r="O14" s="54" t="n"/>
-      <c r="P14" s="54" t="n"/>
-      <c r="Q14" s="54" t="n"/>
-      <c r="R14" s="54" t="n"/>
-      <c r="S14" s="54" t="n"/>
-      <c r="T14" s="54" t="n"/>
-      <c r="U14" s="54" t="n"/>
+      <c r="B14" s="56" t="n"/>
+      <c r="C14" s="56" t="n"/>
+      <c r="D14" s="56" t="n"/>
+      <c r="E14" s="56" t="n"/>
+      <c r="F14" s="56" t="n"/>
+      <c r="G14" s="56" t="n"/>
+      <c r="H14" s="56" t="n"/>
+      <c r="I14" s="56" t="n"/>
+      <c r="J14" s="56" t="n"/>
+      <c r="K14" s="56" t="n"/>
+      <c r="L14" s="56" t="n"/>
+      <c r="M14" s="56" t="n"/>
+      <c r="N14" s="56" t="n"/>
+      <c r="O14" s="56" t="n"/>
+      <c r="P14" s="56" t="n"/>
+      <c r="Q14" s="56" t="n"/>
+      <c r="R14" s="56" t="n"/>
+      <c r="S14" s="56" t="n"/>
+      <c r="T14" s="56" t="n"/>
+      <c r="U14" s="56" t="n"/>
       <c r="V14" s="38" t="n"/>
     </row>
     <row r="15" ht="96" customHeight="1">
@@ -2036,44 +2055,60 @@
       <c r="V15" s="23" t="n"/>
     </row>
     <row r="16" ht="114" customHeight="1">
-      <c r="A16" s="25" t="inlineStr">
-        <is>
-          <t>Barzelay,Udi,Mr</t>
+      <c r="A16" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Udi Barzelay</t>
         </is>
       </c>
       <c r="B16" s="23" t="n"/>
-      <c r="C16" s="7" t="n"/>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D16" s="24" t="inlineStr">
         <is>
           <t>0009</t>
         </is>
       </c>
       <c r="E16" s="23" t="n"/>
-      <c r="F16" s="24" t="n"/>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G16" s="23" t="n"/>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J16" s="9" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
-        </is>
-      </c>
-      <c r="K16" s="8" t="n"/>
-      <c r="L16" s="31" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>27/07/26</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L16" s="94" t="inlineStr">
+        <is>
+          <t>12.00</t>
         </is>
       </c>
       <c r="M16" s="23" t="n"/>
-      <c r="N16" s="22" t="n"/>
+      <c r="N16" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O16" s="23" t="n"/>
       <c r="P16" s="27" t="inlineStr">
         <is>
@@ -2093,20 +2128,29 @@
       <c r="V16" s="23" t="n"/>
     </row>
     <row r="17" ht="114" customHeight="1">
-      <c r="A17" s="25" t="inlineStr">
-        <is>
-          <t>Burgess,Laurenca David,Mr</t>
+      <c r="A17" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Laurenca David Burgess</t>
         </is>
       </c>
       <c r="B17" s="23" t="n"/>
-      <c r="C17" s="7" t="n"/>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D17" s="24" t="inlineStr">
         <is>
           <t>0019</t>
         </is>
       </c>
       <c r="E17" s="23" t="n"/>
-      <c r="F17" s="24" t="n"/>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>VIPG
+SILVER</t>
+        </is>
+      </c>
       <c r="G17" s="23" t="n"/>
       <c r="H17" s="8" t="inlineStr">
         <is>
@@ -2115,18 +2159,30 @@
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
-        </is>
-      </c>
-      <c r="K17" s="8" t="n"/>
-      <c r="L17" s="31" t="n"/>
+          <t>01/08/26</t>
+        </is>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L17" s="50" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
       <c r="M17" s="23" t="n"/>
-      <c r="N17" s="22" t="n"/>
+      <c r="N17" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O17" s="23" t="n"/>
       <c r="P17" s="27" t="inlineStr">
         <is>
@@ -2142,44 +2198,61 @@
       <c r="V17" s="23" t="n"/>
     </row>
     <row r="18" ht="114" customHeight="1">
-      <c r="A18" s="25" t="inlineStr">
-        <is>
-          <t>Kanwatjana,Taniga,Ms</t>
+      <c r="A18" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Taniga Kanwatjana</t>
         </is>
       </c>
       <c r="B18" s="23" t="n"/>
-      <c r="C18" s="7" t="n"/>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D18" s="24" t="inlineStr">
         <is>
           <t>0020</t>
         </is>
       </c>
       <c r="E18" s="23" t="n"/>
-      <c r="F18" s="24" t="n"/>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>VIPG
+SILVER</t>
+        </is>
+      </c>
       <c r="G18" s="23" t="n"/>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6+1</t>
         </is>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J18" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K18" s="8" t="n"/>
-      <c r="L18" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L18" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M18" s="23" t="n"/>
-      <c r="N18" s="22" t="n"/>
+      <c r="N18" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O18" s="23" t="n"/>
       <c r="P18" s="27" t="inlineStr">
         <is>
@@ -2202,44 +2275,60 @@
       <c r="V18" s="23" t="n"/>
     </row>
     <row r="19" ht="114" customHeight="1">
-      <c r="A19" s="25" t="inlineStr">
-        <is>
-          <t>Rakmai,Krit,Mr</t>
+      <c r="A19" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Krit Rakmai</t>
         </is>
       </c>
       <c r="B19" s="23" t="n"/>
-      <c r="C19" s="7" t="n"/>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D19" s="24" t="inlineStr">
         <is>
           <t>0024</t>
         </is>
       </c>
       <c r="E19" s="23" t="n"/>
-      <c r="F19" s="24" t="n"/>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G19" s="23" t="n"/>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2+4</t>
         </is>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J19" s="9" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
-        </is>
-      </c>
-      <c r="K19" s="8" t="n"/>
-      <c r="L19" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>27/07/26</t>
+        </is>
+      </c>
+      <c r="K19" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L19" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M19" s="23" t="n"/>
-      <c r="N19" s="22" t="n"/>
+      <c r="N19" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O19" s="23" t="n"/>
       <c r="P19" s="27" t="inlineStr">
         <is>
@@ -2264,13 +2353,17 @@
       <c r="V19" s="23" t="n"/>
     </row>
     <row r="20" ht="114" customHeight="1">
-      <c r="A20" s="25" t="inlineStr">
-        <is>
-          <t>Ian Jones,Mark,Mr</t>
+      <c r="A20" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Mark Ian Jones</t>
         </is>
       </c>
       <c r="B20" s="23" t="n"/>
-      <c r="C20" s="7" t="n"/>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D20" s="24" t="inlineStr">
         <is>
           <t>0027</t>
@@ -2279,33 +2372,42 @@
       <c r="E20" s="23" t="n"/>
       <c r="F20" s="24" t="inlineStr">
         <is>
-          <t>VIPR</t>
+          <t>VIPR
+SILVER</t>
         </is>
       </c>
       <c r="G20" s="23" t="n"/>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3+3</t>
         </is>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
-        </is>
-      </c>
-      <c r="K20" s="8" t="n"/>
-      <c r="L20" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>29/07/26</t>
+        </is>
+      </c>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L20" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M20" s="23" t="n"/>
-      <c r="N20" s="22" t="n"/>
+      <c r="N20" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O20" s="23" t="n"/>
       <c r="P20" s="27" t="inlineStr">
         <is>
@@ -2325,20 +2427,28 @@
       <c r="V20" s="23" t="n"/>
     </row>
     <row r="21" ht="114" customHeight="1">
-      <c r="A21" s="25" t="inlineStr">
-        <is>
-          <t>Atichosakun,Sahachart,Mr</t>
+      <c r="A21" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Sahachart Atichosakun</t>
         </is>
       </c>
       <c r="B21" s="23" t="n"/>
-      <c r="C21" s="7" t="n"/>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D21" s="24" t="inlineStr">
         <is>
           <t>0028</t>
         </is>
       </c>
       <c r="E21" s="23" t="n"/>
-      <c r="F21" s="24" t="n"/>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G21" s="23" t="n"/>
       <c r="H21" s="8" t="inlineStr">
         <is>
@@ -2347,22 +2457,30 @@
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
-        </is>
-      </c>
-      <c r="K21" s="8" t="n"/>
-      <c r="L21" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>28/07/26</t>
+        </is>
+      </c>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L21" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M21" s="23" t="n"/>
-      <c r="N21" s="22" t="n"/>
+      <c r="N21" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O21" s="23" t="n"/>
       <c r="P21" s="27" t="inlineStr">
         <is>
@@ -2377,44 +2495,60 @@
       <c r="V21" s="23" t="n"/>
     </row>
     <row r="22" ht="114" customHeight="1">
-      <c r="A22" s="25" t="inlineStr">
-        <is>
-          <t>Steckel,Johannes,Mr</t>
+      <c r="A22" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Johannes Steckel</t>
         </is>
       </c>
       <c r="B22" s="23" t="n"/>
-      <c r="C22" s="7" t="n"/>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D22" s="24" t="inlineStr">
         <is>
           <t>0035</t>
         </is>
       </c>
       <c r="E22" s="23" t="n"/>
-      <c r="F22" s="24" t="n"/>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G22" s="23" t="n"/>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
-        </is>
-      </c>
-      <c r="K22" s="8" t="n"/>
-      <c r="L22" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>31/07/26</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L22" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M22" s="23" t="n"/>
-      <c r="N22" s="22" t="n"/>
+      <c r="N22" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O22" s="23" t="n"/>
       <c r="P22" s="27" t="inlineStr">
         <is>
@@ -2431,44 +2565,60 @@
       <c r="V22" s="23" t="n"/>
     </row>
     <row r="23" ht="114" customHeight="1">
-      <c r="A23" s="25" t="inlineStr">
-        <is>
-          <t>Mason,Ben,Mr</t>
+      <c r="A23" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Ben Mason</t>
         </is>
       </c>
       <c r="B23" s="23" t="n"/>
-      <c r="C23" s="7" t="n"/>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D23" s="24" t="inlineStr">
         <is>
           <t>0038</t>
         </is>
       </c>
       <c r="E23" s="23" t="n"/>
-      <c r="F23" s="24" t="n"/>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G23" s="23" t="n"/>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2+2</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J23" s="9" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
-        </is>
-      </c>
-      <c r="K23" s="8" t="n"/>
-      <c r="L23" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>27/07/26</t>
+        </is>
+      </c>
+      <c r="K23" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L23" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M23" s="23" t="n"/>
-      <c r="N23" s="22" t="n"/>
+      <c r="N23" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O23" s="23" t="n"/>
       <c r="P23" s="27" t="inlineStr">
         <is>
@@ -2485,20 +2635,28 @@
       <c r="V23" s="23" t="n"/>
     </row>
     <row r="24" ht="114" customHeight="1">
-      <c r="A24" s="25" t="inlineStr">
-        <is>
-          <t>Marian Marian,Gabriel,Mr</t>
+      <c r="A24" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Gabriel Marian Marian</t>
         </is>
       </c>
       <c r="B24" s="23" t="n"/>
-      <c r="C24" s="7" t="n"/>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D24" s="24" t="inlineStr">
         <is>
           <t>0049</t>
         </is>
       </c>
       <c r="E24" s="23" t="n"/>
-      <c r="F24" s="24" t="n"/>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G24" s="23" t="n"/>
       <c r="H24" s="8" t="inlineStr">
         <is>
@@ -2507,22 +2665,30 @@
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J24" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K24" s="8" t="n"/>
-      <c r="L24" s="31" t="inlineStr">
-        <is>
-          <t>11:35</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L24" s="94" t="inlineStr">
+        <is>
+          <t>11.35</t>
         </is>
       </c>
       <c r="M24" s="23" t="n"/>
-      <c r="N24" s="22" t="n"/>
+      <c r="N24" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O24" s="23" t="n"/>
       <c r="P24" s="27" t="inlineStr">
         <is>
@@ -2546,44 +2712,61 @@
       <c r="V24" s="23" t="n"/>
     </row>
     <row r="25" ht="114" customHeight="1">
-      <c r="A25" s="25" t="inlineStr">
-        <is>
-          <t>Umit,Clare-Marie,Mrs</t>
+      <c r="A25" s="93" t="inlineStr">
+        <is>
+          <t>Mrs. Clare-Marie Umit</t>
         </is>
       </c>
       <c r="B25" s="23" t="n"/>
-      <c r="C25" s="7" t="n"/>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D25" s="24" t="inlineStr">
         <is>
           <t>0054</t>
         </is>
       </c>
       <c r="E25" s="23" t="n"/>
-      <c r="F25" s="24" t="n"/>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>VIPG
+SILVER</t>
+        </is>
+      </c>
       <c r="G25" s="23" t="n"/>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3+1</t>
         </is>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J25" s="9" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
-        </is>
-      </c>
-      <c r="K25" s="8" t="n"/>
-      <c r="L25" s="31" t="inlineStr">
-        <is>
-          <t>12:10</t>
+          <t>28/07/26</t>
+        </is>
+      </c>
+      <c r="K25" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L25" s="94" t="inlineStr">
+        <is>
+          <t>12.10</t>
         </is>
       </c>
       <c r="M25" s="23" t="n"/>
-      <c r="N25" s="22" t="n"/>
+      <c r="N25" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O25" s="23" t="n"/>
       <c r="P25" s="27" t="inlineStr">
         <is>
@@ -2605,13 +2788,17 @@
       <c r="V25" s="23" t="n"/>
     </row>
     <row r="26" ht="114" customHeight="1">
-      <c r="A26" s="25" t="inlineStr">
-        <is>
-          <t>Zou,Rongrong,Mr</t>
+      <c r="A26" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Rongrong Zou</t>
         </is>
       </c>
       <c r="B26" s="23" t="n"/>
-      <c r="C26" s="7" t="n"/>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D26" s="24" t="inlineStr">
         <is>
           <t>0062</t>
@@ -2631,22 +2818,30 @@
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J26" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K26" s="8" t="n"/>
-      <c r="L26" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L26" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M26" s="23" t="n"/>
-      <c r="N26" s="22" t="n"/>
+      <c r="N26" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O26" s="23" t="n"/>
       <c r="P26" s="27" t="inlineStr">
         <is>
@@ -2669,20 +2864,28 @@
       <c r="V26" s="23" t="n"/>
     </row>
     <row r="27" ht="114" customHeight="1">
-      <c r="A27" s="25" t="inlineStr">
-        <is>
-          <t>Arttachariya,Yosapol,Mr</t>
+      <c r="A27" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Yosapol Arttachariya</t>
         </is>
       </c>
       <c r="B27" s="23" t="n"/>
-      <c r="C27" s="7" t="n"/>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D27" s="24" t="inlineStr">
         <is>
           <t>0065</t>
         </is>
       </c>
       <c r="E27" s="23" t="n"/>
-      <c r="F27" s="24" t="n"/>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G27" s="23" t="n"/>
       <c r="H27" s="8" t="inlineStr">
         <is>
@@ -2691,22 +2894,30 @@
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J27" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K27" s="8" t="n"/>
-      <c r="L27" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K27" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L27" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M27" s="23" t="n"/>
-      <c r="N27" s="22" t="n"/>
+      <c r="N27" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O27" s="23" t="n"/>
       <c r="P27" s="27" t="inlineStr">
         <is>
@@ -2725,13 +2936,17 @@
       <c r="V27" s="23" t="n"/>
     </row>
     <row r="28" ht="114" customHeight="1">
-      <c r="A28" s="25" t="inlineStr">
-        <is>
-          <t>Maintenance,Maintenance,Mr</t>
+      <c r="A28" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Maintenance Maintenance</t>
         </is>
       </c>
       <c r="B28" s="23" t="n"/>
-      <c r="C28" s="7" t="n"/>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D28" s="24" t="inlineStr">
         <is>
           <t>0067</t>
@@ -2751,22 +2966,30 @@
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J28" s="9" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
-        </is>
-      </c>
-      <c r="K28" s="8" t="n"/>
-      <c r="L28" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>01/08/26</t>
+        </is>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L28" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M28" s="23" t="n"/>
-      <c r="N28" s="22" t="n"/>
+      <c r="N28" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O28" s="23" t="n"/>
       <c r="P28" s="27" t="inlineStr">
         <is>
@@ -2781,44 +3004,60 @@
       <c r="V28" s="23" t="n"/>
     </row>
     <row r="29" ht="114" customHeight="1">
-      <c r="A29" s="25" t="inlineStr">
-        <is>
-          <t>Raksiltham,Nantana,Ms</t>
+      <c r="A29" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Nantana Raksiltham</t>
         </is>
       </c>
       <c r="B29" s="23" t="n"/>
-      <c r="C29" s="7" t="n"/>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D29" s="24" t="inlineStr">
         <is>
           <t>0068</t>
         </is>
       </c>
       <c r="E29" s="23" t="n"/>
-      <c r="F29" s="24" t="n"/>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G29" s="23" t="n"/>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4+1</t>
         </is>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J29" s="9" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
-        </is>
-      </c>
-      <c r="K29" s="8" t="n"/>
-      <c r="L29" s="31" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>28/07/26</t>
+        </is>
+      </c>
+      <c r="K29" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L29" s="94" t="inlineStr">
+        <is>
+          <t>11.00</t>
         </is>
       </c>
       <c r="M29" s="23" t="n"/>
-      <c r="N29" s="22" t="n"/>
+      <c r="N29" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O29" s="23" t="n"/>
       <c r="P29" s="27" t="inlineStr">
         <is>
@@ -2834,20 +3073,28 @@
       <c r="V29" s="23" t="n"/>
     </row>
     <row r="30" ht="114" customHeight="1">
-      <c r="A30" s="25" t="inlineStr">
-        <is>
-          <t>Kaewthaisong,Katkaew,Ms</t>
+      <c r="A30" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Katkaew Kaewthaisong</t>
         </is>
       </c>
       <c r="B30" s="23" t="n"/>
-      <c r="C30" s="7" t="n"/>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D30" s="24" t="inlineStr">
         <is>
           <t>0071</t>
         </is>
       </c>
       <c r="E30" s="23" t="n"/>
-      <c r="F30" s="24" t="n"/>
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G30" s="23" t="n"/>
       <c r="H30" s="8" t="inlineStr">
         <is>
@@ -2856,22 +3103,30 @@
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J30" s="9" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
-        </is>
-      </c>
-      <c r="K30" s="8" t="n"/>
-      <c r="L30" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>28/07/26</t>
+        </is>
+      </c>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L30" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M30" s="23" t="n"/>
-      <c r="N30" s="22" t="n"/>
+      <c r="N30" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O30" s="23" t="n"/>
       <c r="P30" s="27" t="inlineStr">
         <is>
@@ -2886,13 +3141,17 @@
       <c r="V30" s="23" t="n"/>
     </row>
     <row r="31" ht="114" customHeight="1">
-      <c r="A31" s="25" t="inlineStr">
-        <is>
-          <t>Charoenpak,Nattaporn,Ms</t>
+      <c r="A31" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Nattaporn Charoenpak</t>
         </is>
       </c>
       <c r="B31" s="23" t="n"/>
-      <c r="C31" s="7" t="n"/>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D31" s="24" t="inlineStr">
         <is>
           <t>0073</t>
@@ -2901,7 +3160,8 @@
       <c r="E31" s="23" t="n"/>
       <c r="F31" s="24" t="inlineStr">
         <is>
-          <t>VIPO</t>
+          <t>VIPO
+GOLD</t>
         </is>
       </c>
       <c r="G31" s="23" t="n"/>
@@ -2912,22 +3172,30 @@
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J31" s="9" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
-        </is>
-      </c>
-      <c r="K31" s="8" t="n"/>
-      <c r="L31" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>27/07/26</t>
+        </is>
+      </c>
+      <c r="K31" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L31" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M31" s="23" t="n"/>
-      <c r="N31" s="22" t="n"/>
+      <c r="N31" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O31" s="23" t="n"/>
       <c r="P31" s="27" t="inlineStr">
         <is>
@@ -2942,13 +3210,17 @@
       <c r="V31" s="23" t="n"/>
     </row>
     <row r="32" ht="114" customHeight="1">
-      <c r="A32" s="25" t="inlineStr">
-        <is>
-          <t>Jenpoomjai,Chompunut,Ms</t>
+      <c r="A32" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Chompunut Jenpoomjai</t>
         </is>
       </c>
       <c r="B32" s="23" t="n"/>
-      <c r="C32" s="7" t="n"/>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D32" s="24" t="inlineStr">
         <is>
           <t>0075</t>
@@ -2968,22 +3240,30 @@
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K32" s="8" t="n"/>
-      <c r="L32" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K32" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L32" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M32" s="23" t="n"/>
-      <c r="N32" s="22" t="n"/>
+      <c r="N32" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O32" s="23" t="n"/>
       <c r="P32" s="27" t="inlineStr">
         <is>
@@ -3006,44 +3286,61 @@
       <c r="V32" s="23" t="n"/>
     </row>
     <row r="33" ht="114" customHeight="1">
-      <c r="A33" s="25" t="inlineStr">
-        <is>
-          <t>Eksorakul,Teerawut,Mr</t>
+      <c r="A33" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Teerawut Eksorakul</t>
         </is>
       </c>
       <c r="B33" s="23" t="n"/>
-      <c r="C33" s="7" t="n"/>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D33" s="24" t="inlineStr">
         <is>
           <t>0076</t>
         </is>
       </c>
       <c r="E33" s="23" t="n"/>
-      <c r="F33" s="24" t="n"/>
+      <c r="F33" s="24" t="inlineStr">
+        <is>
+          <t>VIPG
+SILVER</t>
+        </is>
+      </c>
       <c r="G33" s="23" t="n"/>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2+1</t>
         </is>
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J33" s="9" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
-        </is>
-      </c>
-      <c r="K33" s="8" t="n"/>
-      <c r="L33" s="31" t="inlineStr">
-        <is>
-          <t>13:05</t>
+          <t>28/07/26</t>
+        </is>
+      </c>
+      <c r="K33" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L33" s="94" t="inlineStr">
+        <is>
+          <t>13.05</t>
         </is>
       </c>
       <c r="M33" s="23" t="n"/>
-      <c r="N33" s="22" t="n"/>
+      <c r="N33" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O33" s="23" t="n"/>
       <c r="P33" s="27" t="inlineStr">
         <is>
@@ -3059,44 +3356,60 @@
       <c r="V33" s="23" t="n"/>
     </row>
     <row r="34" ht="114" customHeight="1">
-      <c r="A34" s="25" t="inlineStr">
-        <is>
-          <t>Poolsawad,Kajornpong,Mr</t>
+      <c r="A34" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Kajornpong Poolsawad</t>
         </is>
       </c>
       <c r="B34" s="23" t="n"/>
-      <c r="C34" s="7" t="n"/>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D34" s="24" t="inlineStr">
         <is>
           <t>0077</t>
         </is>
       </c>
       <c r="E34" s="23" t="n"/>
-      <c r="F34" s="24" t="n"/>
+      <c r="F34" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G34" s="23" t="n"/>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4+2</t>
         </is>
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J34" s="9" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
-        </is>
-      </c>
-      <c r="K34" s="8" t="n"/>
-      <c r="L34" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>28/07/26</t>
+        </is>
+      </c>
+      <c r="K34" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L34" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M34" s="23" t="n"/>
-      <c r="N34" s="22" t="n"/>
+      <c r="N34" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O34" s="23" t="n"/>
       <c r="P34" s="27" t="inlineStr">
         <is>
@@ -3113,20 +3426,28 @@
       <c r="V34" s="23" t="n"/>
     </row>
     <row r="35" ht="114" customHeight="1">
-      <c r="A35" s="25" t="inlineStr">
-        <is>
-          <t>Sodsri,Sornthep,Mr</t>
+      <c r="A35" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Sornthep Sodsri</t>
         </is>
       </c>
       <c r="B35" s="23" t="n"/>
-      <c r="C35" s="7" t="n"/>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D35" s="24" t="inlineStr">
         <is>
           <t>1201</t>
         </is>
       </c>
       <c r="E35" s="23" t="n"/>
-      <c r="F35" s="24" t="n"/>
+      <c r="F35" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G35" s="23" t="n"/>
       <c r="H35" s="8" t="inlineStr">
         <is>
@@ -3135,22 +3456,30 @@
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J35" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K35" s="8" t="n"/>
-      <c r="L35" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K35" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L35" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M35" s="23" t="n"/>
-      <c r="N35" s="22" t="n"/>
+      <c r="N35" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O35" s="23" t="n"/>
       <c r="P35" s="27" t="inlineStr">
         <is>
@@ -3166,13 +3495,17 @@
       <c r="V35" s="23" t="n"/>
     </row>
     <row r="36" ht="114" customHeight="1">
-      <c r="A36" s="25" t="inlineStr">
-        <is>
-          <t>Kuhamuk,Siwaporn,Ms</t>
+      <c r="A36" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Siwaporn Kuhamuk</t>
         </is>
       </c>
       <c r="B36" s="23" t="n"/>
-      <c r="C36" s="7" t="n"/>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D36" s="24" t="inlineStr">
         <is>
           <t>1202</t>
@@ -3181,7 +3514,8 @@
       <c r="E36" s="23" t="n"/>
       <c r="F36" s="24" t="inlineStr">
         <is>
-          <t>VIPG</t>
+          <t>VIPG
+GOLD</t>
         </is>
       </c>
       <c r="G36" s="23" t="n"/>
@@ -3192,22 +3526,30 @@
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J36" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K36" s="8" t="n"/>
-      <c r="L36" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K36" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L36" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M36" s="23" t="n"/>
-      <c r="N36" s="22" t="n"/>
+      <c r="N36" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O36" s="23" t="n"/>
       <c r="P36" s="27" t="inlineStr">
         <is>
@@ -3229,20 +3571,29 @@
       <c r="V36" s="23" t="n"/>
     </row>
     <row r="37" ht="114" customHeight="1">
-      <c r="A37" s="25" t="inlineStr">
-        <is>
-          <t>Rattanapong,Kanlayanee,Ms</t>
+      <c r="A37" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Kanlayanee Rattanapong</t>
         </is>
       </c>
       <c r="B37" s="23" t="n"/>
-      <c r="C37" s="7" t="n"/>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D37" s="24" t="inlineStr">
         <is>
           <t>1203</t>
         </is>
       </c>
       <c r="E37" s="23" t="n"/>
-      <c r="F37" s="24" t="n"/>
+      <c r="F37" s="24" t="inlineStr">
+        <is>
+          <t>VIPG
+SILVER</t>
+        </is>
+      </c>
       <c r="G37" s="23" t="n"/>
       <c r="H37" s="8" t="inlineStr">
         <is>
@@ -3251,22 +3602,30 @@
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J37" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K37" s="8" t="n"/>
-      <c r="L37" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K37" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L37" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M37" s="23" t="n"/>
-      <c r="N37" s="22" t="n"/>
+      <c r="N37" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O37" s="23" t="n"/>
       <c r="P37" s="27" t="inlineStr">
         <is>
@@ -3286,20 +3645,29 @@
       <c r="V37" s="23" t="n"/>
     </row>
     <row r="38" ht="114" customHeight="1">
-      <c r="A38" s="25" t="inlineStr">
-        <is>
-          <t>Rattanapong,Kanlayanee,Ms</t>
+      <c r="A38" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Kanlayanee Rattanapong</t>
         </is>
       </c>
       <c r="B38" s="23" t="n"/>
-      <c r="C38" s="7" t="n"/>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D38" s="24" t="inlineStr">
         <is>
           <t>1204</t>
         </is>
       </c>
       <c r="E38" s="23" t="n"/>
-      <c r="F38" s="24" t="n"/>
+      <c r="F38" s="24" t="inlineStr">
+        <is>
+          <t>VIPG
+SILVER</t>
+        </is>
+      </c>
       <c r="G38" s="23" t="n"/>
       <c r="H38" s="8" t="inlineStr">
         <is>
@@ -3308,22 +3676,30 @@
       </c>
       <c r="I38" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J38" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K38" s="8" t="n"/>
-      <c r="L38" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K38" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L38" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M38" s="23" t="n"/>
-      <c r="N38" s="22" t="n"/>
+      <c r="N38" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O38" s="23" t="n"/>
       <c r="P38" s="27" t="inlineStr">
         <is>
@@ -3343,20 +3719,29 @@
       <c r="V38" s="23" t="n"/>
     </row>
     <row r="39" ht="114" customHeight="1">
-      <c r="A39" s="25" t="inlineStr">
-        <is>
-          <t>Rattanapong,Kanlayanee,Ms</t>
+      <c r="A39" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Kanlayanee Rattanapong</t>
         </is>
       </c>
       <c r="B39" s="23" t="n"/>
-      <c r="C39" s="7" t="n"/>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D39" s="24" t="inlineStr">
         <is>
           <t>1205</t>
         </is>
       </c>
       <c r="E39" s="23" t="n"/>
-      <c r="F39" s="24" t="n"/>
+      <c r="F39" s="24" t="inlineStr">
+        <is>
+          <t>VIPG
+SILVER</t>
+        </is>
+      </c>
       <c r="G39" s="23" t="n"/>
       <c r="H39" s="8" t="inlineStr">
         <is>
@@ -3365,22 +3750,30 @@
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J39" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K39" s="8" t="n"/>
-      <c r="L39" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K39" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L39" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M39" s="23" t="n"/>
-      <c r="N39" s="22" t="n"/>
+      <c r="N39" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O39" s="23" t="n"/>
       <c r="P39" s="27" t="inlineStr">
         <is>
@@ -3400,44 +3793,61 @@
       <c r="V39" s="23" t="n"/>
     </row>
     <row r="40" ht="114" customHeight="1">
-      <c r="A40" s="25" t="inlineStr">
-        <is>
-          <t>Mirsaitova,Margarita,Mrs</t>
+      <c r="A40" s="93" t="inlineStr">
+        <is>
+          <t>Mrs. Margarita Mirsaitova</t>
         </is>
       </c>
       <c r="B40" s="23" t="n"/>
-      <c r="C40" s="7" t="n"/>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D40" s="24" t="inlineStr">
         <is>
           <t>1206</t>
         </is>
       </c>
       <c r="E40" s="23" t="n"/>
-      <c r="F40" s="24" t="n"/>
+      <c r="F40" s="24" t="inlineStr">
+        <is>
+          <t>VIPG
+SILVER</t>
+        </is>
+      </c>
       <c r="G40" s="23" t="n"/>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2+2</t>
         </is>
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J40" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K40" s="8" t="n"/>
-      <c r="L40" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K40" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L40" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M40" s="23" t="n"/>
-      <c r="N40" s="22" t="n"/>
+      <c r="N40" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O40" s="23" t="n"/>
       <c r="P40" s="27" t="inlineStr">
         <is>
@@ -3461,13 +3871,17 @@
       <c r="V40" s="23" t="n"/>
     </row>
     <row r="41" ht="114" customHeight="1">
-      <c r="A41" s="25" t="inlineStr">
-        <is>
-          <t>Charoenpak,Nattaporn,Ms</t>
+      <c r="A41" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Nattaporn Charoenpak</t>
         </is>
       </c>
       <c r="B41" s="23" t="n"/>
-      <c r="C41" s="7" t="n"/>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D41" s="24" t="inlineStr">
         <is>
           <t>1207</t>
@@ -3476,7 +3890,8 @@
       <c r="E41" s="23" t="n"/>
       <c r="F41" s="24" t="inlineStr">
         <is>
-          <t>VIPO</t>
+          <t>VIPO
+GOLD</t>
         </is>
       </c>
       <c r="G41" s="23" t="n"/>
@@ -3487,22 +3902,30 @@
       </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J41" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K41" s="8" t="n"/>
-      <c r="L41" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K41" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L41" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M41" s="23" t="n"/>
-      <c r="N41" s="22" t="n"/>
+      <c r="N41" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O41" s="23" t="n"/>
       <c r="P41" s="27" t="inlineStr">
         <is>
@@ -3517,13 +3940,17 @@
       <c r="V41" s="23" t="n"/>
     </row>
     <row r="42" ht="114" customHeight="1">
-      <c r="A42" s="25" t="inlineStr">
-        <is>
-          <t>Goncharenko,Olga,Ms</t>
+      <c r="A42" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Olga Goncharenko</t>
         </is>
       </c>
       <c r="B42" s="23" t="n"/>
-      <c r="C42" s="7" t="n"/>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D42" s="24" t="inlineStr">
         <is>
           <t>1209</t>
@@ -3532,7 +3959,8 @@
       <c r="E42" s="23" t="n"/>
       <c r="F42" s="24" t="inlineStr">
         <is>
-          <t>VIPR</t>
+          <t>VIPR
+GOLD</t>
         </is>
       </c>
       <c r="G42" s="23" t="n"/>
@@ -3543,22 +3971,30 @@
       </c>
       <c r="I42" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J42" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K42" s="8" t="n"/>
-      <c r="L42" s="31" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K42" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L42" s="94" t="inlineStr">
+        <is>
+          <t>13.00</t>
         </is>
       </c>
       <c r="M42" s="23" t="n"/>
-      <c r="N42" s="22" t="n"/>
+      <c r="N42" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O42" s="23" t="n"/>
       <c r="P42" s="27" t="inlineStr">
         <is>
@@ -3580,44 +4016,61 @@
       <c r="V42" s="23" t="n"/>
     </row>
     <row r="43" ht="114" customHeight="1">
-      <c r="A43" s="25" t="inlineStr">
-        <is>
-          <t>Masapsomboon,Thammasak,Mr</t>
+      <c r="A43" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Thammasak Masapsomboon</t>
         </is>
       </c>
       <c r="B43" s="23" t="n"/>
-      <c r="C43" s="7" t="n"/>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D43" s="24" t="inlineStr">
         <is>
           <t>1302</t>
         </is>
       </c>
       <c r="E43" s="23" t="n"/>
-      <c r="F43" s="24" t="n"/>
+      <c r="F43" s="24" t="inlineStr">
+        <is>
+          <t>VIPG
+SILVER</t>
+        </is>
+      </c>
       <c r="G43" s="23" t="n"/>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2+1</t>
         </is>
       </c>
       <c r="I43" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J43" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K43" s="8" t="n"/>
-      <c r="L43" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K43" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L43" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M43" s="23" t="n"/>
-      <c r="N43" s="22" t="n"/>
+      <c r="N43" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O43" s="23" t="n"/>
       <c r="P43" s="27" t="inlineStr">
         <is>
@@ -3632,44 +4085,61 @@
       <c r="V43" s="23" t="n"/>
     </row>
     <row r="44" ht="114" customHeight="1">
-      <c r="A44" s="25" t="inlineStr">
-        <is>
-          <t>Yaemkanchoo,Sawadee,Mrs</t>
+      <c r="A44" s="93" t="inlineStr">
+        <is>
+          <t>Mrs. Sawadee Yaemkanchoo</t>
         </is>
       </c>
       <c r="B44" s="23" t="n"/>
-      <c r="C44" s="7" t="n"/>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D44" s="24" t="inlineStr">
         <is>
           <t>1304</t>
         </is>
       </c>
       <c r="E44" s="23" t="n"/>
-      <c r="F44" s="24" t="n"/>
+      <c r="F44" s="24" t="inlineStr">
+        <is>
+          <t>VIPG
+SILVER</t>
+        </is>
+      </c>
       <c r="G44" s="23" t="n"/>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2+1</t>
         </is>
       </c>
       <c r="I44" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J44" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K44" s="8" t="n"/>
-      <c r="L44" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K44" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L44" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M44" s="23" t="n"/>
-      <c r="N44" s="22" t="n"/>
+      <c r="N44" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O44" s="23" t="n"/>
       <c r="P44" s="27" t="inlineStr">
         <is>
@@ -3695,20 +4165,28 @@
       <c r="V44" s="23" t="n"/>
     </row>
     <row r="45" ht="114" customHeight="1">
-      <c r="A45" s="25" t="inlineStr">
-        <is>
-          <t>Khumrak,Jitsopin,Mrs</t>
+      <c r="A45" s="93" t="inlineStr">
+        <is>
+          <t>Mrs. Jitsopin Khumrak</t>
         </is>
       </c>
       <c r="B45" s="23" t="n"/>
-      <c r="C45" s="7" t="n"/>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D45" s="24" t="inlineStr">
         <is>
           <t>1305</t>
         </is>
       </c>
       <c r="E45" s="23" t="n"/>
-      <c r="F45" s="24" t="n"/>
+      <c r="F45" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G45" s="23" t="n"/>
       <c r="H45" s="8" t="inlineStr">
         <is>
@@ -3717,22 +4195,30 @@
       </c>
       <c r="I45" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J45" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K45" s="8" t="n"/>
-      <c r="L45" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K45" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L45" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M45" s="23" t="n"/>
-      <c r="N45" s="22" t="n"/>
+      <c r="N45" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O45" s="23" t="n"/>
       <c r="P45" s="27" t="inlineStr">
         <is>
@@ -3755,44 +4241,60 @@
       <c r="V45" s="23" t="n"/>
     </row>
     <row r="46" ht="114" customHeight="1">
-      <c r="A46" s="25" t="inlineStr">
-        <is>
-          <t>Khumrak,Jitsopin,Mrs</t>
+      <c r="A46" s="93" t="inlineStr">
+        <is>
+          <t>Mrs. Jitsopin Khumrak</t>
         </is>
       </c>
       <c r="B46" s="23" t="n"/>
-      <c r="C46" s="7" t="n"/>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D46" s="24" t="inlineStr">
         <is>
           <t>1306</t>
         </is>
       </c>
       <c r="E46" s="23" t="n"/>
-      <c r="F46" s="24" t="n"/>
+      <c r="F46" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G46" s="23" t="n"/>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2+2</t>
         </is>
       </c>
       <c r="I46" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J46" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K46" s="8" t="n"/>
-      <c r="L46" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K46" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L46" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M46" s="23" t="n"/>
-      <c r="N46" s="22" t="n"/>
+      <c r="N46" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O46" s="23" t="n"/>
       <c r="P46" s="27" t="inlineStr">
         <is>
@@ -3815,44 +4317,60 @@
       <c r="V46" s="23" t="n"/>
     </row>
     <row r="47" ht="114" customHeight="1">
-      <c r="A47" s="25" t="inlineStr">
-        <is>
-          <t>Khumrak,Jitsopin,Mrs</t>
+      <c r="A47" s="93" t="inlineStr">
+        <is>
+          <t>Mrs. Jitsopin Khumrak</t>
         </is>
       </c>
       <c r="B47" s="23" t="n"/>
-      <c r="C47" s="7" t="n"/>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D47" s="24" t="inlineStr">
         <is>
           <t>1307</t>
         </is>
       </c>
       <c r="E47" s="23" t="n"/>
-      <c r="F47" s="24" t="n"/>
+      <c r="F47" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G47" s="23" t="n"/>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2+2</t>
         </is>
       </c>
       <c r="I47" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J47" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K47" s="8" t="n"/>
-      <c r="L47" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K47" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L47" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M47" s="23" t="n"/>
-      <c r="N47" s="22" t="n"/>
+      <c r="N47" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O47" s="23" t="n"/>
       <c r="P47" s="27" t="inlineStr">
         <is>
@@ -3874,44 +4392,60 @@
       <c r="V47" s="23" t="n"/>
     </row>
     <row r="48" ht="114" customHeight="1">
-      <c r="A48" s="25" t="inlineStr">
-        <is>
-          <t>Khumrak,Jitsopin,Mrs</t>
+      <c r="A48" s="93" t="inlineStr">
+        <is>
+          <t>Mrs. Jitsopin Khumrak</t>
         </is>
       </c>
       <c r="B48" s="23" t="n"/>
-      <c r="C48" s="7" t="n"/>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D48" s="24" t="inlineStr">
         <is>
           <t>1308</t>
         </is>
       </c>
       <c r="E48" s="23" t="n"/>
-      <c r="F48" s="24" t="n"/>
+      <c r="F48" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G48" s="23" t="n"/>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2+2</t>
         </is>
       </c>
       <c r="I48" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J48" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K48" s="8" t="n"/>
-      <c r="L48" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K48" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L48" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M48" s="23" t="n"/>
-      <c r="N48" s="22" t="n"/>
+      <c r="N48" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O48" s="23" t="n"/>
       <c r="P48" s="27" t="inlineStr">
         <is>
@@ -3934,20 +4468,28 @@
       <c r="V48" s="23" t="n"/>
     </row>
     <row r="49" ht="114" customHeight="1">
-      <c r="A49" s="25" t="inlineStr">
-        <is>
-          <t>Khumrak,Jitsopin,Mrs</t>
+      <c r="A49" s="93" t="inlineStr">
+        <is>
+          <t>Mrs. Jitsopin Khumrak</t>
         </is>
       </c>
       <c r="B49" s="23" t="n"/>
-      <c r="C49" s="7" t="n"/>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D49" s="24" t="inlineStr">
         <is>
           <t>1309</t>
         </is>
       </c>
       <c r="E49" s="23" t="n"/>
-      <c r="F49" s="24" t="n"/>
+      <c r="F49" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G49" s="23" t="n"/>
       <c r="H49" s="8" t="inlineStr">
         <is>
@@ -3956,22 +4498,30 @@
       </c>
       <c r="I49" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J49" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K49" s="8" t="n"/>
-      <c r="L49" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K49" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M49" s="23" t="n"/>
-      <c r="N49" s="22" t="n"/>
+      <c r="N49" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O49" s="23" t="n"/>
       <c r="P49" s="27" t="inlineStr">
         <is>
@@ -3993,44 +4543,61 @@
       <c r="V49" s="23" t="n"/>
     </row>
     <row r="50" ht="114" customHeight="1">
-      <c r="A50" s="25" t="inlineStr">
-        <is>
-          <t>Soladtenko,Nataliia,Mrs</t>
+      <c r="A50" s="93" t="inlineStr">
+        <is>
+          <t>Mrs. Nataliia Soladtenko</t>
         </is>
       </c>
       <c r="B50" s="23" t="n"/>
-      <c r="C50" s="7" t="n"/>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D50" s="24" t="inlineStr">
         <is>
           <t>1314</t>
         </is>
       </c>
       <c r="E50" s="23" t="n"/>
-      <c r="F50" s="24" t="n"/>
+      <c r="F50" s="24" t="inlineStr">
+        <is>
+          <t>VIPG
+SILVER</t>
+        </is>
+      </c>
       <c r="G50" s="23" t="n"/>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1+2</t>
         </is>
       </c>
       <c r="I50" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J50" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K50" s="8" t="n"/>
-      <c r="L50" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K50" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L50" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M50" s="23" t="n"/>
-      <c r="N50" s="22" t="n"/>
+      <c r="N50" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O50" s="23" t="n"/>
       <c r="P50" s="27" t="inlineStr">
         <is>
@@ -4053,20 +4620,28 @@
       <c r="V50" s="23" t="n"/>
     </row>
     <row r="51" ht="114" customHeight="1">
-      <c r="A51" s="25" t="inlineStr">
-        <is>
-          <t>Ekpinijpittya,Nittaya,Ms</t>
+      <c r="A51" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Nittaya Ekpinijpittya</t>
         </is>
       </c>
       <c r="B51" s="23" t="n"/>
-      <c r="C51" s="7" t="n"/>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D51" s="24" t="inlineStr">
         <is>
           <t>1417</t>
         </is>
       </c>
       <c r="E51" s="23" t="n"/>
-      <c r="F51" s="24" t="n"/>
+      <c r="F51" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G51" s="23" t="n"/>
       <c r="H51" s="8" t="inlineStr">
         <is>
@@ -4075,22 +4650,30 @@
       </c>
       <c r="I51" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J51" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K51" s="8" t="n"/>
-      <c r="L51" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K51" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M51" s="23" t="n"/>
-      <c r="N51" s="22" t="n"/>
+      <c r="N51" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O51" s="23" t="n"/>
       <c r="P51" s="27" t="inlineStr">
         <is>
@@ -4113,20 +4696,28 @@
       <c r="V51" s="23" t="n"/>
     </row>
     <row r="52" ht="114" customHeight="1">
-      <c r="A52" s="25" t="inlineStr">
-        <is>
-          <t>Ekpinijpittya,Nittaya,Ms</t>
+      <c r="A52" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Nittaya Ekpinijpittya</t>
         </is>
       </c>
       <c r="B52" s="23" t="n"/>
-      <c r="C52" s="7" t="n"/>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D52" s="24" t="inlineStr">
         <is>
           <t>1418</t>
         </is>
       </c>
       <c r="E52" s="23" t="n"/>
-      <c r="F52" s="24" t="n"/>
+      <c r="F52" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G52" s="23" t="n"/>
       <c r="H52" s="8" t="inlineStr">
         <is>
@@ -4135,22 +4726,30 @@
       </c>
       <c r="I52" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J52" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K52" s="8" t="n"/>
-      <c r="L52" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K52" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L52" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M52" s="23" t="n"/>
-      <c r="N52" s="22" t="n"/>
+      <c r="N52" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O52" s="23" t="n"/>
       <c r="P52" s="27" t="inlineStr">
         <is>
@@ -4173,20 +4772,28 @@
       <c r="V52" s="23" t="n"/>
     </row>
     <row r="53" ht="114" customHeight="1">
-      <c r="A53" s="25" t="inlineStr">
-        <is>
-          <t>Ekpinijpittya,Nittaya,Ms</t>
+      <c r="A53" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Nittaya Ekpinijpittya</t>
         </is>
       </c>
       <c r="B53" s="23" t="n"/>
-      <c r="C53" s="7" t="n"/>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D53" s="24" t="inlineStr">
         <is>
           <t>1419</t>
         </is>
       </c>
       <c r="E53" s="23" t="n"/>
-      <c r="F53" s="24" t="n"/>
+      <c r="F53" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G53" s="23" t="n"/>
       <c r="H53" s="8" t="inlineStr">
         <is>
@@ -4195,22 +4802,30 @@
       </c>
       <c r="I53" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J53" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K53" s="8" t="n"/>
-      <c r="L53" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K53" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L53" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M53" s="23" t="n"/>
-      <c r="N53" s="22" t="n"/>
+      <c r="N53" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O53" s="23" t="n"/>
       <c r="P53" s="27" t="inlineStr">
         <is>
@@ -4233,44 +4848,60 @@
       <c r="V53" s="23" t="n"/>
     </row>
     <row r="54" ht="114" customHeight="1">
-      <c r="A54" s="25" t="inlineStr">
-        <is>
-          <t>Pattanee,Atthaphon,Mr</t>
+      <c r="A54" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Atthaphon Pattanee</t>
         </is>
       </c>
       <c r="B54" s="23" t="n"/>
-      <c r="C54" s="7" t="n"/>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D54" s="24" t="inlineStr">
         <is>
           <t>1420</t>
         </is>
       </c>
       <c r="E54" s="23" t="n"/>
-      <c r="F54" s="24" t="n"/>
+      <c r="F54" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G54" s="23" t="n"/>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2+1</t>
         </is>
       </c>
       <c r="I54" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J54" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K54" s="8" t="n"/>
-      <c r="L54" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K54" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L54" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M54" s="23" t="n"/>
-      <c r="N54" s="22" t="n"/>
+      <c r="N54" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O54" s="23" t="n"/>
       <c r="P54" s="27" t="inlineStr">
         <is>
@@ -4292,44 +4923,60 @@
       <c r="V54" s="23" t="n"/>
     </row>
     <row r="55" ht="114" customHeight="1">
-      <c r="A55" s="25" t="inlineStr">
-        <is>
-          <t>Krohlek,Amornrat,Mrs</t>
+      <c r="A55" s="93" t="inlineStr">
+        <is>
+          <t>Mrs. Amornrat Krohlek</t>
         </is>
       </c>
       <c r="B55" s="23" t="n"/>
-      <c r="C55" s="7" t="n"/>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D55" s="24" t="inlineStr">
         <is>
           <t>1421</t>
         </is>
       </c>
       <c r="E55" s="23" t="n"/>
-      <c r="F55" s="24" t="n"/>
+      <c r="F55" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G55" s="23" t="n"/>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2+1</t>
         </is>
       </c>
       <c r="I55" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J55" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K55" s="8" t="n"/>
-      <c r="L55" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K55" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M55" s="23" t="n"/>
-      <c r="N55" s="22" t="n"/>
+      <c r="N55" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O55" s="23" t="n"/>
       <c r="P55" s="27" t="inlineStr">
         <is>
@@ -4351,20 +4998,28 @@
       <c r="V55" s="23" t="n"/>
     </row>
     <row r="56" ht="114" customHeight="1">
-      <c r="A56" s="25" t="inlineStr">
-        <is>
-          <t>Krolek,Umaree,Ms</t>
+      <c r="A56" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Umaree Krolek</t>
         </is>
       </c>
       <c r="B56" s="23" t="n"/>
-      <c r="C56" s="7" t="n"/>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D56" s="24" t="inlineStr">
         <is>
           <t>1422</t>
         </is>
       </c>
       <c r="E56" s="23" t="n"/>
-      <c r="F56" s="24" t="n"/>
+      <c r="F56" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G56" s="23" t="n"/>
       <c r="H56" s="8" t="inlineStr">
         <is>
@@ -4373,22 +5028,30 @@
       </c>
       <c r="I56" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J56" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K56" s="8" t="n"/>
-      <c r="L56" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K56" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L56" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M56" s="23" t="n"/>
-      <c r="N56" s="22" t="n"/>
+      <c r="N56" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O56" s="23" t="n"/>
       <c r="P56" s="27" t="inlineStr">
         <is>
@@ -4409,20 +5072,28 @@
       <c r="V56" s="23" t="n"/>
     </row>
     <row r="57" ht="114" customHeight="1">
-      <c r="A57" s="25" t="inlineStr">
-        <is>
-          <t>Bunkrai,Aumarin,Ms</t>
+      <c r="A57" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Aumarin Bunkrai</t>
         </is>
       </c>
       <c r="B57" s="23" t="n"/>
-      <c r="C57" s="7" t="n"/>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D57" s="24" t="inlineStr">
         <is>
           <t>1425</t>
         </is>
       </c>
       <c r="E57" s="23" t="n"/>
-      <c r="F57" s="24" t="n"/>
+      <c r="F57" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G57" s="23" t="n"/>
       <c r="H57" s="8" t="inlineStr">
         <is>
@@ -4431,22 +5102,30 @@
       </c>
       <c r="I57" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J57" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K57" s="8" t="n"/>
-      <c r="L57" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K57" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M57" s="23" t="n"/>
-      <c r="N57" s="22" t="n"/>
+      <c r="N57" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O57" s="23" t="n"/>
       <c r="P57" s="27" t="inlineStr">
         <is>
@@ -4466,13 +5145,17 @@
       <c r="V57" s="23" t="n"/>
     </row>
     <row r="58" ht="114" customHeight="1">
-      <c r="A58" s="25" t="inlineStr">
-        <is>
-          <t>Lee,Yoo Seung,Mrs</t>
+      <c r="A58" s="93" t="inlineStr">
+        <is>
+          <t>Mrs. Yoo Seung Lee</t>
         </is>
       </c>
       <c r="B58" s="23" t="n"/>
-      <c r="C58" s="7" t="n"/>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D58" s="24" t="inlineStr">
         <is>
           <t>1510</t>
@@ -4481,33 +5164,42 @@
       <c r="E58" s="23" t="n"/>
       <c r="F58" s="24" t="inlineStr">
         <is>
-          <t>VIPO</t>
+          <t>VIPO
+SILVER</t>
         </is>
       </c>
       <c r="G58" s="23" t="n"/>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2+1</t>
         </is>
       </c>
       <c r="I58" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J58" s="9" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
-        </is>
-      </c>
-      <c r="K58" s="8" t="n"/>
-      <c r="L58" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>29/07/26</t>
+        </is>
+      </c>
+      <c r="K58" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L58" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M58" s="23" t="n"/>
-      <c r="N58" s="22" t="n"/>
+      <c r="N58" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O58" s="23" t="n"/>
       <c r="P58" s="27" t="inlineStr">
         <is>
@@ -4532,13 +5224,17 @@
       <c r="V58" s="23" t="n"/>
     </row>
     <row r="59" ht="114" customHeight="1">
-      <c r="A59" s="25" t="inlineStr">
-        <is>
-          <t>Visutharumanee,Suvadee,Ms</t>
+      <c r="A59" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Suvadee Visutharumanee</t>
         </is>
       </c>
       <c r="B59" s="23" t="n"/>
-      <c r="C59" s="7" t="n"/>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D59" s="24" t="inlineStr">
         <is>
           <t>1511</t>
@@ -4553,27 +5249,35 @@
       <c r="G59" s="23" t="n"/>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2+1</t>
         </is>
       </c>
       <c r="I59" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J59" s="9" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
-        </is>
-      </c>
-      <c r="K59" s="8" t="n"/>
-      <c r="L59" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>28/07/26</t>
+        </is>
+      </c>
+      <c r="K59" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M59" s="23" t="n"/>
-      <c r="N59" s="22" t="n"/>
+      <c r="N59" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O59" s="23" t="n"/>
       <c r="P59" s="27" t="inlineStr">
         <is>
@@ -4594,13 +5298,17 @@
       <c r="V59" s="23" t="n"/>
     </row>
     <row r="60" ht="114" customHeight="1">
-      <c r="A60" s="25" t="inlineStr">
-        <is>
-          <t>Zou,Rongrong,Mr</t>
+      <c r="A60" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Rongrong Zou</t>
         </is>
       </c>
       <c r="B60" s="23" t="n"/>
-      <c r="C60" s="7" t="n"/>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D60" s="24" t="inlineStr">
         <is>
           <t>1513</t>
@@ -4620,22 +5328,30 @@
       </c>
       <c r="I60" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J60" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K60" s="8" t="n"/>
-      <c r="L60" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K60" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L60" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M60" s="23" t="n"/>
-      <c r="N60" s="22" t="n"/>
+      <c r="N60" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O60" s="23" t="n"/>
       <c r="P60" s="27" t="inlineStr">
         <is>
@@ -4658,20 +5374,28 @@
       <c r="V60" s="23" t="n"/>
     </row>
     <row r="61" ht="114" customHeight="1">
-      <c r="A61" s="25" t="inlineStr">
-        <is>
-          <t>Suwannarat,Nanticha,Ms</t>
+      <c r="A61" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Nanticha Suwannarat</t>
         </is>
       </c>
       <c r="B61" s="23" t="n"/>
-      <c r="C61" s="7" t="n"/>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D61" s="24" t="inlineStr">
         <is>
           <t>1514</t>
         </is>
       </c>
       <c r="E61" s="23" t="n"/>
-      <c r="F61" s="24" t="n"/>
+      <c r="F61" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G61" s="23" t="n"/>
       <c r="H61" s="8" t="inlineStr">
         <is>
@@ -4680,22 +5404,30 @@
       </c>
       <c r="I61" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J61" s="9" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
-        </is>
-      </c>
-      <c r="K61" s="8" t="n"/>
-      <c r="L61" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>27/07/26</t>
+        </is>
+      </c>
+      <c r="K61" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M61" s="23" t="n"/>
-      <c r="N61" s="22" t="n"/>
+      <c r="N61" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O61" s="23" t="n"/>
       <c r="P61" s="27" t="inlineStr">
         <is>
@@ -4714,20 +5446,28 @@
       <c r="V61" s="23" t="n"/>
     </row>
     <row r="62" ht="114" customHeight="1">
-      <c r="A62" s="25" t="inlineStr">
-        <is>
-          <t>Suwannarat,Nanticha,Ms</t>
+      <c r="A62" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Nanticha Suwannarat</t>
         </is>
       </c>
       <c r="B62" s="23" t="n"/>
-      <c r="C62" s="7" t="n"/>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D62" s="24" t="inlineStr">
         <is>
           <t>1515</t>
         </is>
       </c>
       <c r="E62" s="23" t="n"/>
-      <c r="F62" s="24" t="n"/>
+      <c r="F62" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G62" s="23" t="n"/>
       <c r="H62" s="8" t="inlineStr">
         <is>
@@ -4736,22 +5476,30 @@
       </c>
       <c r="I62" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J62" s="9" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
-        </is>
-      </c>
-      <c r="K62" s="8" t="n"/>
-      <c r="L62" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>27/07/26</t>
+        </is>
+      </c>
+      <c r="K62" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L62" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M62" s="23" t="n"/>
-      <c r="N62" s="22" t="n"/>
+      <c r="N62" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O62" s="23" t="n"/>
       <c r="P62" s="27" t="inlineStr">
         <is>
@@ -4770,20 +5518,28 @@
       <c r="V62" s="23" t="n"/>
     </row>
     <row r="63" ht="114" customHeight="1">
-      <c r="A63" s="25" t="inlineStr">
-        <is>
-          <t>Suwannarat,Nanticha,Ms</t>
+      <c r="A63" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Nanticha Suwannarat</t>
         </is>
       </c>
       <c r="B63" s="23" t="n"/>
-      <c r="C63" s="7" t="n"/>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D63" s="24" t="inlineStr">
         <is>
           <t>1516</t>
         </is>
       </c>
       <c r="E63" s="23" t="n"/>
-      <c r="F63" s="24" t="n"/>
+      <c r="F63" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G63" s="23" t="n"/>
       <c r="H63" s="8" t="inlineStr">
         <is>
@@ -4792,22 +5548,30 @@
       </c>
       <c r="I63" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J63" s="9" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
-        </is>
-      </c>
-      <c r="K63" s="8" t="n"/>
-      <c r="L63" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>27/07/26</t>
+        </is>
+      </c>
+      <c r="K63" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L63" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M63" s="23" t="n"/>
-      <c r="N63" s="22" t="n"/>
+      <c r="N63" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O63" s="23" t="n"/>
       <c r="P63" s="27" t="inlineStr">
         <is>
@@ -4826,20 +5590,28 @@
       <c r="V63" s="23" t="n"/>
     </row>
     <row r="64" ht="114" customHeight="1">
-      <c r="A64" s="25" t="inlineStr">
-        <is>
-          <t>Suwannarat,Nanticha,Ms</t>
+      <c r="A64" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Nanticha Suwannarat</t>
         </is>
       </c>
       <c r="B64" s="23" t="n"/>
-      <c r="C64" s="7" t="n"/>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D64" s="24" t="inlineStr">
         <is>
           <t>1517</t>
         </is>
       </c>
       <c r="E64" s="23" t="n"/>
-      <c r="F64" s="24" t="n"/>
+      <c r="F64" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G64" s="23" t="n"/>
       <c r="H64" s="8" t="inlineStr">
         <is>
@@ -4848,22 +5620,30 @@
       </c>
       <c r="I64" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J64" s="9" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
-        </is>
-      </c>
-      <c r="K64" s="8" t="n"/>
-      <c r="L64" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>27/07/26</t>
+        </is>
+      </c>
+      <c r="K64" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L64" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M64" s="23" t="n"/>
-      <c r="N64" s="22" t="n"/>
+      <c r="N64" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O64" s="23" t="n"/>
       <c r="P64" s="27" t="inlineStr">
         <is>
@@ -4882,20 +5662,28 @@
       <c r="V64" s="23" t="n"/>
     </row>
     <row r="65" ht="114" customHeight="1">
-      <c r="A65" s="25" t="inlineStr">
-        <is>
-          <t>Wiboonsabtawee,Anusak,Mr</t>
+      <c r="A65" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Anusak Wiboonsabtawee</t>
         </is>
       </c>
       <c r="B65" s="23" t="n"/>
-      <c r="C65" s="7" t="n"/>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D65" s="24" t="inlineStr">
         <is>
           <t>1601</t>
         </is>
       </c>
       <c r="E65" s="23" t="n"/>
-      <c r="F65" s="24" t="n"/>
+      <c r="F65" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G65" s="23" t="n"/>
       <c r="H65" s="8" t="inlineStr">
         <is>
@@ -4904,22 +5692,30 @@
       </c>
       <c r="I65" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J65" s="9" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
-        </is>
-      </c>
-      <c r="K65" s="8" t="n"/>
-      <c r="L65" s="31" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>28/07/26</t>
+        </is>
+      </c>
+      <c r="K65" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L65" s="94" t="inlineStr">
+        <is>
+          <t>18.00</t>
         </is>
       </c>
       <c r="M65" s="23" t="n"/>
-      <c r="N65" s="22" t="n"/>
+      <c r="N65" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O65" s="23" t="n"/>
       <c r="P65" s="27" t="inlineStr">
         <is>
@@ -4934,13 +5730,17 @@
       <c r="V65" s="23" t="n"/>
     </row>
     <row r="66" ht="114" customHeight="1">
-      <c r="A66" s="25" t="inlineStr">
-        <is>
-          <t>Tutsiexusakoon,Apinya,Ms</t>
+      <c r="A66" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Apinya Tutsiexusakoon</t>
         </is>
       </c>
       <c r="B66" s="23" t="n"/>
-      <c r="C66" s="7" t="n"/>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D66" s="24" t="inlineStr">
         <is>
           <t>1605</t>
@@ -4955,27 +5755,35 @@
       <c r="G66" s="23" t="n"/>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2+1</t>
         </is>
       </c>
       <c r="I66" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J66" s="9" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
-        </is>
-      </c>
-      <c r="K66" s="8" t="n"/>
-      <c r="L66" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>28/07/26</t>
+        </is>
+      </c>
+      <c r="K66" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L66" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M66" s="23" t="n"/>
-      <c r="N66" s="22" t="n"/>
+      <c r="N66" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O66" s="23" t="n"/>
       <c r="P66" s="27" t="inlineStr">
         <is>
@@ -4996,20 +5804,28 @@
       <c r="V66" s="23" t="n"/>
     </row>
     <row r="67" ht="114" customHeight="1">
-      <c r="A67" s="25" t="inlineStr">
-        <is>
-          <t>Zaltsman,Chanika,Mrs</t>
+      <c r="A67" s="93" t="inlineStr">
+        <is>
+          <t>Mrs. Chanika Zaltsman</t>
         </is>
       </c>
       <c r="B67" s="23" t="n"/>
-      <c r="C67" s="7" t="n"/>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D67" s="24" t="inlineStr">
         <is>
           <t>1606</t>
         </is>
       </c>
       <c r="E67" s="23" t="n"/>
-      <c r="F67" s="24" t="n"/>
+      <c r="F67" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G67" s="23" t="n"/>
       <c r="H67" s="8" t="inlineStr">
         <is>
@@ -5018,22 +5834,30 @@
       </c>
       <c r="I67" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J67" s="9" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
-        </is>
-      </c>
-      <c r="K67" s="8" t="n"/>
-      <c r="L67" s="31" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>28/07/26</t>
+        </is>
+      </c>
+      <c r="K67" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" s="94" t="inlineStr">
+        <is>
+          <t>14.30</t>
         </is>
       </c>
       <c r="M67" s="23" t="n"/>
-      <c r="N67" s="22" t="n"/>
+      <c r="N67" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O67" s="23" t="n"/>
       <c r="P67" s="27" t="inlineStr">
         <is>
@@ -5048,20 +5872,28 @@
       <c r="V67" s="23" t="n"/>
     </row>
     <row r="68" ht="114" customHeight="1">
-      <c r="A68" s="25" t="inlineStr">
-        <is>
-          <t>Jutiboot,Nantida,Ms</t>
+      <c r="A68" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Nantida Jutiboot</t>
         </is>
       </c>
       <c r="B68" s="23" t="n"/>
-      <c r="C68" s="7" t="n"/>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D68" s="24" t="inlineStr">
         <is>
           <t>1611</t>
         </is>
       </c>
       <c r="E68" s="23" t="n"/>
-      <c r="F68" s="24" t="n"/>
+      <c r="F68" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G68" s="23" t="n"/>
       <c r="H68" s="8" t="inlineStr">
         <is>
@@ -5070,22 +5902,30 @@
       </c>
       <c r="I68" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J68" s="9" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
-        </is>
-      </c>
-      <c r="K68" s="8" t="n"/>
-      <c r="L68" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>27/07/26</t>
+        </is>
+      </c>
+      <c r="K68" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L68" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M68" s="23" t="n"/>
-      <c r="N68" s="22" t="n"/>
+      <c r="N68" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O68" s="23" t="n"/>
       <c r="P68" s="27" t="inlineStr">
         <is>
@@ -5100,44 +5940,61 @@
       <c r="V68" s="23" t="n"/>
     </row>
     <row r="69" ht="114" customHeight="1">
-      <c r="A69" s="25" t="inlineStr">
-        <is>
-          <t>Kawai,Sayuri,Mrs</t>
+      <c r="A69" s="93" t="inlineStr">
+        <is>
+          <t>Mrs. Sayuri Kawai</t>
         </is>
       </c>
       <c r="B69" s="23" t="n"/>
-      <c r="C69" s="7" t="n"/>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D69" s="24" t="inlineStr">
         <is>
           <t>1621</t>
         </is>
       </c>
       <c r="E69" s="23" t="n"/>
-      <c r="F69" s="24" t="n"/>
+      <c r="F69" s="24" t="inlineStr">
+        <is>
+          <t>VIPG
+SILVER</t>
+        </is>
+      </c>
       <c r="G69" s="23" t="n"/>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2+1</t>
         </is>
       </c>
       <c r="I69" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J69" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K69" s="8" t="n"/>
-      <c r="L69" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K69" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L69" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M69" s="23" t="n"/>
-      <c r="N69" s="22" t="n"/>
+      <c r="N69" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O69" s="23" t="n"/>
       <c r="P69" s="27" t="inlineStr">
         <is>
@@ -5162,13 +6019,17 @@
       <c r="V69" s="23" t="n"/>
     </row>
     <row r="70" ht="114" customHeight="1">
-      <c r="A70" s="25" t="inlineStr">
-        <is>
-          <t>Sartyaem,Phanuphong,Mr</t>
+      <c r="A70" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Phanuphong Sartyaem</t>
         </is>
       </c>
       <c r="B70" s="23" t="n"/>
-      <c r="C70" s="7" t="n"/>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D70" s="24" t="inlineStr">
         <is>
           <t>2102</t>
@@ -5177,33 +6038,42 @@
       <c r="E70" s="23" t="n"/>
       <c r="F70" s="24" t="inlineStr">
         <is>
-          <t>VIP2</t>
+          <t>VIP2
+TITANIUM</t>
         </is>
       </c>
       <c r="G70" s="23" t="n"/>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2+1</t>
         </is>
       </c>
       <c r="I70" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J70" s="9" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
-        </is>
-      </c>
-      <c r="K70" s="8" t="n"/>
-      <c r="L70" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>27/07/26</t>
+        </is>
+      </c>
+      <c r="K70" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L70" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M70" s="23" t="n"/>
-      <c r="N70" s="22" t="n"/>
+      <c r="N70" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O70" s="23" t="n"/>
       <c r="P70" s="27" t="inlineStr">
         <is>
@@ -5228,13 +6098,17 @@
       <c r="V70" s="23" t="n"/>
     </row>
     <row r="71" ht="114" customHeight="1">
-      <c r="A71" s="25" t="inlineStr">
-        <is>
-          <t>Sartyaem,Phanuphong,Mr</t>
+      <c r="A71" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Phanuphong Sartyaem</t>
         </is>
       </c>
       <c r="B71" s="23" t="n"/>
-      <c r="C71" s="7" t="n"/>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D71" s="24" t="inlineStr">
         <is>
           <t>2103</t>
@@ -5243,33 +6117,42 @@
       <c r="E71" s="23" t="n"/>
       <c r="F71" s="24" t="inlineStr">
         <is>
-          <t>VIP2</t>
+          <t>VIP2
+TITANIUM</t>
         </is>
       </c>
       <c r="G71" s="23" t="n"/>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2+1</t>
         </is>
       </c>
       <c r="I71" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J71" s="9" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
-        </is>
-      </c>
-      <c r="K71" s="8" t="n"/>
-      <c r="L71" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>27/07/26</t>
+        </is>
+      </c>
+      <c r="K71" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L71" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M71" s="23" t="n"/>
-      <c r="N71" s="22" t="n"/>
+      <c r="N71" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O71" s="23" t="n"/>
       <c r="P71" s="27" t="inlineStr">
         <is>
@@ -5294,13 +6177,17 @@
       <c r="V71" s="23" t="n"/>
     </row>
     <row r="72" ht="114" customHeight="1">
-      <c r="A72" s="25" t="inlineStr">
-        <is>
-          <t>Sartyaem,Phanuphong,Mr</t>
+      <c r="A72" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Phanuphong Sartyaem</t>
         </is>
       </c>
       <c r="B72" s="23" t="n"/>
-      <c r="C72" s="7" t="n"/>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D72" s="24" t="inlineStr">
         <is>
           <t>2104</t>
@@ -5309,7 +6196,8 @@
       <c r="E72" s="23" t="n"/>
       <c r="F72" s="24" t="inlineStr">
         <is>
-          <t>VIP2</t>
+          <t>VIP2
+TITANIUM</t>
         </is>
       </c>
       <c r="G72" s="23" t="n"/>
@@ -5320,22 +6208,30 @@
       </c>
       <c r="I72" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J72" s="9" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
-        </is>
-      </c>
-      <c r="K72" s="8" t="n"/>
-      <c r="L72" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>27/07/26</t>
+        </is>
+      </c>
+      <c r="K72" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L72" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M72" s="23" t="n"/>
-      <c r="N72" s="22" t="n"/>
+      <c r="N72" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O72" s="23" t="n"/>
       <c r="P72" s="27" t="inlineStr">
         <is>
@@ -5359,13 +6255,17 @@
       <c r="V72" s="23" t="n"/>
     </row>
     <row r="73" ht="114" customHeight="1">
-      <c r="A73" s="25" t="inlineStr">
-        <is>
-          <t>Sartyaem,Phanuphong,Mr</t>
+      <c r="A73" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Phanuphong Sartyaem</t>
         </is>
       </c>
       <c r="B73" s="23" t="n"/>
-      <c r="C73" s="7" t="n"/>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D73" s="24" t="inlineStr">
         <is>
           <t>2105</t>
@@ -5374,7 +6274,8 @@
       <c r="E73" s="23" t="n"/>
       <c r="F73" s="24" t="inlineStr">
         <is>
-          <t>VIP2</t>
+          <t>VIP2
+TITANIUM</t>
         </is>
       </c>
       <c r="G73" s="23" t="n"/>
@@ -5385,22 +6286,30 @@
       </c>
       <c r="I73" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J73" s="9" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
-        </is>
-      </c>
-      <c r="K73" s="8" t="n"/>
-      <c r="L73" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>27/07/26</t>
+        </is>
+      </c>
+      <c r="K73" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L73" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M73" s="23" t="n"/>
-      <c r="N73" s="22" t="n"/>
+      <c r="N73" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O73" s="23" t="n"/>
       <c r="P73" s="27" t="inlineStr">
         <is>
@@ -5424,13 +6333,17 @@
       <c r="V73" s="23" t="n"/>
     </row>
     <row r="74" ht="114" customHeight="1">
-      <c r="A74" s="25" t="inlineStr">
-        <is>
-          <t>Sartyaem,Phanuphong,Mr</t>
+      <c r="A74" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Phanuphong Sartyaem</t>
         </is>
       </c>
       <c r="B74" s="23" t="n"/>
-      <c r="C74" s="7" t="n"/>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D74" s="24" t="inlineStr">
         <is>
           <t>2106</t>
@@ -5439,33 +6352,42 @@
       <c r="E74" s="23" t="n"/>
       <c r="F74" s="24" t="inlineStr">
         <is>
-          <t>VIP2</t>
+          <t>VIP2
+TITANIUM</t>
         </is>
       </c>
       <c r="G74" s="23" t="n"/>
       <c r="H74" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2+1</t>
         </is>
       </c>
       <c r="I74" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J74" s="9" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
-        </is>
-      </c>
-      <c r="K74" s="8" t="n"/>
-      <c r="L74" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>27/07/26</t>
+        </is>
+      </c>
+      <c r="K74" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L74" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M74" s="23" t="n"/>
-      <c r="N74" s="22" t="n"/>
+      <c r="N74" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O74" s="23" t="n"/>
       <c r="P74" s="27" t="inlineStr">
         <is>
@@ -5490,44 +6412,60 @@
       <c r="V74" s="23" t="n"/>
     </row>
     <row r="75" ht="114" customHeight="1">
-      <c r="A75" s="25" t="inlineStr">
-        <is>
-          <t>Preechanonda,Busabong,Ms</t>
+      <c r="A75" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Busabong Preechanonda</t>
         </is>
       </c>
       <c r="B75" s="23" t="n"/>
-      <c r="C75" s="7" t="n"/>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D75" s="24" t="inlineStr">
         <is>
           <t>2113</t>
         </is>
       </c>
       <c r="E75" s="23" t="n"/>
-      <c r="F75" s="24" t="n"/>
+      <c r="F75" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G75" s="23" t="n"/>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2+1</t>
         </is>
       </c>
       <c r="I75" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J75" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K75" s="8" t="n"/>
-      <c r="L75" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K75" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L75" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M75" s="23" t="n"/>
-      <c r="N75" s="22" t="n"/>
+      <c r="N75" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O75" s="23" t="n"/>
       <c r="P75" s="27" t="inlineStr">
         <is>
@@ -5546,20 +6484,28 @@
       <c r="V75" s="23" t="n"/>
     </row>
     <row r="76" ht="114" customHeight="1">
-      <c r="A76" s="25" t="inlineStr">
-        <is>
-          <t>Achiha,Motoki,Mr</t>
+      <c r="A76" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Motoki Achiha</t>
         </is>
       </c>
       <c r="B76" s="23" t="n"/>
-      <c r="C76" s="7" t="n"/>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D76" s="24" t="inlineStr">
         <is>
           <t>2201</t>
         </is>
       </c>
       <c r="E76" s="23" t="n"/>
-      <c r="F76" s="24" t="n"/>
+      <c r="F76" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G76" s="23" t="n"/>
       <c r="H76" s="8" t="inlineStr">
         <is>
@@ -5568,22 +6514,30 @@
       </c>
       <c r="I76" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J76" s="9" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
-        </is>
-      </c>
-      <c r="K76" s="8" t="n"/>
-      <c r="L76" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>27/07/26</t>
+        </is>
+      </c>
+      <c r="K76" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L76" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M76" s="23" t="n"/>
-      <c r="N76" s="22" t="n"/>
+      <c r="N76" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O76" s="23" t="n"/>
       <c r="P76" s="27" t="inlineStr">
         <is>
@@ -5599,20 +6553,29 @@
       <c r="V76" s="23" t="n"/>
     </row>
     <row r="77" ht="114" customHeight="1">
-      <c r="A77" s="25" t="inlineStr">
-        <is>
-          <t>Khabipova,Landysh,Ms</t>
+      <c r="A77" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Landysh Khabipova</t>
         </is>
       </c>
       <c r="B77" s="23" t="n"/>
-      <c r="C77" s="7" t="n"/>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D77" s="24" t="inlineStr">
         <is>
           <t>2202</t>
         </is>
       </c>
       <c r="E77" s="23" t="n"/>
-      <c r="F77" s="24" t="n"/>
+      <c r="F77" s="24" t="inlineStr">
+        <is>
+          <t>VIPG
+SILVER</t>
+        </is>
+      </c>
       <c r="G77" s="23" t="n"/>
       <c r="H77" s="8" t="inlineStr">
         <is>
@@ -5621,22 +6584,30 @@
       </c>
       <c r="I77" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J77" s="9" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
-        </is>
-      </c>
-      <c r="K77" s="8" t="n"/>
-      <c r="L77" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>28/07/26</t>
+        </is>
+      </c>
+      <c r="K77" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M77" s="23" t="n"/>
-      <c r="N77" s="22" t="n"/>
+      <c r="N77" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O77" s="23" t="n"/>
       <c r="P77" s="27" t="inlineStr">
         <is>
@@ -5661,20 +6632,29 @@
       <c r="V77" s="23" t="n"/>
     </row>
     <row r="78" ht="114" customHeight="1">
-      <c r="A78" s="25" t="inlineStr">
-        <is>
-          <t>Khabipova,Landysh,Ms</t>
+      <c r="A78" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Landysh Khabipova</t>
         </is>
       </c>
       <c r="B78" s="23" t="n"/>
-      <c r="C78" s="7" t="n"/>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D78" s="24" t="inlineStr">
         <is>
           <t>2203</t>
         </is>
       </c>
       <c r="E78" s="23" t="n"/>
-      <c r="F78" s="24" t="n"/>
+      <c r="F78" s="24" t="inlineStr">
+        <is>
+          <t>VIPG
+SILVER</t>
+        </is>
+      </c>
       <c r="G78" s="23" t="n"/>
       <c r="H78" s="8" t="inlineStr">
         <is>
@@ -5683,22 +6663,30 @@
       </c>
       <c r="I78" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J78" s="9" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
-        </is>
-      </c>
-      <c r="K78" s="8" t="n"/>
-      <c r="L78" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>28/07/26</t>
+        </is>
+      </c>
+      <c r="K78" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L78" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M78" s="23" t="n"/>
-      <c r="N78" s="22" t="n"/>
+      <c r="N78" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O78" s="23" t="n"/>
       <c r="P78" s="27" t="inlineStr">
         <is>
@@ -5722,20 +6710,29 @@
       <c r="V78" s="23" t="n"/>
     </row>
     <row r="79" ht="114" customHeight="1">
-      <c r="A79" s="25" t="inlineStr">
-        <is>
-          <t>Khabipova,Landysh,Ms</t>
+      <c r="A79" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Landysh Khabipova</t>
         </is>
       </c>
       <c r="B79" s="23" t="n"/>
-      <c r="C79" s="7" t="n"/>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D79" s="24" t="inlineStr">
         <is>
           <t>2204</t>
         </is>
       </c>
       <c r="E79" s="23" t="n"/>
-      <c r="F79" s="24" t="n"/>
+      <c r="F79" s="24" t="inlineStr">
+        <is>
+          <t>VIPG
+SILVER</t>
+        </is>
+      </c>
       <c r="G79" s="23" t="n"/>
       <c r="H79" s="8" t="inlineStr">
         <is>
@@ -5744,22 +6741,30 @@
       </c>
       <c r="I79" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J79" s="9" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
-        </is>
-      </c>
-      <c r="K79" s="8" t="n"/>
-      <c r="L79" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>28/07/26</t>
+        </is>
+      </c>
+      <c r="K79" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L79" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M79" s="23" t="n"/>
-      <c r="N79" s="22" t="n"/>
+      <c r="N79" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O79" s="23" t="n"/>
       <c r="P79" s="27" t="inlineStr">
         <is>
@@ -5783,20 +6788,28 @@
       <c r="V79" s="23" t="n"/>
     </row>
     <row r="80" ht="114" customHeight="1">
-      <c r="A80" s="25" t="inlineStr">
-        <is>
-          <t>Audomthongkon,Patcharin,Ms</t>
+      <c r="A80" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Patcharin Audomthongkon</t>
         </is>
       </c>
       <c r="B80" s="23" t="n"/>
-      <c r="C80" s="7" t="n"/>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D80" s="24" t="inlineStr">
         <is>
           <t>2206</t>
         </is>
       </c>
       <c r="E80" s="23" t="n"/>
-      <c r="F80" s="24" t="n"/>
+      <c r="F80" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G80" s="23" t="n"/>
       <c r="H80" s="8" t="inlineStr">
         <is>
@@ -5805,22 +6818,30 @@
       </c>
       <c r="I80" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J80" s="9" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
-        </is>
-      </c>
-      <c r="K80" s="8" t="n"/>
-      <c r="L80" s="31" t="inlineStr">
-        <is>
-          <t>11:10</t>
+          <t>28/07/26</t>
+        </is>
+      </c>
+      <c r="K80" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L80" s="94" t="inlineStr">
+        <is>
+          <t>11.10</t>
         </is>
       </c>
       <c r="M80" s="23" t="n"/>
-      <c r="N80" s="22" t="n"/>
+      <c r="N80" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O80" s="23" t="n"/>
       <c r="P80" s="27" t="inlineStr">
         <is>
@@ -5836,13 +6857,17 @@
       <c r="V80" s="23" t="n"/>
     </row>
     <row r="81" ht="114" customHeight="1">
-      <c r="A81" s="25" t="inlineStr">
-        <is>
-          <t>Suslina,Elena,Mrs</t>
+      <c r="A81" s="93" t="inlineStr">
+        <is>
+          <t>Mrs. Elena Suslina</t>
         </is>
       </c>
       <c r="B81" s="23" t="n"/>
-      <c r="C81" s="7" t="n"/>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D81" s="24" t="inlineStr">
         <is>
           <t>2207</t>
@@ -5851,7 +6876,8 @@
       <c r="E81" s="23" t="n"/>
       <c r="F81" s="24" t="inlineStr">
         <is>
-          <t>VIPS</t>
+          <t>VIPS
+SILVER</t>
         </is>
       </c>
       <c r="G81" s="23" t="n"/>
@@ -5862,22 +6888,30 @@
       </c>
       <c r="I81" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J81" s="9" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
-        </is>
-      </c>
-      <c r="K81" s="8" t="n"/>
-      <c r="L81" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>27/07/26</t>
+        </is>
+      </c>
+      <c r="K81" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L81" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M81" s="23" t="n"/>
-      <c r="N81" s="22" t="n"/>
+      <c r="N81" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O81" s="23" t="n"/>
       <c r="P81" s="27" t="inlineStr">
         <is>
@@ -5896,20 +6930,28 @@
       <c r="V81" s="23" t="n"/>
     </row>
     <row r="82" ht="114" customHeight="1">
-      <c r="A82" s="25" t="inlineStr">
-        <is>
-          <t>Saisangthong,Suphachoke,Mr</t>
+      <c r="A82" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Suphachoke Saisangthong</t>
         </is>
       </c>
       <c r="B82" s="23" t="n"/>
-      <c r="C82" s="7" t="n"/>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D82" s="24" t="inlineStr">
         <is>
           <t>2208</t>
         </is>
       </c>
       <c r="E82" s="23" t="n"/>
-      <c r="F82" s="24" t="n"/>
+      <c r="F82" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G82" s="23" t="n"/>
       <c r="H82" s="8" t="inlineStr">
         <is>
@@ -5918,18 +6960,30 @@
       </c>
       <c r="I82" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J82" s="9" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
-        </is>
-      </c>
-      <c r="K82" s="8" t="n"/>
-      <c r="L82" s="31" t="n"/>
+          <t>29/07/26</t>
+        </is>
+      </c>
+      <c r="K82" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L82" s="50" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
       <c r="M82" s="23" t="n"/>
-      <c r="N82" s="22" t="n"/>
+      <c r="N82" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O82" s="23" t="n"/>
       <c r="P82" s="27" t="inlineStr">
         <is>
@@ -5952,44 +7006,60 @@
       <c r="V82" s="23" t="n"/>
     </row>
     <row r="83" ht="114" customHeight="1">
-      <c r="A83" s="25" t="inlineStr">
-        <is>
-          <t>Midey,Nattha,Mrs</t>
+      <c r="A83" s="93" t="inlineStr">
+        <is>
+          <t>Mrs. Nattha Midey</t>
         </is>
       </c>
       <c r="B83" s="23" t="n"/>
-      <c r="C83" s="7" t="n"/>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D83" s="24" t="inlineStr">
         <is>
           <t>2210</t>
         </is>
       </c>
       <c r="E83" s="23" t="n"/>
-      <c r="F83" s="24" t="n"/>
+      <c r="F83" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G83" s="23" t="n"/>
       <c r="H83" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2+1</t>
         </is>
       </c>
       <c r="I83" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J83" s="9" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
-        </is>
-      </c>
-      <c r="K83" s="8" t="n"/>
-      <c r="L83" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>29/07/26</t>
+        </is>
+      </c>
+      <c r="K83" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M83" s="23" t="n"/>
-      <c r="N83" s="22" t="n"/>
+      <c r="N83" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O83" s="23" t="n"/>
       <c r="P83" s="27" t="inlineStr">
         <is>
@@ -6013,20 +7083,29 @@
       <c r="V83" s="23" t="n"/>
     </row>
     <row r="84" ht="114" customHeight="1">
-      <c r="A84" s="25" t="inlineStr">
-        <is>
-          <t>Lertsirisathaporn,Benjawan,Miss</t>
+      <c r="A84" s="93" t="inlineStr">
+        <is>
+          <t>Miss. Benjawan Lertsirisathaporn</t>
         </is>
       </c>
       <c r="B84" s="23" t="n"/>
-      <c r="C84" s="7" t="n"/>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D84" s="24" t="inlineStr">
         <is>
           <t>2212</t>
         </is>
       </c>
       <c r="E84" s="23" t="n"/>
-      <c r="F84" s="24" t="n"/>
+      <c r="F84" s="24" t="inlineStr">
+        <is>
+          <t>VIPG
+SILVER</t>
+        </is>
+      </c>
       <c r="G84" s="23" t="n"/>
       <c r="H84" s="8" t="inlineStr">
         <is>
@@ -6035,22 +7114,30 @@
       </c>
       <c r="I84" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J84" s="9" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
-        </is>
-      </c>
-      <c r="K84" s="8" t="n"/>
-      <c r="L84" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>28/07/26</t>
+        </is>
+      </c>
+      <c r="K84" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L84" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M84" s="23" t="n"/>
-      <c r="N84" s="22" t="n"/>
+      <c r="N84" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O84" s="23" t="n"/>
       <c r="P84" s="27" t="inlineStr">
         <is>
@@ -6073,20 +7160,29 @@
       <c r="V84" s="23" t="n"/>
     </row>
     <row r="85" ht="114" customHeight="1">
-      <c r="A85" s="25" t="inlineStr">
-        <is>
-          <t>Lertsirisathaporn,Benjawan,Miss</t>
+      <c r="A85" s="93" t="inlineStr">
+        <is>
+          <t>Miss. Benjawan Lertsirisathaporn</t>
         </is>
       </c>
       <c r="B85" s="23" t="n"/>
-      <c r="C85" s="7" t="n"/>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D85" s="24" t="inlineStr">
         <is>
           <t>2213</t>
         </is>
       </c>
       <c r="E85" s="23" t="n"/>
-      <c r="F85" s="24" t="n"/>
+      <c r="F85" s="24" t="inlineStr">
+        <is>
+          <t>VIPG
+SILVER</t>
+        </is>
+      </c>
       <c r="G85" s="23" t="n"/>
       <c r="H85" s="8" t="inlineStr">
         <is>
@@ -6095,22 +7191,30 @@
       </c>
       <c r="I85" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J85" s="9" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
-        </is>
-      </c>
-      <c r="K85" s="8" t="n"/>
-      <c r="L85" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>28/07/26</t>
+        </is>
+      </c>
+      <c r="K85" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M85" s="23" t="n"/>
-      <c r="N85" s="22" t="n"/>
+      <c r="N85" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O85" s="23" t="n"/>
       <c r="P85" s="27" t="inlineStr">
         <is>
@@ -6125,44 +7229,61 @@
       <c r="V85" s="23" t="n"/>
     </row>
     <row r="86" ht="114" customHeight="1">
-      <c r="A86" s="25" t="inlineStr">
-        <is>
-          <t>Carfati,Shirley,Mrs</t>
+      <c r="A86" s="93" t="inlineStr">
+        <is>
+          <t>Mrs. Shirley Carfati</t>
         </is>
       </c>
       <c r="B86" s="23" t="n"/>
-      <c r="C86" s="7" t="n"/>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D86" s="24" t="inlineStr">
         <is>
           <t>2301</t>
         </is>
       </c>
       <c r="E86" s="23" t="n"/>
-      <c r="F86" s="24" t="n"/>
+      <c r="F86" s="24" t="inlineStr">
+        <is>
+          <t>VIPG
+SILVER</t>
+        </is>
+      </c>
       <c r="G86" s="23" t="n"/>
       <c r="H86" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2+1</t>
         </is>
       </c>
       <c r="I86" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J86" s="9" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
-        </is>
-      </c>
-      <c r="K86" s="8" t="n"/>
-      <c r="L86" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>28/07/26</t>
+        </is>
+      </c>
+      <c r="K86" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L86" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M86" s="23" t="n"/>
-      <c r="N86" s="22" t="n"/>
+      <c r="N86" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O86" s="23" t="n"/>
       <c r="P86" s="27" t="inlineStr">
         <is>
@@ -6182,44 +7303,60 @@
       <c r="V86" s="23" t="n"/>
     </row>
     <row r="87" ht="114" customHeight="1">
-      <c r="A87" s="25" t="inlineStr">
-        <is>
-          <t>Nontakarn,Matuwan,Ms</t>
+      <c r="A87" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Matuwan Nontakarn</t>
         </is>
       </c>
       <c r="B87" s="23" t="n"/>
-      <c r="C87" s="7" t="n"/>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D87" s="24" t="inlineStr">
         <is>
           <t>2304</t>
         </is>
       </c>
       <c r="E87" s="23" t="n"/>
-      <c r="F87" s="24" t="n"/>
+      <c r="F87" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G87" s="23" t="n"/>
       <c r="H87" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2+1</t>
         </is>
       </c>
       <c r="I87" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J87" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K87" s="8" t="n"/>
-      <c r="L87" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K87" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L87" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M87" s="23" t="n"/>
-      <c r="N87" s="22" t="n"/>
+      <c r="N87" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O87" s="23" t="n"/>
       <c r="P87" s="27" t="inlineStr">
         <is>
@@ -6241,20 +7378,28 @@
       <c r="V87" s="23" t="n"/>
     </row>
     <row r="88" ht="114" customHeight="1">
-      <c r="A88" s="25" t="inlineStr">
-        <is>
-          <t>Nontakarn,Matuwan,Ms</t>
+      <c r="A88" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Matuwan Nontakarn</t>
         </is>
       </c>
       <c r="B88" s="23" t="n"/>
-      <c r="C88" s="7" t="n"/>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D88" s="24" t="inlineStr">
         <is>
           <t>2305</t>
         </is>
       </c>
       <c r="E88" s="23" t="n"/>
-      <c r="F88" s="24" t="n"/>
+      <c r="F88" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G88" s="23" t="n"/>
       <c r="H88" s="8" t="inlineStr">
         <is>
@@ -6263,22 +7408,30 @@
       </c>
       <c r="I88" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J88" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K88" s="8" t="n"/>
-      <c r="L88" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K88" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L88" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M88" s="23" t="n"/>
-      <c r="N88" s="22" t="n"/>
+      <c r="N88" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O88" s="23" t="n"/>
       <c r="P88" s="27" t="inlineStr">
         <is>
@@ -6299,13 +7452,17 @@
       <c r="V88" s="23" t="n"/>
     </row>
     <row r="89" ht="114" customHeight="1">
-      <c r="A89" s="25" t="inlineStr">
-        <is>
-          <t>Nomkran,Sarochar,Ms</t>
+      <c r="A89" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Sarochar Nomkran</t>
         </is>
       </c>
       <c r="B89" s="23" t="n"/>
-      <c r="C89" s="7" t="n"/>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D89" s="24" t="inlineStr">
         <is>
           <t>2306</t>
@@ -6325,22 +7482,30 @@
       </c>
       <c r="I89" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J89" s="9" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
-        </is>
-      </c>
-      <c r="K89" s="8" t="n"/>
-      <c r="L89" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>27/07/26</t>
+        </is>
+      </c>
+      <c r="K89" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L89" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M89" s="23" t="n"/>
-      <c r="N89" s="22" t="n"/>
+      <c r="N89" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O89" s="23" t="n"/>
       <c r="P89" s="27" t="inlineStr">
         <is>
@@ -6359,20 +7524,28 @@
       <c r="V89" s="23" t="n"/>
     </row>
     <row r="90" ht="114" customHeight="1">
-      <c r="A90" s="25" t="inlineStr">
-        <is>
-          <t>Jiansiri,Wohranuch,Ms</t>
+      <c r="A90" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Wohranuch Jiansiri</t>
         </is>
       </c>
       <c r="B90" s="23" t="n"/>
-      <c r="C90" s="7" t="n"/>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D90" s="24" t="inlineStr">
         <is>
           <t>2307</t>
         </is>
       </c>
       <c r="E90" s="23" t="n"/>
-      <c r="F90" s="24" t="n"/>
+      <c r="F90" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G90" s="23" t="n"/>
       <c r="H90" s="8" t="inlineStr">
         <is>
@@ -6381,22 +7554,30 @@
       </c>
       <c r="I90" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J90" s="9" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
-        </is>
-      </c>
-      <c r="K90" s="8" t="n"/>
-      <c r="L90" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>27/07/26</t>
+        </is>
+      </c>
+      <c r="K90" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L90" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M90" s="23" t="n"/>
-      <c r="N90" s="22" t="n"/>
+      <c r="N90" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O90" s="23" t="n"/>
       <c r="P90" s="27" t="inlineStr">
         <is>
@@ -6415,44 +7596,61 @@
       <c r="V90" s="23" t="n"/>
     </row>
     <row r="91" ht="114" customHeight="1">
-      <c r="A91" s="25" t="inlineStr">
-        <is>
-          <t>Panpuch,Watchara,Mr</t>
+      <c r="A91" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Watchara Panpuch</t>
         </is>
       </c>
       <c r="B91" s="23" t="n"/>
-      <c r="C91" s="7" t="n"/>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D91" s="24" t="inlineStr">
         <is>
           <t>2308</t>
         </is>
       </c>
       <c r="E91" s="23" t="n"/>
-      <c r="F91" s="24" t="n"/>
+      <c r="F91" s="24" t="inlineStr">
+        <is>
+          <t>VIPG
+SILVER</t>
+        </is>
+      </c>
       <c r="G91" s="23" t="n"/>
       <c r="H91" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2+1</t>
         </is>
       </c>
       <c r="I91" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J91" s="9" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
-        </is>
-      </c>
-      <c r="K91" s="8" t="n"/>
-      <c r="L91" s="31" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>27/07/26</t>
+        </is>
+      </c>
+      <c r="K91" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="94" t="inlineStr">
+        <is>
+          <t>14.00</t>
         </is>
       </c>
       <c r="M91" s="23" t="n"/>
-      <c r="N91" s="22" t="n"/>
+      <c r="N91" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O91" s="23" t="n"/>
       <c r="P91" s="27" t="inlineStr">
         <is>
@@ -6476,44 +7674,61 @@
       <c r="V91" s="23" t="n"/>
     </row>
     <row r="92" ht="114" customHeight="1">
-      <c r="A92" s="25" t="inlineStr">
-        <is>
-          <t>Panpuch,Watchara,Mr</t>
+      <c r="A92" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Watchara Panpuch</t>
         </is>
       </c>
       <c r="B92" s="23" t="n"/>
-      <c r="C92" s="7" t="n"/>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D92" s="24" t="inlineStr">
         <is>
           <t>2309</t>
         </is>
       </c>
       <c r="E92" s="23" t="n"/>
-      <c r="F92" s="24" t="n"/>
+      <c r="F92" s="24" t="inlineStr">
+        <is>
+          <t>VIPG
+SILVER</t>
+        </is>
+      </c>
       <c r="G92" s="23" t="n"/>
       <c r="H92" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2+1</t>
         </is>
       </c>
       <c r="I92" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J92" s="9" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
-        </is>
-      </c>
-      <c r="K92" s="8" t="n"/>
-      <c r="L92" s="31" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>27/07/26</t>
+        </is>
+      </c>
+      <c r="K92" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L92" s="94" t="inlineStr">
+        <is>
+          <t>14.00</t>
         </is>
       </c>
       <c r="M92" s="23" t="n"/>
-      <c r="N92" s="22" t="n"/>
+      <c r="N92" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O92" s="23" t="n"/>
       <c r="P92" s="27" t="inlineStr">
         <is>
@@ -6537,44 +7752,60 @@
       <c r="V92" s="23" t="n"/>
     </row>
     <row r="93" ht="114" customHeight="1">
-      <c r="A93" s="25" t="inlineStr">
-        <is>
-          <t>Belanis,Sharon,Ms</t>
+      <c r="A93" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Sharon Belanis</t>
         </is>
       </c>
       <c r="B93" s="23" t="n"/>
-      <c r="C93" s="7" t="n"/>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D93" s="24" t="inlineStr">
         <is>
           <t>2310</t>
         </is>
       </c>
       <c r="E93" s="23" t="n"/>
-      <c r="F93" s="24" t="n"/>
+      <c r="F93" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G93" s="23" t="n"/>
       <c r="H93" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1+1</t>
         </is>
       </c>
       <c r="I93" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J93" s="9" t="inlineStr">
         <is>
-          <t>01-AUG-26</t>
-        </is>
-      </c>
-      <c r="K93" s="8" t="n"/>
-      <c r="L93" s="31" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>01/08/26</t>
+        </is>
+      </c>
+      <c r="K93" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L93" s="94" t="inlineStr">
+        <is>
+          <t>14.00</t>
         </is>
       </c>
       <c r="M93" s="23" t="n"/>
-      <c r="N93" s="22" t="n"/>
+      <c r="N93" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O93" s="23" t="n"/>
       <c r="P93" s="27" t="inlineStr">
         <is>
@@ -6592,13 +7823,17 @@
       <c r="V93" s="23" t="n"/>
     </row>
     <row r="94" ht="114" customHeight="1">
-      <c r="A94" s="25" t="inlineStr">
-        <is>
-          <t>Pradubsriphet,Chaowit,Mr</t>
+      <c r="A94" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Chaowit Pradubsriphet</t>
         </is>
       </c>
       <c r="B94" s="23" t="n"/>
-      <c r="C94" s="7" t="n"/>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D94" s="24" t="inlineStr">
         <is>
           <t>2311</t>
@@ -6607,33 +7842,42 @@
       <c r="E94" s="23" t="n"/>
       <c r="F94" s="24" t="inlineStr">
         <is>
-          <t>VIPR</t>
+          <t>VIPR
+GOLD</t>
         </is>
       </c>
       <c r="G94" s="23" t="n"/>
       <c r="H94" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2+2</t>
         </is>
       </c>
       <c r="I94" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J94" s="9" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
-        </is>
-      </c>
-      <c r="K94" s="8" t="n"/>
-      <c r="L94" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>28/07/26</t>
+        </is>
+      </c>
+      <c r="K94" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L94" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M94" s="23" t="n"/>
-      <c r="N94" s="22" t="n"/>
+      <c r="N94" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O94" s="23" t="n"/>
       <c r="P94" s="27" t="inlineStr">
         <is>
@@ -6657,13 +7901,17 @@
       <c r="V94" s="23" t="n"/>
     </row>
     <row r="95" ht="114" customHeight="1">
-      <c r="A95" s="25" t="inlineStr">
-        <is>
-          <t>Rohde,Andreas,Mr</t>
+      <c r="A95" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Andreas Rohde</t>
         </is>
       </c>
       <c r="B95" s="23" t="n"/>
-      <c r="C95" s="7" t="n"/>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D95" s="24" t="inlineStr">
         <is>
           <t>2312</t>
@@ -6678,27 +7926,35 @@
       <c r="G95" s="23" t="n"/>
       <c r="H95" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2+1</t>
         </is>
       </c>
       <c r="I95" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J95" s="9" t="inlineStr">
         <is>
-          <t>09-AUG-26</t>
-        </is>
-      </c>
-      <c r="K95" s="8" t="n"/>
-      <c r="L95" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>09/08/26</t>
+        </is>
+      </c>
+      <c r="K95" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L95" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M95" s="23" t="n"/>
-      <c r="N95" s="22" t="n"/>
+      <c r="N95" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O95" s="23" t="n"/>
       <c r="P95" s="27" t="inlineStr">
         <is>
@@ -6715,20 +7971,28 @@
       <c r="V95" s="23" t="n"/>
     </row>
     <row r="96" ht="114" customHeight="1">
-      <c r="A96" s="25" t="inlineStr">
-        <is>
-          <t>Suryahudaya,Della Laurencia,Ms</t>
+      <c r="A96" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Della Laurencia Suryahudaya</t>
         </is>
       </c>
       <c r="B96" s="23" t="n"/>
-      <c r="C96" s="7" t="n"/>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D96" s="24" t="inlineStr">
         <is>
           <t>2313</t>
         </is>
       </c>
       <c r="E96" s="23" t="n"/>
-      <c r="F96" s="24" t="n"/>
+      <c r="F96" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G96" s="23" t="n"/>
       <c r="H96" s="8" t="inlineStr">
         <is>
@@ -6737,22 +8001,30 @@
       </c>
       <c r="I96" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J96" s="9" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
-        </is>
-      </c>
-      <c r="K96" s="8" t="n"/>
-      <c r="L96" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>27/07/26</t>
+        </is>
+      </c>
+      <c r="K96" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L96" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M96" s="23" t="n"/>
-      <c r="N96" s="22" t="n"/>
+      <c r="N96" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O96" s="23" t="n"/>
       <c r="P96" s="27" t="inlineStr">
         <is>
@@ -6769,44 +8041,61 @@
       <c r="V96" s="23" t="n"/>
     </row>
     <row r="97" ht="114" customHeight="1">
-      <c r="A97" s="25" t="inlineStr">
-        <is>
-          <t>Carfati,Shirley,Mrs</t>
+      <c r="A97" s="93" t="inlineStr">
+        <is>
+          <t>Mrs. Shirley Carfati</t>
         </is>
       </c>
       <c r="B97" s="23" t="n"/>
-      <c r="C97" s="7" t="n"/>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D97" s="24" t="inlineStr">
         <is>
           <t>2314</t>
         </is>
       </c>
       <c r="E97" s="23" t="n"/>
-      <c r="F97" s="24" t="n"/>
+      <c r="F97" s="24" t="inlineStr">
+        <is>
+          <t>VIPG
+SILVER</t>
+        </is>
+      </c>
       <c r="G97" s="23" t="n"/>
       <c r="H97" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2+1</t>
         </is>
       </c>
       <c r="I97" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J97" s="9" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
-        </is>
-      </c>
-      <c r="K97" s="8" t="n"/>
-      <c r="L97" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>28/07/26</t>
+        </is>
+      </c>
+      <c r="K97" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M97" s="23" t="n"/>
-      <c r="N97" s="22" t="n"/>
+      <c r="N97" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O97" s="23" t="n"/>
       <c r="P97" s="27" t="inlineStr">
         <is>
@@ -6821,20 +8110,28 @@
       <c r="V97" s="23" t="n"/>
     </row>
     <row r="98" ht="114" customHeight="1">
-      <c r="A98" s="25" t="inlineStr">
-        <is>
-          <t>Immaneerat,Sunanta,Mrs</t>
+      <c r="A98" s="93" t="inlineStr">
+        <is>
+          <t>Mrs. Sunanta Immaneerat</t>
         </is>
       </c>
       <c r="B98" s="23" t="n"/>
-      <c r="C98" s="7" t="n"/>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D98" s="24" t="inlineStr">
         <is>
           <t>2405</t>
         </is>
       </c>
       <c r="E98" s="23" t="n"/>
-      <c r="F98" s="24" t="n"/>
+      <c r="F98" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G98" s="23" t="n"/>
       <c r="H98" s="8" t="inlineStr">
         <is>
@@ -6843,22 +8140,30 @@
       </c>
       <c r="I98" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J98" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K98" s="8" t="n"/>
-      <c r="L98" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K98" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L98" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M98" s="23" t="n"/>
-      <c r="N98" s="22" t="n"/>
+      <c r="N98" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O98" s="23" t="n"/>
       <c r="P98" s="27" t="inlineStr">
         <is>
@@ -6881,20 +8186,28 @@
       <c r="V98" s="23" t="n"/>
     </row>
     <row r="99" ht="114" customHeight="1">
-      <c r="A99" s="25" t="inlineStr">
-        <is>
-          <t>Isayeva,Albina,Ms</t>
+      <c r="A99" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Albina Isayeva</t>
         </is>
       </c>
       <c r="B99" s="23" t="n"/>
-      <c r="C99" s="7" t="n"/>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D99" s="24" t="inlineStr">
         <is>
           <t>2407</t>
         </is>
       </c>
       <c r="E99" s="23" t="n"/>
-      <c r="F99" s="24" t="n"/>
+      <c r="F99" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G99" s="23" t="n"/>
       <c r="H99" s="8" t="inlineStr">
         <is>
@@ -6903,22 +8216,30 @@
       </c>
       <c r="I99" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J99" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K99" s="8" t="n"/>
-      <c r="L99" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K99" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L99" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M99" s="23" t="n"/>
-      <c r="N99" s="22" t="n"/>
+      <c r="N99" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O99" s="23" t="n"/>
       <c r="P99" s="27" t="inlineStr">
         <is>
@@ -6934,20 +8255,29 @@
       <c r="V99" s="23" t="n"/>
     </row>
     <row r="100" ht="114" customHeight="1">
-      <c r="A100" s="25" t="inlineStr">
-        <is>
-          <t>Hongmungkorn,Tinada,Miss</t>
+      <c r="A100" s="93" t="inlineStr">
+        <is>
+          <t>Miss. Tinada Hongmungkorn</t>
         </is>
       </c>
       <c r="B100" s="23" t="n"/>
-      <c r="C100" s="7" t="n"/>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D100" s="24" t="inlineStr">
         <is>
           <t>2408</t>
         </is>
       </c>
       <c r="E100" s="23" t="n"/>
-      <c r="F100" s="24" t="n"/>
+      <c r="F100" s="24" t="inlineStr">
+        <is>
+          <t>VIPG
+SILVER</t>
+        </is>
+      </c>
       <c r="G100" s="23" t="n"/>
       <c r="H100" s="8" t="inlineStr">
         <is>
@@ -6956,22 +8286,30 @@
       </c>
       <c r="I100" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J100" s="9" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
-        </is>
-      </c>
-      <c r="K100" s="8" t="n"/>
-      <c r="L100" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>27/07/26</t>
+        </is>
+      </c>
+      <c r="K100" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L100" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M100" s="23" t="n"/>
-      <c r="N100" s="22" t="n"/>
+      <c r="N100" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O100" s="23" t="n"/>
       <c r="P100" s="27" t="inlineStr">
         <is>
@@ -6993,20 +8331,28 @@
       <c r="V100" s="23" t="n"/>
     </row>
     <row r="101" ht="114" customHeight="1">
-      <c r="A101" s="25" t="inlineStr">
-        <is>
-          <t>Guntatun,Nanaphat,Mr</t>
+      <c r="A101" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Nanaphat Guntatun</t>
         </is>
       </c>
       <c r="B101" s="23" t="n"/>
-      <c r="C101" s="7" t="n"/>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D101" s="24" t="inlineStr">
         <is>
           <t>2506</t>
         </is>
       </c>
       <c r="E101" s="23" t="n"/>
-      <c r="F101" s="24" t="n"/>
+      <c r="F101" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G101" s="23" t="n"/>
       <c r="H101" s="8" t="inlineStr">
         <is>
@@ -7015,22 +8361,30 @@
       </c>
       <c r="I101" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J101" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K101" s="8" t="n"/>
-      <c r="L101" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K101" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L101" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M101" s="23" t="n"/>
-      <c r="N101" s="22" t="n"/>
+      <c r="N101" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O101" s="23" t="n"/>
       <c r="P101" s="27" t="inlineStr">
         <is>
@@ -7048,20 +8402,28 @@
       <c r="V101" s="23" t="n"/>
     </row>
     <row r="102" ht="114" customHeight="1">
-      <c r="A102" s="25" t="inlineStr">
-        <is>
-          <t>Pimsen,Naruemon,Miss</t>
+      <c r="A102" s="93" t="inlineStr">
+        <is>
+          <t>Miss. Naruemon Pimsen</t>
         </is>
       </c>
       <c r="B102" s="23" t="n"/>
-      <c r="C102" s="7" t="n"/>
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D102" s="24" t="inlineStr">
         <is>
           <t>2510</t>
         </is>
       </c>
       <c r="E102" s="23" t="n"/>
-      <c r="F102" s="24" t="n"/>
+      <c r="F102" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G102" s="23" t="n"/>
       <c r="H102" s="8" t="inlineStr">
         <is>
@@ -7070,22 +8432,30 @@
       </c>
       <c r="I102" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J102" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K102" s="8" t="n"/>
-      <c r="L102" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K102" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L102" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M102" s="23" t="n"/>
-      <c r="N102" s="22" t="n"/>
+      <c r="N102" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O102" s="23" t="n"/>
       <c r="P102" s="27" t="inlineStr">
         <is>
@@ -7108,20 +8478,28 @@
       <c r="V102" s="23" t="n"/>
     </row>
     <row r="103" ht="114" customHeight="1">
-      <c r="A103" s="25" t="inlineStr">
-        <is>
-          <t>Kitkusolsab,Watcharamon,Mr</t>
+      <c r="A103" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Watcharamon Kitkusolsab</t>
         </is>
       </c>
       <c r="B103" s="23" t="n"/>
-      <c r="C103" s="7" t="n"/>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D103" s="24" t="inlineStr">
         <is>
           <t>2512</t>
         </is>
       </c>
       <c r="E103" s="23" t="n"/>
-      <c r="F103" s="24" t="n"/>
+      <c r="F103" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G103" s="23" t="n"/>
       <c r="H103" s="8" t="inlineStr">
         <is>
@@ -7130,22 +8508,30 @@
       </c>
       <c r="I103" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J103" s="9" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
-        </is>
-      </c>
-      <c r="K103" s="8" t="n"/>
-      <c r="L103" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>27/07/26</t>
+        </is>
+      </c>
+      <c r="K103" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L103" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M103" s="23" t="n"/>
-      <c r="N103" s="22" t="n"/>
+      <c r="N103" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O103" s="23" t="n"/>
       <c r="P103" s="27" t="inlineStr">
         <is>
@@ -7161,20 +8547,29 @@
       <c r="V103" s="23" t="n"/>
     </row>
     <row r="104" ht="114" customHeight="1">
-      <c r="A104" s="25" t="inlineStr">
-        <is>
-          <t>Hanggasee,Tharit,Mr</t>
+      <c r="A104" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Tharit Hanggasee</t>
         </is>
       </c>
       <c r="B104" s="23" t="n"/>
-      <c r="C104" s="7" t="n"/>
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D104" s="24" t="inlineStr">
         <is>
           <t>2602</t>
         </is>
       </c>
       <c r="E104" s="23" t="n"/>
-      <c r="F104" s="24" t="n"/>
+      <c r="F104" s="24" t="inlineStr">
+        <is>
+          <t>VIPG
+SILVER</t>
+        </is>
+      </c>
       <c r="G104" s="23" t="n"/>
       <c r="H104" s="8" t="inlineStr">
         <is>
@@ -7183,22 +8578,30 @@
       </c>
       <c r="I104" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J104" s="9" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
-        </is>
-      </c>
-      <c r="K104" s="8" t="n"/>
-      <c r="L104" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>28/07/26</t>
+        </is>
+      </c>
+      <c r="K104" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L104" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M104" s="23" t="n"/>
-      <c r="N104" s="22" t="n"/>
+      <c r="N104" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O104" s="23" t="n"/>
       <c r="P104" s="27" t="inlineStr">
         <is>
@@ -7222,20 +8625,28 @@
       <c r="V104" s="23" t="n"/>
     </row>
     <row r="105" ht="114" customHeight="1">
-      <c r="A105" s="25" t="inlineStr">
-        <is>
-          <t>Wongchaigosoh,Panutda,Ms</t>
+      <c r="A105" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Panutda Wongchaigosoh</t>
         </is>
       </c>
       <c r="B105" s="23" t="n"/>
-      <c r="C105" s="7" t="n"/>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D105" s="24" t="inlineStr">
         <is>
           <t>2603</t>
         </is>
       </c>
       <c r="E105" s="23" t="n"/>
-      <c r="F105" s="24" t="n"/>
+      <c r="F105" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G105" s="23" t="n"/>
       <c r="H105" s="8" t="inlineStr">
         <is>
@@ -7244,22 +8655,30 @@
       </c>
       <c r="I105" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J105" s="9" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
-        </is>
-      </c>
-      <c r="K105" s="8" t="n"/>
-      <c r="L105" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>27/07/26</t>
+        </is>
+      </c>
+      <c r="K105" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L105" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M105" s="23" t="n"/>
-      <c r="N105" s="22" t="n"/>
+      <c r="N105" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O105" s="23" t="n"/>
       <c r="P105" s="27" t="inlineStr">
         <is>
@@ -7281,20 +8700,29 @@
       <c r="V105" s="23" t="n"/>
     </row>
     <row r="106" ht="114" customHeight="1">
-      <c r="A106" s="25" t="inlineStr">
-        <is>
-          <t>Chee Meng,Yap,Mr</t>
+      <c r="A106" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Yap Chee Meng</t>
         </is>
       </c>
       <c r="B106" s="23" t="n"/>
-      <c r="C106" s="7" t="n"/>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D106" s="24" t="inlineStr">
         <is>
           <t>2606</t>
         </is>
       </c>
       <c r="E106" s="23" t="n"/>
-      <c r="F106" s="24" t="n"/>
+      <c r="F106" s="24" t="inlineStr">
+        <is>
+          <t>VIPG
+SILVER</t>
+        </is>
+      </c>
       <c r="G106" s="23" t="n"/>
       <c r="H106" s="8" t="inlineStr">
         <is>
@@ -7303,22 +8731,30 @@
       </c>
       <c r="I106" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J106" s="9" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
-        </is>
-      </c>
-      <c r="K106" s="8" t="n"/>
-      <c r="L106" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>27/07/26</t>
+        </is>
+      </c>
+      <c r="K106" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L106" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M106" s="23" t="n"/>
-      <c r="N106" s="22" t="n"/>
+      <c r="N106" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O106" s="23" t="n"/>
       <c r="P106" s="27" t="inlineStr">
         <is>
@@ -7341,20 +8777,28 @@
       <c r="V106" s="23" t="n"/>
     </row>
     <row r="107" ht="114" customHeight="1">
-      <c r="A107" s="25" t="inlineStr">
-        <is>
-          <t>Graham,Pailin,Ms</t>
+      <c r="A107" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Pailin Graham</t>
         </is>
       </c>
       <c r="B107" s="23" t="n"/>
-      <c r="C107" s="7" t="n"/>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D107" s="24" t="inlineStr">
         <is>
           <t>2607</t>
         </is>
       </c>
       <c r="E107" s="23" t="n"/>
-      <c r="F107" s="24" t="n"/>
+      <c r="F107" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G107" s="23" t="n"/>
       <c r="H107" s="8" t="inlineStr">
         <is>
@@ -7363,22 +8807,30 @@
       </c>
       <c r="I107" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J107" s="9" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
-        </is>
-      </c>
-      <c r="K107" s="8" t="n"/>
-      <c r="L107" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>27/07/26</t>
+        </is>
+      </c>
+      <c r="K107" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L107" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M107" s="23" t="n"/>
-      <c r="N107" s="22" t="n"/>
+      <c r="N107" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O107" s="23" t="n"/>
       <c r="P107" s="27" t="inlineStr">
         <is>
@@ -7400,20 +8852,28 @@
       <c r="V107" s="23" t="n"/>
     </row>
     <row r="108" ht="114" customHeight="1">
-      <c r="A108" s="25" t="inlineStr">
-        <is>
-          <t>Graham,Pailin,Ms</t>
+      <c r="A108" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Pailin Graham</t>
         </is>
       </c>
       <c r="B108" s="23" t="n"/>
-      <c r="C108" s="7" t="n"/>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D108" s="24" t="inlineStr">
         <is>
           <t>2608</t>
         </is>
       </c>
       <c r="E108" s="23" t="n"/>
-      <c r="F108" s="24" t="n"/>
+      <c r="F108" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G108" s="23" t="n"/>
       <c r="H108" s="8" t="inlineStr">
         <is>
@@ -7422,22 +8882,30 @@
       </c>
       <c r="I108" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J108" s="9" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
-        </is>
-      </c>
-      <c r="K108" s="8" t="n"/>
-      <c r="L108" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>27/07/26</t>
+        </is>
+      </c>
+      <c r="K108" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L108" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M108" s="23" t="n"/>
-      <c r="N108" s="22" t="n"/>
+      <c r="N108" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O108" s="23" t="n"/>
       <c r="P108" s="27" t="inlineStr">
         <is>
@@ -7459,13 +8927,17 @@
       <c r="V108" s="23" t="n"/>
     </row>
     <row r="109" ht="114" customHeight="1">
-      <c r="A109" s="25" t="inlineStr">
-        <is>
-          <t>Pengkoom,Krisadakorn,Mr</t>
+      <c r="A109" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Krisadakorn Pengkoom</t>
         </is>
       </c>
       <c r="B109" s="23" t="n"/>
-      <c r="C109" s="7" t="n"/>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D109" s="24" t="inlineStr">
         <is>
           <t>3101</t>
@@ -7474,7 +8946,8 @@
       <c r="E109" s="23" t="n"/>
       <c r="F109" s="24" t="inlineStr">
         <is>
-          <t>VIP2</t>
+          <t>VIP2
+TITANIUM</t>
         </is>
       </c>
       <c r="G109" s="23" t="n"/>
@@ -7485,22 +8958,30 @@
       </c>
       <c r="I109" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J109" s="9" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
-        </is>
-      </c>
-      <c r="K109" s="8" t="n"/>
-      <c r="L109" s="31" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>28/07/26</t>
+        </is>
+      </c>
+      <c r="K109" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L109" s="94" t="inlineStr">
+        <is>
+          <t>12.00</t>
         </is>
       </c>
       <c r="M109" s="23" t="n"/>
-      <c r="N109" s="22" t="n"/>
+      <c r="N109" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O109" s="23" t="n"/>
       <c r="P109" s="27" t="inlineStr">
         <is>
@@ -7521,44 +9002,61 @@
       <c r="V109" s="23" t="n"/>
     </row>
     <row r="110" ht="114" customHeight="1">
-      <c r="A110" s="25" t="inlineStr">
-        <is>
-          <t>Joknoi,Jeerana,Ms</t>
+      <c r="A110" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Jeerana Joknoi</t>
         </is>
       </c>
       <c r="B110" s="23" t="n"/>
-      <c r="C110" s="7" t="n"/>
+      <c r="C110" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D110" s="24" t="inlineStr">
         <is>
           <t>3108</t>
         </is>
       </c>
       <c r="E110" s="23" t="n"/>
-      <c r="F110" s="24" t="n"/>
+      <c r="F110" s="24" t="inlineStr">
+        <is>
+          <t>VIPG
+SILVER</t>
+        </is>
+      </c>
       <c r="G110" s="23" t="n"/>
       <c r="H110" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2+1</t>
         </is>
       </c>
       <c r="I110" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J110" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K110" s="8" t="n"/>
-      <c r="L110" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K110" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L110" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M110" s="23" t="n"/>
-      <c r="N110" s="22" t="n"/>
+      <c r="N110" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O110" s="23" t="n"/>
       <c r="P110" s="27" t="inlineStr">
         <is>
@@ -7577,13 +9075,17 @@
       <c r="V110" s="23" t="n"/>
     </row>
     <row r="111" ht="114" customHeight="1">
-      <c r="A111" s="25" t="inlineStr">
-        <is>
-          <t>Shait,Dafna,Ms</t>
+      <c r="A111" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Dafna Shait</t>
         </is>
       </c>
       <c r="B111" s="23" t="n"/>
-      <c r="C111" s="7" t="n"/>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D111" s="24" t="inlineStr">
         <is>
           <t>3109</t>
@@ -7592,7 +9094,8 @@
       <c r="E111" s="23" t="n"/>
       <c r="F111" s="24" t="inlineStr">
         <is>
-          <t>VIPG</t>
+          <t>VIPG
+PLATINUM</t>
         </is>
       </c>
       <c r="G111" s="23" t="n"/>
@@ -7603,22 +9106,30 @@
       </c>
       <c r="I111" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J111" s="9" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
-        </is>
-      </c>
-      <c r="K111" s="8" t="n"/>
-      <c r="L111" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>29/07/26</t>
+        </is>
+      </c>
+      <c r="K111" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L111" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M111" s="23" t="n"/>
-      <c r="N111" s="22" t="n"/>
+      <c r="N111" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O111" s="23" t="n"/>
       <c r="P111" s="27" t="inlineStr">
         <is>
@@ -7642,13 +9153,17 @@
       <c r="V111" s="23" t="n"/>
     </row>
     <row r="112" ht="114" customHeight="1">
-      <c r="A112" s="25" t="inlineStr">
-        <is>
-          <t>Norasetgamol,Pawinee,Ms</t>
+      <c r="A112" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Pawinee Norasetgamol</t>
         </is>
       </c>
       <c r="B112" s="23" t="n"/>
-      <c r="C112" s="7" t="n"/>
+      <c r="C112" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D112" s="24" t="inlineStr">
         <is>
           <t>3111</t>
@@ -7657,7 +9172,8 @@
       <c r="E112" s="23" t="n"/>
       <c r="F112" s="24" t="inlineStr">
         <is>
-          <t>VIP2</t>
+          <t>VIP2
+TITANIUM</t>
         </is>
       </c>
       <c r="G112" s="23" t="n"/>
@@ -7668,22 +9184,30 @@
       </c>
       <c r="I112" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J112" s="9" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
-        </is>
-      </c>
-      <c r="K112" s="8" t="n"/>
-      <c r="L112" s="31" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>27/07/26</t>
+        </is>
+      </c>
+      <c r="K112" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L112" s="94" t="inlineStr">
+        <is>
+          <t>17.00</t>
         </is>
       </c>
       <c r="M112" s="23" t="n"/>
-      <c r="N112" s="22" t="n"/>
+      <c r="N112" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O112" s="23" t="n"/>
       <c r="P112" s="27" t="inlineStr">
         <is>
@@ -7698,20 +9222,28 @@
       <c r="V112" s="23" t="n"/>
     </row>
     <row r="113" ht="114" customHeight="1">
-      <c r="A113" s="25" t="inlineStr">
-        <is>
-          <t>Cohen,Eyal,Mr</t>
+      <c r="A113" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Eyal Cohen</t>
         </is>
       </c>
       <c r="B113" s="23" t="n"/>
-      <c r="C113" s="7" t="n"/>
+      <c r="C113" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D113" s="24" t="inlineStr">
         <is>
           <t>3202</t>
         </is>
       </c>
       <c r="E113" s="23" t="n"/>
-      <c r="F113" s="24" t="n"/>
+      <c r="F113" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G113" s="23" t="n"/>
       <c r="H113" s="8" t="inlineStr">
         <is>
@@ -7720,22 +9252,30 @@
       </c>
       <c r="I113" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J113" s="9" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
-        </is>
-      </c>
-      <c r="K113" s="8" t="n"/>
-      <c r="L113" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>28/07/26</t>
+        </is>
+      </c>
+      <c r="K113" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L113" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M113" s="23" t="n"/>
-      <c r="N113" s="22" t="n"/>
+      <c r="N113" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O113" s="23" t="n"/>
       <c r="P113" s="27" t="inlineStr">
         <is>
@@ -7752,44 +9292,60 @@
       <c r="V113" s="23" t="n"/>
     </row>
     <row r="114" ht="114" customHeight="1">
-      <c r="A114" s="25" t="inlineStr">
-        <is>
-          <t>Cohen,Eyal,Mr</t>
+      <c r="A114" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Eyal Cohen</t>
         </is>
       </c>
       <c r="B114" s="23" t="n"/>
-      <c r="C114" s="7" t="n"/>
+      <c r="C114" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D114" s="24" t="inlineStr">
         <is>
           <t>3203</t>
         </is>
       </c>
       <c r="E114" s="23" t="n"/>
-      <c r="F114" s="24" t="n"/>
+      <c r="F114" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G114" s="23" t="n"/>
       <c r="H114" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2+1</t>
         </is>
       </c>
       <c r="I114" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J114" s="9" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
-        </is>
-      </c>
-      <c r="K114" s="8" t="n"/>
-      <c r="L114" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>28/07/26</t>
+        </is>
+      </c>
+      <c r="K114" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L114" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M114" s="23" t="n"/>
-      <c r="N114" s="22" t="n"/>
+      <c r="N114" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O114" s="23" t="n"/>
       <c r="P114" s="27" t="inlineStr">
         <is>
@@ -7807,20 +9363,28 @@
       <c r="V114" s="23" t="n"/>
     </row>
     <row r="115" ht="114" customHeight="1">
-      <c r="A115" s="25" t="inlineStr">
-        <is>
-          <t>Spencer,Poppy,Ms</t>
+      <c r="A115" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Poppy Spencer</t>
         </is>
       </c>
       <c r="B115" s="23" t="n"/>
-      <c r="C115" s="7" t="n"/>
+      <c r="C115" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D115" s="24" t="inlineStr">
         <is>
           <t>3204</t>
         </is>
       </c>
       <c r="E115" s="23" t="n"/>
-      <c r="F115" s="24" t="n"/>
+      <c r="F115" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G115" s="23" t="n"/>
       <c r="H115" s="8" t="inlineStr">
         <is>
@@ -7829,22 +9393,30 @@
       </c>
       <c r="I115" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J115" s="9" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
-        </is>
-      </c>
-      <c r="K115" s="8" t="n"/>
-      <c r="L115" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>31/07/26</t>
+        </is>
+      </c>
+      <c r="K115" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L115" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M115" s="23" t="n"/>
-      <c r="N115" s="22" t="n"/>
+      <c r="N115" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O115" s="23" t="n"/>
       <c r="P115" s="27" t="inlineStr">
         <is>
@@ -7862,20 +9434,28 @@
       <c r="V115" s="23" t="n"/>
     </row>
     <row r="116" ht="114" customHeight="1">
-      <c r="A116" s="25" t="inlineStr">
-        <is>
-          <t>Spencer,Louise,Mr</t>
+      <c r="A116" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Louise Spencer</t>
         </is>
       </c>
       <c r="B116" s="23" t="n"/>
-      <c r="C116" s="7" t="n"/>
+      <c r="C116" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D116" s="24" t="inlineStr">
         <is>
           <t>3205</t>
         </is>
       </c>
       <c r="E116" s="23" t="n"/>
-      <c r="F116" s="24" t="n"/>
+      <c r="F116" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G116" s="23" t="n"/>
       <c r="H116" s="8" t="inlineStr">
         <is>
@@ -7884,22 +9464,30 @@
       </c>
       <c r="I116" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J116" s="9" t="inlineStr">
         <is>
-          <t>31-JUL-26</t>
-        </is>
-      </c>
-      <c r="K116" s="8" t="n"/>
-      <c r="L116" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>31/07/26</t>
+        </is>
+      </c>
+      <c r="K116" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L116" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M116" s="23" t="n"/>
-      <c r="N116" s="22" t="n"/>
+      <c r="N116" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O116" s="23" t="n"/>
       <c r="P116" s="27" t="inlineStr">
         <is>
@@ -7916,13 +9504,17 @@
       <c r="V116" s="23" t="n"/>
     </row>
     <row r="117" ht="114" customHeight="1">
-      <c r="A117" s="25" t="inlineStr">
-        <is>
-          <t>Ajsamart,Amonrat,Ms</t>
+      <c r="A117" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Amonrat Ajsamart</t>
         </is>
       </c>
       <c r="B117" s="23" t="n"/>
-      <c r="C117" s="7" t="n"/>
+      <c r="C117" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D117" s="24" t="inlineStr">
         <is>
           <t>3208</t>
@@ -7931,7 +9523,8 @@
       <c r="E117" s="23" t="n"/>
       <c r="F117" s="24" t="inlineStr">
         <is>
-          <t>VIPS</t>
+          <t>VIPS
+SILVER</t>
         </is>
       </c>
       <c r="G117" s="23" t="n"/>
@@ -7942,22 +9535,30 @@
       </c>
       <c r="I117" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J117" s="9" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
-        </is>
-      </c>
-      <c r="K117" s="8" t="n"/>
-      <c r="L117" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>28/07/26</t>
+        </is>
+      </c>
+      <c r="K117" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L117" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M117" s="23" t="n"/>
-      <c r="N117" s="22" t="n"/>
+      <c r="N117" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O117" s="23" t="n"/>
       <c r="P117" s="27" t="inlineStr">
         <is>
@@ -7980,20 +9581,28 @@
       <c r="V117" s="23" t="n"/>
     </row>
     <row r="118" ht="114" customHeight="1">
-      <c r="A118" s="25" t="inlineStr">
-        <is>
-          <t>Thanasombat,Chayapas,Ms</t>
+      <c r="A118" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Chayapas Thanasombat</t>
         </is>
       </c>
       <c r="B118" s="23" t="n"/>
-      <c r="C118" s="7" t="n"/>
+      <c r="C118" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D118" s="24" t="inlineStr">
         <is>
           <t>3209</t>
         </is>
       </c>
       <c r="E118" s="23" t="n"/>
-      <c r="F118" s="24" t="n"/>
+      <c r="F118" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G118" s="23" t="n"/>
       <c r="H118" s="8" t="inlineStr">
         <is>
@@ -8002,22 +9611,30 @@
       </c>
       <c r="I118" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J118" s="9" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
-        </is>
-      </c>
-      <c r="K118" s="8" t="n"/>
-      <c r="L118" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>27/07/26</t>
+        </is>
+      </c>
+      <c r="K118" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L118" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M118" s="23" t="n"/>
-      <c r="N118" s="22" t="n"/>
+      <c r="N118" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O118" s="23" t="n"/>
       <c r="P118" s="27" t="inlineStr">
         <is>
@@ -8034,20 +9651,28 @@
       <c r="V118" s="23" t="n"/>
     </row>
     <row r="119" ht="114" customHeight="1">
-      <c r="A119" s="25" t="inlineStr">
-        <is>
-          <t>Hallam,Axl,Mr</t>
+      <c r="A119" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Axl Hallam</t>
         </is>
       </c>
       <c r="B119" s="23" t="n"/>
-      <c r="C119" s="7" t="n"/>
+      <c r="C119" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D119" s="24" t="inlineStr">
         <is>
           <t>3210</t>
         </is>
       </c>
       <c r="E119" s="23" t="n"/>
-      <c r="F119" s="24" t="n"/>
+      <c r="F119" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G119" s="23" t="n"/>
       <c r="H119" s="8" t="inlineStr">
         <is>
@@ -8056,22 +9681,30 @@
       </c>
       <c r="I119" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J119" s="9" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
-        </is>
-      </c>
-      <c r="K119" s="8" t="n"/>
-      <c r="L119" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>28/07/26</t>
+        </is>
+      </c>
+      <c r="K119" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L119" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M119" s="23" t="n"/>
-      <c r="N119" s="22" t="n"/>
+      <c r="N119" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O119" s="23" t="n"/>
       <c r="P119" s="27" t="inlineStr">
         <is>
@@ -8088,20 +9721,29 @@
       <c r="V119" s="23" t="n"/>
     </row>
     <row r="120" ht="114" customHeight="1">
-      <c r="A120" s="25" t="inlineStr">
-        <is>
-          <t>Wongchaisuriya,Waratchaya,Ms</t>
+      <c r="A120" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Waratchaya Wongchaisuriya</t>
         </is>
       </c>
       <c r="B120" s="23" t="n"/>
-      <c r="C120" s="7" t="n"/>
+      <c r="C120" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D120" s="24" t="inlineStr">
         <is>
           <t>3306</t>
         </is>
       </c>
       <c r="E120" s="23" t="n"/>
-      <c r="F120" s="24" t="n"/>
+      <c r="F120" s="24" t="inlineStr">
+        <is>
+          <t>VIPG
+SILVER</t>
+        </is>
+      </c>
       <c r="G120" s="23" t="n"/>
       <c r="H120" s="8" t="inlineStr">
         <is>
@@ -8110,22 +9752,30 @@
       </c>
       <c r="I120" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J120" s="9" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
-        </is>
-      </c>
-      <c r="K120" s="8" t="n"/>
-      <c r="L120" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>28/07/26</t>
+        </is>
+      </c>
+      <c r="K120" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L120" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M120" s="23" t="n"/>
-      <c r="N120" s="22" t="n"/>
+      <c r="N120" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O120" s="23" t="n"/>
       <c r="P120" s="27" t="inlineStr">
         <is>
@@ -8152,20 +9802,29 @@
       <c r="V120" s="23" t="n"/>
     </row>
     <row r="121" ht="114" customHeight="1">
-      <c r="A121" s="25" t="inlineStr">
-        <is>
-          <t>Wongchaisuriya,Waratchaya,Ms</t>
+      <c r="A121" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Waratchaya Wongchaisuriya</t>
         </is>
       </c>
       <c r="B121" s="23" t="n"/>
-      <c r="C121" s="7" t="n"/>
+      <c r="C121" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D121" s="24" t="inlineStr">
         <is>
           <t>3308</t>
         </is>
       </c>
       <c r="E121" s="23" t="n"/>
-      <c r="F121" s="24" t="n"/>
+      <c r="F121" s="24" t="inlineStr">
+        <is>
+          <t>VIPG
+SILVER</t>
+        </is>
+      </c>
       <c r="G121" s="23" t="n"/>
       <c r="H121" s="8" t="inlineStr">
         <is>
@@ -8174,22 +9833,30 @@
       </c>
       <c r="I121" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J121" s="9" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
-        </is>
-      </c>
-      <c r="K121" s="8" t="n"/>
-      <c r="L121" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>28/07/26</t>
+        </is>
+      </c>
+      <c r="K121" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L121" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M121" s="23" t="n"/>
-      <c r="N121" s="22" t="n"/>
+      <c r="N121" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O121" s="23" t="n"/>
       <c r="P121" s="27" t="inlineStr">
         <is>
@@ -8216,20 +9883,28 @@
       <c r="V121" s="23" t="n"/>
     </row>
     <row r="122" ht="114" customHeight="1">
-      <c r="A122" s="25" t="inlineStr">
-        <is>
-          <t>Wongsakul,Nichakarn,Ms</t>
+      <c r="A122" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Nichakarn Wongsakul</t>
         </is>
       </c>
       <c r="B122" s="23" t="n"/>
-      <c r="C122" s="7" t="n"/>
+      <c r="C122" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D122" s="24" t="inlineStr">
         <is>
           <t>3310</t>
         </is>
       </c>
       <c r="E122" s="23" t="n"/>
-      <c r="F122" s="24" t="n"/>
+      <c r="F122" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G122" s="23" t="n"/>
       <c r="H122" s="8" t="inlineStr">
         <is>
@@ -8238,22 +9913,30 @@
       </c>
       <c r="I122" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J122" s="9" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
-        </is>
-      </c>
-      <c r="K122" s="8" t="n"/>
-      <c r="L122" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>28/07/26</t>
+        </is>
+      </c>
+      <c r="K122" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L122" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M122" s="23" t="n"/>
-      <c r="N122" s="22" t="n"/>
+      <c r="N122" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O122" s="23" t="n"/>
       <c r="P122" s="27" t="inlineStr">
         <is>
@@ -8273,20 +9956,28 @@
       <c r="V122" s="23" t="n"/>
     </row>
     <row r="123" ht="114" customHeight="1">
-      <c r="A123" s="25" t="inlineStr">
-        <is>
-          <t>Jienjitlert,Vichai,Mr</t>
+      <c r="A123" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Vichai Jienjitlert</t>
         </is>
       </c>
       <c r="B123" s="23" t="n"/>
-      <c r="C123" s="7" t="n"/>
+      <c r="C123" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D123" s="24" t="inlineStr">
         <is>
           <t>3404</t>
         </is>
       </c>
       <c r="E123" s="23" t="n"/>
-      <c r="F123" s="24" t="n"/>
+      <c r="F123" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G123" s="23" t="n"/>
       <c r="H123" s="8" t="inlineStr">
         <is>
@@ -8295,22 +9986,30 @@
       </c>
       <c r="I123" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J123" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K123" s="8" t="n"/>
-      <c r="L123" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K123" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L123" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M123" s="23" t="n"/>
-      <c r="N123" s="22" t="n"/>
+      <c r="N123" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O123" s="23" t="n"/>
       <c r="P123" s="27" t="inlineStr">
         <is>
@@ -8336,44 +10035,60 @@
       <c r="V123" s="23" t="n"/>
     </row>
     <row r="124" ht="114" customHeight="1">
-      <c r="A124" s="25" t="inlineStr">
-        <is>
-          <t>Nuanla-ong,Thanchanok,Ms</t>
+      <c r="A124" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Thanchanok Nuanla-ong</t>
         </is>
       </c>
       <c r="B124" s="23" t="n"/>
-      <c r="C124" s="7" t="n"/>
+      <c r="C124" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D124" s="24" t="inlineStr">
         <is>
           <t>3409</t>
         </is>
       </c>
       <c r="E124" s="23" t="n"/>
-      <c r="F124" s="24" t="n"/>
+      <c r="F124" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G124" s="23" t="n"/>
       <c r="H124" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2+1</t>
         </is>
       </c>
       <c r="I124" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J124" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K124" s="8" t="n"/>
-      <c r="L124" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K124" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L124" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M124" s="23" t="n"/>
-      <c r="N124" s="22" t="n"/>
+      <c r="N124" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O124" s="23" t="n"/>
       <c r="P124" s="27" t="inlineStr">
         <is>
@@ -8394,44 +10109,60 @@
       <c r="V124" s="23" t="n"/>
     </row>
     <row r="125" ht="114" customHeight="1">
-      <c r="A125" s="25" t="inlineStr">
-        <is>
-          <t>Santiskulpong,Chatchai,Mr</t>
+      <c r="A125" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Chatchai Santiskulpong</t>
         </is>
       </c>
       <c r="B125" s="23" t="n"/>
-      <c r="C125" s="7" t="n"/>
+      <c r="C125" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D125" s="24" t="inlineStr">
         <is>
           <t>3411</t>
         </is>
       </c>
       <c r="E125" s="23" t="n"/>
-      <c r="F125" s="24" t="n"/>
+      <c r="F125" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G125" s="23" t="n"/>
       <c r="H125" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2+1</t>
         </is>
       </c>
       <c r="I125" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J125" s="9" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
-        </is>
-      </c>
-      <c r="K125" s="8" t="n"/>
-      <c r="L125" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>27/07/26</t>
+        </is>
+      </c>
+      <c r="K125" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L125" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M125" s="23" t="n"/>
-      <c r="N125" s="22" t="n"/>
+      <c r="N125" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O125" s="23" t="n"/>
       <c r="P125" s="27" t="inlineStr">
         <is>
@@ -8454,13 +10185,17 @@
       <c r="V125" s="23" t="n"/>
     </row>
     <row r="126" ht="114" customHeight="1">
-      <c r="A126" s="25" t="inlineStr">
-        <is>
-          <t>Saetun,Napatsakorn,Mrs</t>
+      <c r="A126" s="93" t="inlineStr">
+        <is>
+          <t>Mrs. Napatsakorn Saetun</t>
         </is>
       </c>
       <c r="B126" s="23" t="n"/>
-      <c r="C126" s="7" t="n"/>
+      <c r="C126" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D126" s="24" t="inlineStr">
         <is>
           <t>3501</t>
@@ -8469,7 +10204,8 @@
       <c r="E126" s="23" t="n"/>
       <c r="F126" s="24" t="inlineStr">
         <is>
-          <t>VIPS</t>
+          <t>VIPS
+PLATINUM</t>
         </is>
       </c>
       <c r="G126" s="23" t="n"/>
@@ -8480,22 +10216,30 @@
       </c>
       <c r="I126" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J126" s="9" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
-        </is>
-      </c>
-      <c r="K126" s="8" t="n"/>
-      <c r="L126" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>27/07/26</t>
+        </is>
+      </c>
+      <c r="K126" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L126" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M126" s="23" t="n"/>
-      <c r="N126" s="22" t="n"/>
+      <c r="N126" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O126" s="23" t="n"/>
       <c r="P126" s="27" t="inlineStr">
         <is>
@@ -8522,20 +10266,28 @@
       <c r="V126" s="23" t="n"/>
     </row>
     <row r="127" ht="114" customHeight="1">
-      <c r="A127" s="25" t="inlineStr">
-        <is>
-          <t>Anansetsiri,Kotchapan,Ms</t>
+      <c r="A127" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Kotchapan Anansetsiri</t>
         </is>
       </c>
       <c r="B127" s="23" t="n"/>
-      <c r="C127" s="7" t="n"/>
+      <c r="C127" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D127" s="24" t="inlineStr">
         <is>
           <t>3511</t>
         </is>
       </c>
       <c r="E127" s="23" t="n"/>
-      <c r="F127" s="24" t="n"/>
+      <c r="F127" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G127" s="23" t="n"/>
       <c r="H127" s="8" t="inlineStr">
         <is>
@@ -8544,22 +10296,30 @@
       </c>
       <c r="I127" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J127" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K127" s="8" t="n"/>
-      <c r="L127" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K127" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L127" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M127" s="23" t="n"/>
-      <c r="N127" s="22" t="n"/>
+      <c r="N127" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O127" s="23" t="n"/>
       <c r="P127" s="27" t="inlineStr">
         <is>
@@ -8577,20 +10337,28 @@
       <c r="V127" s="23" t="n"/>
     </row>
     <row r="128" ht="114" customHeight="1">
-      <c r="A128" s="25" t="inlineStr">
-        <is>
-          <t>Klinmeang,Surajit,Mr</t>
+      <c r="A128" s="93" t="inlineStr">
+        <is>
+          <t>Mr. Surajit Klinmeang</t>
         </is>
       </c>
       <c r="B128" s="23" t="n"/>
-      <c r="C128" s="7" t="n"/>
+      <c r="C128" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D128" s="24" t="inlineStr">
         <is>
           <t>3512</t>
         </is>
       </c>
       <c r="E128" s="23" t="n"/>
-      <c r="F128" s="24" t="n"/>
+      <c r="F128" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G128" s="23" t="n"/>
       <c r="H128" s="8" t="inlineStr">
         <is>
@@ -8599,22 +10367,30 @@
       </c>
       <c r="I128" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J128" s="9" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
-        </is>
-      </c>
-      <c r="K128" s="8" t="n"/>
-      <c r="L128" s="31" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>26/07/26</t>
+        </is>
+      </c>
+      <c r="K128" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L128" s="94" t="inlineStr">
+        <is>
+          <t>14.00</t>
         </is>
       </c>
       <c r="M128" s="23" t="n"/>
-      <c r="N128" s="22" t="n"/>
+      <c r="N128" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O128" s="23" t="n"/>
       <c r="P128" s="27" t="inlineStr">
         <is>
@@ -8635,20 +10411,28 @@
       <c r="V128" s="23" t="n"/>
     </row>
     <row r="129" ht="114" customHeight="1">
-      <c r="A129" s="25" t="inlineStr">
-        <is>
-          <t>Saelo,Nitikul,Ms</t>
+      <c r="A129" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Nitikul Saelo</t>
         </is>
       </c>
       <c r="B129" s="23" t="n"/>
-      <c r="C129" s="7" t="n"/>
+      <c r="C129" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D129" s="24" t="inlineStr">
         <is>
           <t>3602</t>
         </is>
       </c>
       <c r="E129" s="23" t="n"/>
-      <c r="F129" s="24" t="n"/>
+      <c r="F129" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G129" s="23" t="n"/>
       <c r="H129" s="8" t="inlineStr">
         <is>
@@ -8657,22 +10441,30 @@
       </c>
       <c r="I129" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J129" s="9" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
-        </is>
-      </c>
-      <c r="K129" s="8" t="n"/>
-      <c r="L129" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>27/07/26</t>
+        </is>
+      </c>
+      <c r="K129" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L129" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M129" s="23" t="n"/>
-      <c r="N129" s="22" t="n"/>
+      <c r="N129" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O129" s="23" t="n"/>
       <c r="P129" s="27" t="inlineStr">
         <is>
@@ -8695,20 +10487,28 @@
       <c r="V129" s="23" t="n"/>
     </row>
     <row r="130" ht="114" customHeight="1">
-      <c r="A130" s="25" t="inlineStr">
-        <is>
-          <t>Saelo,Nitikul,Ms</t>
+      <c r="A130" s="93" t="inlineStr">
+        <is>
+          <t>Ms. Nitikul Saelo</t>
         </is>
       </c>
       <c r="B130" s="23" t="n"/>
-      <c r="C130" s="7" t="n"/>
+      <c r="C130" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D130" s="24" t="inlineStr">
         <is>
           <t>3603</t>
         </is>
       </c>
       <c r="E130" s="23" t="n"/>
-      <c r="F130" s="24" t="n"/>
+      <c r="F130" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G130" s="23" t="n"/>
       <c r="H130" s="8" t="inlineStr">
         <is>
@@ -8717,22 +10517,30 @@
       </c>
       <c r="I130" s="9" t="inlineStr">
         <is>
-          <t>25-JUL-26</t>
+          <t>25/07/26</t>
         </is>
       </c>
       <c r="J130" s="9" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
-        </is>
-      </c>
-      <c r="K130" s="8" t="n"/>
-      <c r="L130" s="31" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>27/07/26</t>
+        </is>
+      </c>
+      <c r="K130" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L130" s="94" t="inlineStr">
+        <is>
+          <t>15.00</t>
         </is>
       </c>
       <c r="M130" s="23" t="n"/>
-      <c r="N130" s="22" t="n"/>
+      <c r="N130" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="O130" s="23" t="n"/>
       <c r="P130" s="27" t="inlineStr">
         <is>
@@ -8755,32 +10563,32 @@
       <c r="V130" s="23" t="n"/>
     </row>
     <row r="131" ht="99" customFormat="1" customHeight="1" s="2">
-      <c r="A131" s="91" t="inlineStr">
+      <c r="A131" s="95" t="inlineStr">
         <is>
           <t>VIP DEPARTURE</t>
         </is>
       </c>
-      <c r="B131" s="91" t="n"/>
-      <c r="C131" s="91" t="n"/>
-      <c r="D131" s="91" t="n"/>
-      <c r="E131" s="91" t="n"/>
-      <c r="F131" s="91" t="n"/>
-      <c r="G131" s="91" t="n"/>
-      <c r="H131" s="91" t="n"/>
-      <c r="I131" s="91" t="n"/>
-      <c r="J131" s="91" t="n"/>
-      <c r="K131" s="91" t="n"/>
-      <c r="L131" s="91" t="n"/>
-      <c r="M131" s="91" t="n"/>
-      <c r="N131" s="91" t="n"/>
-      <c r="O131" s="91" t="n"/>
-      <c r="P131" s="91" t="n"/>
-      <c r="Q131" s="91" t="n"/>
-      <c r="R131" s="91" t="n"/>
-      <c r="S131" s="91" t="n"/>
-      <c r="T131" s="91" t="n"/>
-      <c r="U131" s="91" t="n"/>
-      <c r="V131" s="91" t="n"/>
+      <c r="B131" s="95" t="n"/>
+      <c r="C131" s="95" t="n"/>
+      <c r="D131" s="95" t="n"/>
+      <c r="E131" s="95" t="n"/>
+      <c r="F131" s="95" t="n"/>
+      <c r="G131" s="95" t="n"/>
+      <c r="H131" s="95" t="n"/>
+      <c r="I131" s="95" t="n"/>
+      <c r="J131" s="95" t="n"/>
+      <c r="K131" s="95" t="n"/>
+      <c r="L131" s="95" t="n"/>
+      <c r="M131" s="95" t="n"/>
+      <c r="N131" s="95" t="n"/>
+      <c r="O131" s="95" t="n"/>
+      <c r="P131" s="95" t="n"/>
+      <c r="Q131" s="95" t="n"/>
+      <c r="R131" s="95" t="n"/>
+      <c r="S131" s="95" t="n"/>
+      <c r="T131" s="95" t="n"/>
+      <c r="U131" s="95" t="n"/>
+      <c r="V131" s="95" t="n"/>
     </row>
     <row r="132" ht="96" customHeight="1">
       <c r="A132" s="26" t="inlineStr">
@@ -8851,7 +10659,7 @@
       <c r="V132" s="23" t="n"/>
     </row>
     <row r="133" ht="114" customHeight="1">
-      <c r="A133" s="25" t="n"/>
+      <c r="A133" s="75" t="n"/>
       <c r="B133" s="23" t="n"/>
       <c r="C133" s="7" t="n"/>
       <c r="D133" s="24" t="n"/>
@@ -8862,7 +10670,7 @@
       <c r="I133" s="9" t="n"/>
       <c r="J133" s="9" t="n"/>
       <c r="K133" s="8" t="n"/>
-      <c r="L133" s="31" t="n"/>
+      <c r="L133" s="50" t="n"/>
       <c r="M133" s="23" t="n"/>
       <c r="N133" s="22" t="n"/>
       <c r="O133" s="23" t="n"/>
@@ -8875,7 +10683,7 @@
       <c r="V133" s="23" t="n"/>
     </row>
     <row r="134" ht="114" customHeight="1">
-      <c r="A134" s="25" t="n"/>
+      <c r="A134" s="75" t="n"/>
       <c r="B134" s="23" t="n"/>
       <c r="C134" s="7" t="n"/>
       <c r="D134" s="24" t="n"/>
@@ -8886,7 +10694,7 @@
       <c r="I134" s="9" t="n"/>
       <c r="J134" s="9" t="n"/>
       <c r="K134" s="8" t="n"/>
-      <c r="L134" s="31" t="n"/>
+      <c r="L134" s="50" t="n"/>
       <c r="M134" s="23" t="n"/>
       <c r="N134" s="22" t="n"/>
       <c r="O134" s="23" t="n"/>
@@ -8899,7 +10707,7 @@
       <c r="V134" s="23" t="n"/>
     </row>
     <row r="135" ht="99" customFormat="1" customHeight="1" s="2">
-      <c r="A135" s="92" t="inlineStr">
+      <c r="A135" s="96" t="inlineStr">
         <is>
           <t>Priority Guest (Handicap In House)</t>
         </is>
@@ -8995,7 +10803,7 @@
       <c r="V136" s="23" t="n"/>
     </row>
     <row r="137" ht="114" customHeight="1">
-      <c r="A137" s="25" t="n"/>
+      <c r="A137" s="75" t="n"/>
       <c r="B137" s="23" t="n"/>
       <c r="C137" s="7" t="n"/>
       <c r="D137" s="24" t="n"/>
@@ -9006,7 +10814,7 @@
       <c r="I137" s="9" t="n"/>
       <c r="J137" s="9" t="n"/>
       <c r="K137" s="8" t="n"/>
-      <c r="L137" s="31" t="n"/>
+      <c r="L137" s="50" t="n"/>
       <c r="M137" s="23" t="n"/>
       <c r="N137" s="22" t="n"/>
       <c r="O137" s="23" t="n"/>
@@ -9019,7 +10827,7 @@
       <c r="V137" s="23" t="n"/>
     </row>
     <row r="138" ht="103.5" customHeight="1">
-      <c r="A138" s="71" t="inlineStr">
+      <c r="A138" s="72" t="inlineStr">
         <is>
           <t>Guest's Birthday</t>
         </is>
@@ -9151,7 +10959,7 @@
       <c r="V142" s="23" t="n"/>
     </row>
     <row r="143" ht="103.5" customHeight="1">
-      <c r="A143" s="71" t="inlineStr">
+      <c r="A143" s="72" t="inlineStr">
         <is>
           <t>INSPECTION</t>
         </is>
@@ -9275,7 +11083,7 @@
       <c r="V146" s="46" t="n"/>
     </row>
     <row r="147" ht="103.5" customFormat="1" customHeight="1" s="10">
-      <c r="A147" s="71" t="inlineStr">
+      <c r="A147" s="72" t="inlineStr">
         <is>
           <t>GROUP</t>
         </is>
@@ -9371,7 +11179,7 @@
       <c r="V149" s="29" t="n"/>
     </row>
     <row r="150" ht="93.75" customFormat="1" customHeight="1" s="10">
-      <c r="A150" s="49" t="inlineStr">
+      <c r="A150" s="51" t="inlineStr">
         <is>
           <t>Outlet</t>
         </is>
@@ -9411,13 +11219,13 @@
       <c r="V150" s="23" t="n"/>
     </row>
     <row r="151" ht="114" customHeight="1">
-      <c r="A151" s="74" t="inlineStr">
+      <c r="A151" s="76" t="inlineStr">
         <is>
           <t>Elements</t>
         </is>
       </c>
-      <c r="B151" s="54" t="n"/>
-      <c r="C151" s="54" t="n"/>
+      <c r="B151" s="56" t="n"/>
+      <c r="C151" s="56" t="n"/>
       <c r="D151" s="45" t="inlineStr">
         <is>
           <t>Opening from 06.30 - 10.30 for breakfast</t>
@@ -9429,32 +11237,32 @@
       <c r="H151" s="28" t="n"/>
       <c r="I151" s="28" t="n"/>
       <c r="J151" s="23" t="n"/>
-      <c r="K151" s="69" t="inlineStr">
+      <c r="K151" s="70" t="inlineStr">
         <is>
           <t xml:space="preserve">Burger N' Wing </t>
         </is>
       </c>
-      <c r="L151" s="54" t="n"/>
-      <c r="M151" s="54" t="n"/>
-      <c r="N151" s="54" t="n"/>
-      <c r="O151" s="54" t="n"/>
-      <c r="P151" s="73" t="inlineStr">
+      <c r="L151" s="56" t="n"/>
+      <c r="M151" s="56" t="n"/>
+      <c r="N151" s="56" t="n"/>
+      <c r="O151" s="56" t="n"/>
+      <c r="P151" s="74" t="inlineStr">
         <is>
           <t>Opening from 12.00 - 20.00</t>
         </is>
       </c>
-      <c r="Q151" s="54" t="n"/>
-      <c r="R151" s="54" t="n"/>
-      <c r="S151" s="54" t="n"/>
-      <c r="T151" s="54" t="n"/>
-      <c r="U151" s="54" t="n"/>
+      <c r="Q151" s="56" t="n"/>
+      <c r="R151" s="56" t="n"/>
+      <c r="S151" s="56" t="n"/>
+      <c r="T151" s="56" t="n"/>
+      <c r="U151" s="56" t="n"/>
       <c r="V151" s="38" t="n"/>
     </row>
     <row r="152" ht="114" customHeight="1">
       <c r="A152" s="39" t="n"/>
-      <c r="B152" s="55" t="n"/>
-      <c r="C152" s="55" t="n"/>
-      <c r="D152" s="64" t="inlineStr">
+      <c r="B152" s="57" t="n"/>
+      <c r="C152" s="57" t="n"/>
+      <c r="D152" s="65" t="inlineStr">
         <is>
           <t>Opening from 18.00 - 22.00 for dinner (only Friday to Sunday)</t>
         </is>
@@ -9465,7 +11273,7 @@
       <c r="H152" s="28" t="n"/>
       <c r="I152" s="28" t="n"/>
       <c r="J152" s="23" t="n"/>
-      <c r="K152" s="66" t="inlineStr">
+      <c r="K152" s="67" t="inlineStr">
         <is>
           <t>Coco Fire</t>
         </is>
@@ -9487,25 +11295,25 @@
       <c r="V152" s="23" t="n"/>
     </row>
     <row r="153" ht="114" customHeight="1">
-      <c r="A153" s="74" t="inlineStr">
+      <c r="A153" s="76" t="inlineStr">
         <is>
           <t>The Pantry</t>
         </is>
       </c>
       <c r="B153" s="28" t="n"/>
       <c r="C153" s="28" t="n"/>
-      <c r="D153" s="77" t="inlineStr">
+      <c r="D153" s="79" t="inlineStr">
         <is>
           <t>Opening from 07.00 - 19.00</t>
         </is>
       </c>
-      <c r="E153" s="55" t="n"/>
-      <c r="F153" s="55" t="n"/>
-      <c r="G153" s="55" t="n"/>
-      <c r="H153" s="55" t="n"/>
-      <c r="I153" s="55" t="n"/>
-      <c r="J153" s="55" t="n"/>
-      <c r="K153" s="66" t="inlineStr">
+      <c r="E153" s="57" t="n"/>
+      <c r="F153" s="57" t="n"/>
+      <c r="G153" s="57" t="n"/>
+      <c r="H153" s="57" t="n"/>
+      <c r="I153" s="57" t="n"/>
+      <c r="J153" s="57" t="n"/>
+      <c r="K153" s="67" t="inlineStr">
         <is>
           <t>Mizu Bar</t>
         </is>
@@ -9527,14 +11335,14 @@
       <c r="V153" s="23" t="n"/>
     </row>
     <row r="154" ht="114" customHeight="1">
-      <c r="A154" s="66" t="inlineStr">
+      <c r="A154" s="67" t="inlineStr">
         <is>
           <t>Mi Scusi</t>
         </is>
       </c>
       <c r="B154" s="28" t="n"/>
       <c r="C154" s="28" t="n"/>
-      <c r="D154" s="64" t="inlineStr">
+      <c r="D154" s="65" t="inlineStr">
         <is>
           <t>Monday to Thursday 11.00 - 21.00 | Friday to Sunday 11.00 - 18.00</t>
         </is>
@@ -9545,7 +11353,7 @@
       <c r="H154" s="28" t="n"/>
       <c r="I154" s="28" t="n"/>
       <c r="J154" s="23" t="n"/>
-      <c r="K154" s="66" t="inlineStr">
+      <c r="K154" s="67" t="inlineStr">
         <is>
           <t>AvaniSpa</t>
         </is>
@@ -9567,14 +11375,14 @@
       <c r="V154" s="23" t="n"/>
     </row>
     <row r="155" ht="114" customHeight="1">
-      <c r="A155" s="74" t="inlineStr">
+      <c r="A155" s="76" t="inlineStr">
         <is>
           <t>Scoop It</t>
         </is>
       </c>
       <c r="B155" s="28" t="n"/>
       <c r="C155" s="28" t="n"/>
-      <c r="D155" s="80" t="inlineStr">
+      <c r="D155" s="82" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
@@ -9594,7 +11402,7 @@
       <c r="M155" s="28" t="n"/>
       <c r="N155" s="28" t="n"/>
       <c r="O155" s="28" t="n"/>
-      <c r="P155" s="47" t="inlineStr">
+      <c r="P155" s="48" t="inlineStr">
         <is>
           <t>Opening from 09.00 - 20.00</t>
         </is>
@@ -9607,7 +11415,7 @@
       <c r="V155" s="23" t="n"/>
     </row>
     <row r="156" ht="114" customHeight="1">
-      <c r="A156" s="66" t="inlineStr">
+      <c r="A156" s="67" t="inlineStr">
         <is>
           <t>The Beach House</t>
         </is>
@@ -9634,7 +11442,7 @@
       <c r="M156" s="28" t="n"/>
       <c r="N156" s="28" t="n"/>
       <c r="O156" s="28" t="n"/>
-      <c r="P156" s="47" t="inlineStr">
+      <c r="P156" s="48" t="inlineStr">
         <is>
           <t>Opening from 09.00 - 20.00</t>
         </is>
@@ -9647,7 +11455,7 @@
       <c r="V156" s="23" t="n"/>
     </row>
     <row r="157" ht="114" customHeight="1">
-      <c r="A157" s="66" t="inlineStr">
+      <c r="A157" s="67" t="inlineStr">
         <is>
           <t>The Beach Bar</t>
         </is>
@@ -9674,7 +11482,7 @@
       <c r="M157" s="28" t="n"/>
       <c r="N157" s="28" t="n"/>
       <c r="O157" s="28" t="n"/>
-      <c r="P157" s="47" t="inlineStr">
+      <c r="P157" s="48" t="inlineStr">
         <is>
           <t>Opening from 06.00 - 22.00</t>
         </is>
@@ -9687,7 +11495,7 @@
       <c r="V157" s="23" t="n"/>
     </row>
     <row r="158" ht="99" customFormat="1" customHeight="1" s="2">
-      <c r="A158" s="58" t="inlineStr">
+      <c r="A158" s="60" t="inlineStr">
         <is>
           <t>Room Available for Upsell</t>
         </is>
@@ -9697,7 +11505,7 @@
       <c r="D158" s="28" t="n"/>
       <c r="E158" s="28" t="n"/>
       <c r="F158" s="23" t="n"/>
-      <c r="G158" s="60" t="inlineStr">
+      <c r="G158" s="62" t="inlineStr">
         <is>
           <t>Room Number</t>
         </is>
@@ -9710,7 +11518,7 @@
       <c r="M158" s="28" t="n"/>
       <c r="N158" s="28" t="n"/>
       <c r="O158" s="23" t="n"/>
-      <c r="P158" s="60" t="inlineStr">
+      <c r="P158" s="62" t="inlineStr">
         <is>
           <t>Available unit</t>
         </is>
@@ -9723,7 +11531,7 @@
       <c r="V158" s="23" t="n"/>
     </row>
     <row r="159" ht="114" customHeight="1">
-      <c r="A159" s="84" t="inlineStr">
+      <c r="A159" s="86" t="inlineStr">
         <is>
           <t>Suite</t>
         </is>
@@ -9733,7 +11541,7 @@
       <c r="D159" s="28" t="n"/>
       <c r="E159" s="28" t="n"/>
       <c r="F159" s="23" t="n"/>
-      <c r="G159" s="81" t="n"/>
+      <c r="G159" s="83" t="n"/>
       <c r="H159" s="28" t="n"/>
       <c r="I159" s="28" t="n"/>
       <c r="J159" s="28" t="n"/>
@@ -9751,7 +11559,7 @@
       <c r="V159" s="23" t="n"/>
     </row>
     <row r="160" ht="114" customHeight="1">
-      <c r="A160" s="84" t="inlineStr">
+      <c r="A160" s="86" t="inlineStr">
         <is>
           <t>Pool Access</t>
         </is>
@@ -9779,7 +11587,7 @@
       <c r="V160" s="23" t="n"/>
     </row>
     <row r="161" ht="99" customFormat="1" customHeight="1" s="2">
-      <c r="A161" s="58" t="inlineStr">
+      <c r="A161" s="60" t="inlineStr">
         <is>
           <t>ReviewPro</t>
         </is>
@@ -9807,7 +11615,7 @@
       <c r="V161" s="23" t="n"/>
     </row>
     <row r="722" ht="101.25" customHeight="1">
-      <c r="A722" s="58" t="inlineStr">
+      <c r="A722" s="60" t="inlineStr">
         <is>
           <t>ReviewPro Comment</t>
         </is>
@@ -9939,6 +11747,7 @@
     <mergeCell ref="N116:O116"/>
     <mergeCell ref="F46:G46"/>
     <mergeCell ref="P96:V96"/>
+    <mergeCell ref="A127:B127"/>
     <mergeCell ref="P90:V90"/>
     <mergeCell ref="F111:G111"/>
     <mergeCell ref="F61:G61"/>
@@ -9948,7 +11757,6 @@
     <mergeCell ref="P154:V154"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="A145:D145"/>
-    <mergeCell ref="M4:N4"/>
     <mergeCell ref="D129:E129"/>
     <mergeCell ref="P91:V91"/>
     <mergeCell ref="D79:E79"/>
@@ -10057,7 +11865,6 @@
     <mergeCell ref="P59:V59"/>
     <mergeCell ref="P130:V130"/>
     <mergeCell ref="N137:O137"/>
-    <mergeCell ref="L36:M36"/>
     <mergeCell ref="P46:V46"/>
     <mergeCell ref="F67:G67"/>
     <mergeCell ref="P111:V111"/>
@@ -10068,8 +11875,8 @@
     <mergeCell ref="F5:G6"/>
     <mergeCell ref="P48:V48"/>
     <mergeCell ref="N114:O114"/>
+    <mergeCell ref="G160:O160"/>
     <mergeCell ref="P125:V125"/>
-    <mergeCell ref="G160:O160"/>
     <mergeCell ref="P112:V112"/>
     <mergeCell ref="D100:E100"/>
     <mergeCell ref="F29:G29"/>
@@ -10081,6 +11888,7 @@
     <mergeCell ref="L28:M28"/>
     <mergeCell ref="N53:O53"/>
     <mergeCell ref="A70:B70"/>
+    <mergeCell ref="D50:E50"/>
     <mergeCell ref="D77:E77"/>
     <mergeCell ref="A161:V161"/>
     <mergeCell ref="L130:M130"/>
@@ -10093,6 +11901,7 @@
     <mergeCell ref="L68:M68"/>
     <mergeCell ref="N117:O117"/>
     <mergeCell ref="A99:B99"/>
+    <mergeCell ref="D44:E44"/>
     <mergeCell ref="P139:V139"/>
     <mergeCell ref="A74:B74"/>
     <mergeCell ref="L132:M132"/>
@@ -10138,9 +11947,9 @@
     <mergeCell ref="N122:O122"/>
     <mergeCell ref="B9:C10"/>
     <mergeCell ref="P62:V62"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="P133:V133"/>
     <mergeCell ref="F83:G83"/>
-    <mergeCell ref="P133:V133"/>
-    <mergeCell ref="A87:B87"/>
     <mergeCell ref="P127:V127"/>
     <mergeCell ref="F20:G20"/>
     <mergeCell ref="A46:B46"/>
@@ -10215,8 +12024,8 @@
     <mergeCell ref="F93:G93"/>
     <mergeCell ref="F22:G22"/>
     <mergeCell ref="A23:B23"/>
+    <mergeCell ref="L113:M113"/>
     <mergeCell ref="P146:Q146"/>
-    <mergeCell ref="L113:M113"/>
     <mergeCell ref="L100:M100"/>
     <mergeCell ref="P5:P6"/>
     <mergeCell ref="B12:C13"/>
@@ -10238,13 +12047,13 @@
     <mergeCell ref="D46:E46"/>
     <mergeCell ref="D40:E40"/>
     <mergeCell ref="L37:M37"/>
-    <mergeCell ref="A110:B110"/>
-    <mergeCell ref="M149:U149"/>
-    <mergeCell ref="D111:E111"/>
     <mergeCell ref="L97:M97"/>
     <mergeCell ref="F40:G40"/>
     <mergeCell ref="N37:O37"/>
     <mergeCell ref="N97:O97"/>
+    <mergeCell ref="A110:B110"/>
+    <mergeCell ref="D111:E111"/>
+    <mergeCell ref="M149:U149"/>
     <mergeCell ref="N72:O72"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="D104:E104"/>
@@ -10275,21 +12084,20 @@
     <mergeCell ref="J1:K2"/>
     <mergeCell ref="D137:E137"/>
     <mergeCell ref="P124:V124"/>
+    <mergeCell ref="L96:M96"/>
     <mergeCell ref="P80:V80"/>
     <mergeCell ref="D74:E74"/>
     <mergeCell ref="P151:V151"/>
     <mergeCell ref="D130:E130"/>
+    <mergeCell ref="A134:B134"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="F130:G130"/>
+    <mergeCell ref="R145:U145"/>
     <mergeCell ref="K157:O157"/>
     <mergeCell ref="D68:E68"/>
-    <mergeCell ref="L90:M90"/>
+    <mergeCell ref="A121:B121"/>
+    <mergeCell ref="P126:V126"/>
     <mergeCell ref="N90:O90"/>
-    <mergeCell ref="L96:M96"/>
-    <mergeCell ref="R145:U145"/>
-    <mergeCell ref="A134:B134"/>
-    <mergeCell ref="P126:V126"/>
-    <mergeCell ref="A121:B121"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="F130:G130"/>
     <mergeCell ref="L27:M27"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="N27:O27"/>
@@ -10307,15 +12115,14 @@
     <mergeCell ref="A73:B73"/>
     <mergeCell ref="N85:O85"/>
     <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F123:G123"/>
     <mergeCell ref="D36:E36"/>
     <mergeCell ref="P15:V15"/>
     <mergeCell ref="N22:O22"/>
     <mergeCell ref="P71:V71"/>
-    <mergeCell ref="P58:V58"/>
     <mergeCell ref="L116:M116"/>
     <mergeCell ref="A147:V147"/>
     <mergeCell ref="E146:K146"/>
+    <mergeCell ref="P58:V58"/>
     <mergeCell ref="P79:V79"/>
     <mergeCell ref="P73:V73"/>
     <mergeCell ref="D61:E61"/>
@@ -10332,19 +12139,20 @@
     <mergeCell ref="A42:B42"/>
     <mergeCell ref="L122:M122"/>
     <mergeCell ref="D62:E62"/>
+    <mergeCell ref="D56:E56"/>
     <mergeCell ref="A17:B17"/>
-    <mergeCell ref="D56:E56"/>
     <mergeCell ref="A126:B126"/>
     <mergeCell ref="F56:G56"/>
     <mergeCell ref="D127:E127"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="F105:G105"/>
+    <mergeCell ref="L90:M90"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A109:B109"/>
     <mergeCell ref="P155:V155"/>
     <mergeCell ref="D114:E114"/>
     <mergeCell ref="F43:G43"/>
     <mergeCell ref="N40:O40"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="F105:G105"/>
     <mergeCell ref="A151:C152"/>
     <mergeCell ref="N15:O15"/>
     <mergeCell ref="D64:E64"/>
@@ -10354,9 +12162,9 @@
     <mergeCell ref="D51:E51"/>
     <mergeCell ref="A117:B117"/>
     <mergeCell ref="P86:V86"/>
+    <mergeCell ref="A111:B111"/>
+    <mergeCell ref="P157:V157"/>
     <mergeCell ref="F107:G107"/>
-    <mergeCell ref="P157:V157"/>
-    <mergeCell ref="A111:B111"/>
     <mergeCell ref="D1:G2"/>
     <mergeCell ref="N79:O79"/>
     <mergeCell ref="F57:G57"/>
@@ -10412,11 +12220,11 @@
     <mergeCell ref="N104:O104"/>
     <mergeCell ref="Q9:R10"/>
     <mergeCell ref="S9:T10"/>
+    <mergeCell ref="L125:M125"/>
+    <mergeCell ref="N54:O54"/>
     <mergeCell ref="D128:E128"/>
-    <mergeCell ref="N54:O54"/>
+    <mergeCell ref="F128:G128"/>
     <mergeCell ref="E144:K144"/>
-    <mergeCell ref="F128:G128"/>
-    <mergeCell ref="L125:M125"/>
     <mergeCell ref="L112:M112"/>
     <mergeCell ref="N41:O41"/>
     <mergeCell ref="A119:B119"/>
@@ -10430,9 +12238,9 @@
     <mergeCell ref="F21:G21"/>
     <mergeCell ref="L43:M43"/>
     <mergeCell ref="N105:O105"/>
+    <mergeCell ref="N43:O43"/>
+    <mergeCell ref="P92:V92"/>
     <mergeCell ref="M11:N11"/>
-    <mergeCell ref="P92:V92"/>
-    <mergeCell ref="N43:O43"/>
     <mergeCell ref="P54:V54"/>
     <mergeCell ref="A133:B133"/>
     <mergeCell ref="A143:V143"/>
@@ -10480,9 +12288,9 @@
     <mergeCell ref="P123:V123"/>
     <mergeCell ref="L62:M62"/>
     <mergeCell ref="I12:I13"/>
+    <mergeCell ref="L133:M133"/>
     <mergeCell ref="D136:E136"/>
     <mergeCell ref="K12:K13"/>
-    <mergeCell ref="L133:M133"/>
     <mergeCell ref="L127:M127"/>
     <mergeCell ref="A66:B66"/>
     <mergeCell ref="N62:O62"/>
@@ -10586,15 +12394,15 @@
     <mergeCell ref="N25:O25"/>
     <mergeCell ref="F74:G74"/>
     <mergeCell ref="P142:V142"/>
-    <mergeCell ref="F30:G30"/>
     <mergeCell ref="D101:E101"/>
     <mergeCell ref="L145:O145"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="D76:E76"/>
     <mergeCell ref="P117:V117"/>
     <mergeCell ref="P55:V55"/>
     <mergeCell ref="F76:G76"/>
+    <mergeCell ref="K150:O150"/>
     <mergeCell ref="F94:G94"/>
-    <mergeCell ref="K150:O150"/>
     <mergeCell ref="L83:M83"/>
     <mergeCell ref="P119:V119"/>
     <mergeCell ref="D9:D10"/>
@@ -10629,9 +12437,9 @@
     <mergeCell ref="A75:B75"/>
     <mergeCell ref="L33:M33"/>
     <mergeCell ref="D107:E107"/>
+    <mergeCell ref="N33:O33"/>
     <mergeCell ref="N58:O58"/>
     <mergeCell ref="F36:G36"/>
-    <mergeCell ref="N33:O33"/>
     <mergeCell ref="F101:G101"/>
     <mergeCell ref="L35:M35"/>
     <mergeCell ref="A104:B104"/>
@@ -10665,6 +12473,7 @@
     <mergeCell ref="A132:B132"/>
     <mergeCell ref="F59:G59"/>
     <mergeCell ref="D95:E95"/>
+    <mergeCell ref="K153:O153"/>
     <mergeCell ref="N21:O21"/>
     <mergeCell ref="F24:G24"/>
     <mergeCell ref="P74:V74"/>
@@ -10674,21 +12483,20 @@
     <mergeCell ref="U11:V11"/>
     <mergeCell ref="N81:O81"/>
     <mergeCell ref="D57:E57"/>
-    <mergeCell ref="K153:O153"/>
     <mergeCell ref="F113:G113"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="H7:H8"/>
     <mergeCell ref="F32:G32"/>
     <mergeCell ref="L23:M23"/>
-    <mergeCell ref="D97:E97"/>
+    <mergeCell ref="J7:J8"/>
     <mergeCell ref="N23:O23"/>
+    <mergeCell ref="I9:I11"/>
     <mergeCell ref="P76:V76"/>
     <mergeCell ref="F97:G97"/>
     <mergeCell ref="P145:Q145"/>
     <mergeCell ref="K149:L149"/>
     <mergeCell ref="F26:G26"/>
-    <mergeCell ref="I9:I11"/>
-    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="D97:E97"/>
     <mergeCell ref="M9:N10"/>
     <mergeCell ref="L104:M104"/>
     <mergeCell ref="O9:P10"/>
@@ -10700,9 +12508,9 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="D121:E121"/>
     <mergeCell ref="L56:M56"/>
-    <mergeCell ref="A125:B125"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="L34:M34"/>
+    <mergeCell ref="A125:B125"/>
     <mergeCell ref="L105:M105"/>
     <mergeCell ref="N34:O34"/>
     <mergeCell ref="D42:E42"/>
@@ -10710,13 +12518,13 @@
     <mergeCell ref="A112:B112"/>
     <mergeCell ref="N99:O99"/>
     <mergeCell ref="L49:M49"/>
+    <mergeCell ref="D123:E123"/>
     <mergeCell ref="N74:O74"/>
     <mergeCell ref="N49:O49"/>
-    <mergeCell ref="D123:E123"/>
-    <mergeCell ref="A127:B127"/>
-    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="F123:G123"/>
+    <mergeCell ref="L36:M36"/>
     <mergeCell ref="D110:E110"/>
-    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="M4:N4"/>
     <mergeCell ref="A114:B114"/>
     <mergeCell ref="F44:G44"/>
   </mergeCells>

--- a/Briefing/Briefing.xlsx
+++ b/Briefing/Briefing.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2445" yWindow="3285" windowWidth="20160" windowHeight="17100" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="825" yWindow="3285" windowWidth="20160" windowHeight="17100" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Ori Format" sheetId="1" state="visible" r:id="rId1"/>
@@ -1315,7 +1315,7 @@
       <c r="A2" s="85" t="inlineStr">
         <is>
           <t>Daily Briefing
-Tuesday July 28, 2026</t>
+Wednesday July 29, 2026</t>
         </is>
       </c>
       <c r="B2" s="47" t="n"/>
@@ -2083,7 +2083,7 @@
       <c r="B16" s="24" t="n"/>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="D16" s="39" t="inlineStr">
@@ -2156,7 +2156,7 @@
       <c r="B17" s="24" t="n"/>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D17" s="39" t="inlineStr">
@@ -2226,7 +2226,7 @@
       <c r="B18" s="24" t="n"/>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D18" s="39" t="inlineStr">
@@ -2303,7 +2303,7 @@
       <c r="B19" s="24" t="n"/>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D19" s="39" t="inlineStr">
@@ -2381,7 +2381,7 @@
       <c r="B20" s="24" t="n"/>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D20" s="39" t="inlineStr">
@@ -2455,7 +2455,7 @@
       <c r="B21" s="24" t="n"/>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D21" s="39" t="inlineStr">
@@ -2524,7 +2524,7 @@
       <c r="B22" s="24" t="n"/>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D22" s="39" t="inlineStr">
@@ -2594,7 +2594,7 @@
       <c r="B23" s="24" t="n"/>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D23" s="39" t="inlineStr">
@@ -2665,7 +2665,7 @@
       <c r="B24" s="24" t="n"/>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="D24" s="39" t="inlineStr">
@@ -3176,7 +3176,7 @@
       <c r="B31" s="24" t="n"/>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D31" s="39" t="inlineStr">
@@ -3463,7 +3463,7 @@
       <c r="B35" s="24" t="n"/>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D35" s="39" t="inlineStr">
@@ -3533,7 +3533,7 @@
       <c r="B36" s="24" t="n"/>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D36" s="39" t="inlineStr">
@@ -3609,7 +3609,7 @@
       <c r="B37" s="24" t="n"/>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D37" s="39" t="inlineStr">
@@ -3683,7 +3683,7 @@
       <c r="B38" s="24" t="n"/>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D38" s="39" t="inlineStr">
@@ -3757,7 +3757,7 @@
       <c r="B39" s="24" t="n"/>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D39" s="39" t="inlineStr">
@@ -3831,7 +3831,7 @@
       <c r="B40" s="24" t="n"/>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D40" s="39" t="inlineStr">
@@ -3909,7 +3909,7 @@
       <c r="B41" s="24" t="n"/>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D41" s="39" t="inlineStr">
@@ -3978,7 +3978,7 @@
       <c r="B42" s="24" t="n"/>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="D42" s="39" t="inlineStr">
@@ -4054,7 +4054,7 @@
       <c r="B43" s="24" t="n"/>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D43" s="39" t="inlineStr">
@@ -4123,7 +4123,7 @@
       <c r="B44" s="24" t="n"/>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D44" s="39" t="inlineStr">
@@ -4203,7 +4203,7 @@
       <c r="B45" s="24" t="n"/>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D45" s="39" t="inlineStr">
@@ -4279,7 +4279,7 @@
       <c r="B46" s="24" t="n"/>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D46" s="39" t="inlineStr">
@@ -4355,7 +4355,7 @@
       <c r="B47" s="24" t="n"/>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D47" s="39" t="inlineStr">
@@ -4430,7 +4430,7 @@
       <c r="B48" s="24" t="n"/>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D48" s="39" t="inlineStr">
@@ -4506,7 +4506,7 @@
       <c r="B49" s="24" t="n"/>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D49" s="39" t="inlineStr">
@@ -4581,7 +4581,7 @@
       <c r="B50" s="24" t="n"/>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D50" s="39" t="inlineStr">
@@ -4658,7 +4658,7 @@
       <c r="B51" s="24" t="n"/>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D51" s="39" t="inlineStr">
@@ -4734,7 +4734,7 @@
       <c r="B52" s="24" t="n"/>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D52" s="39" t="inlineStr">
@@ -4810,7 +4810,7 @@
       <c r="B53" s="24" t="n"/>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D53" s="39" t="inlineStr">
@@ -4886,7 +4886,7 @@
       <c r="B54" s="24" t="n"/>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D54" s="39" t="inlineStr">
@@ -4961,7 +4961,7 @@
       <c r="B55" s="24" t="n"/>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D55" s="39" t="inlineStr">
@@ -5036,7 +5036,7 @@
       <c r="B56" s="24" t="n"/>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D56" s="39" t="inlineStr">
@@ -5110,7 +5110,7 @@
       <c r="B57" s="24" t="n"/>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D57" s="39" t="inlineStr">
@@ -5414,7 +5414,7 @@
       <c r="B61" s="24" t="n"/>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D61" s="39" t="inlineStr">
@@ -5487,7 +5487,7 @@
       <c r="B62" s="24" t="n"/>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D62" s="39" t="inlineStr">
@@ -5560,7 +5560,7 @@
       <c r="B63" s="24" t="n"/>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D63" s="39" t="inlineStr">
@@ -5633,7 +5633,7 @@
       <c r="B64" s="24" t="n"/>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D64" s="39" t="inlineStr">
@@ -5988,7 +5988,7 @@
       <c r="B69" s="24" t="n"/>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D69" s="39" t="inlineStr">
@@ -6067,7 +6067,7 @@
       <c r="B70" s="24" t="n"/>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D70" s="39" t="inlineStr">
@@ -6146,7 +6146,7 @@
       <c r="B71" s="24" t="n"/>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D71" s="39" t="inlineStr">
@@ -6225,7 +6225,7 @@
       <c r="B72" s="24" t="n"/>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D72" s="39" t="inlineStr">
@@ -6303,7 +6303,7 @@
       <c r="B73" s="24" t="n"/>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D73" s="39" t="inlineStr">
@@ -6381,7 +6381,7 @@
       <c r="B74" s="24" t="n"/>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D74" s="39" t="inlineStr">
@@ -6460,7 +6460,7 @@
       <c r="B75" s="24" t="n"/>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D75" s="39" t="inlineStr">
@@ -6533,7 +6533,7 @@
       <c r="B76" s="24" t="n"/>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D76" s="39" t="inlineStr">
@@ -6603,7 +6603,7 @@
       <c r="B77" s="24" t="n"/>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D77" s="39" t="inlineStr">
@@ -6682,7 +6682,7 @@
       <c r="B78" s="24" t="n"/>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D78" s="39" t="inlineStr">
@@ -6760,7 +6760,7 @@
       <c r="B79" s="24" t="n"/>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D79" s="39" t="inlineStr">
@@ -6838,7 +6838,7 @@
       <c r="B80" s="24" t="n"/>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D80" s="39" t="inlineStr">
@@ -6908,7 +6908,7 @@
       <c r="B81" s="24" t="n"/>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D81" s="39" t="inlineStr">
@@ -6982,7 +6982,7 @@
       <c r="B82" s="24" t="n"/>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D82" s="39" t="inlineStr">
@@ -7135,7 +7135,7 @@
       <c r="B84" s="24" t="n"/>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D84" s="39" t="inlineStr">
@@ -7212,7 +7212,7 @@
       <c r="B85" s="24" t="n"/>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D85" s="39" t="inlineStr">
@@ -7355,7 +7355,7 @@
       <c r="B87" s="24" t="n"/>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D87" s="39" t="inlineStr">
@@ -7430,7 +7430,7 @@
       <c r="B88" s="24" t="n"/>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D88" s="39" t="inlineStr">
@@ -7504,7 +7504,7 @@
       <c r="B89" s="24" t="n"/>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D89" s="39" t="inlineStr">
@@ -7577,7 +7577,7 @@
       <c r="B90" s="24" t="n"/>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D90" s="39" t="inlineStr">
@@ -7650,7 +7650,7 @@
       <c r="B91" s="24" t="n"/>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D91" s="39" t="inlineStr">
@@ -7728,7 +7728,7 @@
       <c r="B92" s="24" t="n"/>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D92" s="39" t="inlineStr">
@@ -7806,7 +7806,7 @@
       <c r="B93" s="24" t="n"/>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="D93" s="39" t="inlineStr">
@@ -7878,7 +7878,7 @@
       <c r="B94" s="24" t="n"/>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D94" s="39" t="inlineStr">
@@ -7956,7 +7956,7 @@
       <c r="B95" s="24" t="n"/>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D95" s="39" t="inlineStr">
@@ -8027,7 +8027,7 @@
       <c r="B96" s="24" t="n"/>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D96" s="39" t="inlineStr">
@@ -8167,7 +8167,7 @@
       <c r="B98" s="24" t="n"/>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D98" s="39" t="inlineStr">
@@ -8243,7 +8243,7 @@
       <c r="B99" s="24" t="n"/>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="D99" s="39" t="inlineStr">
@@ -8313,7 +8313,7 @@
       <c r="B100" s="24" t="n"/>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D100" s="39" t="inlineStr">
@@ -8389,7 +8389,7 @@
       <c r="B101" s="24" t="n"/>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D101" s="39" t="inlineStr">
@@ -8461,7 +8461,7 @@
       <c r="B102" s="24" t="n"/>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D102" s="39" t="inlineStr">
@@ -8537,7 +8537,7 @@
       <c r="B103" s="24" t="n"/>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D103" s="39" t="inlineStr">
@@ -8607,7 +8607,7 @@
       <c r="B104" s="24" t="n"/>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D104" s="39" t="inlineStr">
@@ -8685,7 +8685,7 @@
       <c r="B105" s="24" t="n"/>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D105" s="39" t="inlineStr">
@@ -8760,7 +8760,7 @@
       <c r="B106" s="24" t="n"/>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D106" s="39" t="inlineStr">
@@ -8837,7 +8837,7 @@
       <c r="B107" s="24" t="n"/>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D107" s="39" t="inlineStr">
@@ -8912,7 +8912,7 @@
       <c r="B108" s="24" t="n"/>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D108" s="39" t="inlineStr">
@@ -8987,7 +8987,7 @@
       <c r="B109" s="24" t="n"/>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D109" s="39" t="inlineStr">
@@ -9062,7 +9062,7 @@
       <c r="B110" s="24" t="n"/>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D110" s="39" t="inlineStr">
@@ -9135,7 +9135,7 @@
       <c r="B111" s="24" t="n"/>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="D111" s="39" t="inlineStr">
@@ -9213,7 +9213,7 @@
       <c r="B112" s="24" t="n"/>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D112" s="39" t="inlineStr">
@@ -9282,7 +9282,7 @@
       <c r="B113" s="24" t="n"/>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="D113" s="39" t="inlineStr">
@@ -9353,7 +9353,7 @@
       <c r="B114" s="24" t="n"/>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="D114" s="39" t="inlineStr">
@@ -9425,7 +9425,7 @@
       <c r="B115" s="24" t="n"/>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D115" s="39" t="inlineStr">
@@ -9497,7 +9497,7 @@
       <c r="B116" s="24" t="n"/>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D116" s="39" t="inlineStr">
@@ -9568,7 +9568,7 @@
       <c r="B117" s="24" t="n"/>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D117" s="39" t="inlineStr">
@@ -9645,7 +9645,7 @@
       <c r="B118" s="24" t="n"/>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D118" s="39" t="inlineStr">
@@ -9786,7 +9786,7 @@
       <c r="B120" s="24" t="n"/>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D120" s="39" t="inlineStr">
@@ -9867,7 +9867,7 @@
       <c r="B121" s="24" t="n"/>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D121" s="39" t="inlineStr">
@@ -9948,7 +9948,7 @@
       <c r="B122" s="24" t="n"/>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D122" s="39" t="inlineStr">
@@ -10021,7 +10021,7 @@
       <c r="B123" s="24" t="n"/>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D123" s="39" t="inlineStr">
@@ -10100,7 +10100,7 @@
       <c r="B124" s="24" t="n"/>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D124" s="39" t="inlineStr">
@@ -10250,7 +10250,7 @@
       <c r="B126" s="24" t="n"/>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D126" s="39" t="inlineStr">
@@ -10331,7 +10331,7 @@
       <c r="B127" s="24" t="n"/>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="D127" s="39" t="inlineStr">
@@ -10402,7 +10402,7 @@
       <c r="B128" s="24" t="n"/>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D128" s="39" t="inlineStr">
@@ -10476,7 +10476,7 @@
       <c r="B129" s="24" t="n"/>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D129" s="39" t="inlineStr">
@@ -10552,7 +10552,7 @@
       <c r="B130" s="24" t="n"/>
       <c r="C130" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D130" s="39" t="inlineStr">
@@ -10724,7 +10724,7 @@
       <c r="B133" s="24" t="n"/>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="D133" s="39" t="inlineStr">
@@ -10794,7 +10794,7 @@
       <c r="B134" s="24" t="n"/>
       <c r="C134" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D134" s="39" t="inlineStr">
@@ -10868,7 +10868,7 @@
       <c r="B135" s="24" t="n"/>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="D135" s="39" t="inlineStr">
@@ -10940,7 +10940,7 @@
       <c r="B136" s="24" t="n"/>
       <c r="C136" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D136" s="39" t="inlineStr">
@@ -11013,7 +11013,7 @@
       <c r="B137" s="24" t="n"/>
       <c r="C137" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="D137" s="39" t="inlineStr">
@@ -11083,7 +11083,7 @@
       <c r="B138" s="24" t="n"/>
       <c r="C138" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D138" s="39" t="inlineStr">
@@ -11445,7 +11445,7 @@
       <c r="B143" s="24" t="n"/>
       <c r="C143" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Taiwan (Chinese Taipei)</t>
         </is>
       </c>
       <c r="D143" s="39" t="inlineStr">
@@ -11762,7 +11762,7 @@
       <c r="B147" s="24" t="n"/>
       <c r="C147" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D147" s="39" t="inlineStr">
@@ -11833,7 +11833,7 @@
       <c r="B148" s="24" t="n"/>
       <c r="C148" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="D148" s="39" t="inlineStr">
@@ -11904,7 +11904,7 @@
       <c r="B149" s="24" t="n"/>
       <c r="C149" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D149" s="39" t="inlineStr">
@@ -12126,7 +12126,7 @@
       <c r="B152" s="24" t="n"/>
       <c r="C152" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D152" s="39" t="inlineStr">
@@ -12195,7 +12195,7 @@
       <c r="B153" s="24" t="n"/>
       <c r="C153" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="D153" s="39" t="inlineStr">
@@ -12266,7 +12266,7 @@
       <c r="B154" s="24" t="n"/>
       <c r="C154" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D154" s="39" t="inlineStr">
@@ -12337,7 +12337,7 @@
       <c r="B155" s="24" t="n"/>
       <c r="C155" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D155" s="39" t="inlineStr">
@@ -12411,7 +12411,7 @@
       <c r="B156" s="24" t="n"/>
       <c r="C156" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D156" s="39" t="inlineStr">
@@ -12480,7 +12480,7 @@
       <c r="B157" s="24" t="n"/>
       <c r="C157" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D157" s="39" t="inlineStr">
@@ -12549,7 +12549,7 @@
       <c r="B158" s="24" t="n"/>
       <c r="C158" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D158" s="39" t="inlineStr">
@@ -12618,7 +12618,7 @@
       <c r="B159" s="24" t="n"/>
       <c r="C159" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D159" s="39" t="inlineStr">
@@ -12687,7 +12687,7 @@
       <c r="B160" s="24" t="n"/>
       <c r="C160" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D160" s="39" t="inlineStr">
@@ -12756,7 +12756,7 @@
       <c r="B161" s="24" t="n"/>
       <c r="C161" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D161" s="39" t="inlineStr">
@@ -12825,7 +12825,7 @@
       <c r="B162" s="24" t="n"/>
       <c r="C162" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="D162" s="39" t="inlineStr">
@@ -12893,7 +12893,7 @@
       <c r="B163" s="24" t="n"/>
       <c r="C163" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D163" s="39" t="inlineStr">
@@ -12962,7 +12962,7 @@
       <c r="B164" s="24" t="n"/>
       <c r="C164" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D164" s="39" t="inlineStr">
@@ -13031,7 +13031,7 @@
       <c r="B165" s="24" t="n"/>
       <c r="C165" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D165" s="39" t="inlineStr">
@@ -13100,7 +13100,7 @@
       <c r="B166" s="24" t="n"/>
       <c r="C166" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D166" s="39" t="inlineStr">
@@ -13169,7 +13169,7 @@
       <c r="B167" s="24" t="n"/>
       <c r="C167" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D167" s="39" t="inlineStr">
@@ -13238,7 +13238,7 @@
       <c r="B168" s="24" t="n"/>
       <c r="C168" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D168" s="39" t="inlineStr">
@@ -13307,7 +13307,7 @@
       <c r="B169" s="24" t="n"/>
       <c r="C169" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D169" s="39" t="inlineStr">
@@ -13376,7 +13376,7 @@
       <c r="B170" s="24" t="n"/>
       <c r="C170" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D170" s="39" t="inlineStr">
@@ -13445,7 +13445,7 @@
       <c r="B171" s="24" t="n"/>
       <c r="C171" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D171" s="39" t="inlineStr">
@@ -13514,7 +13514,7 @@
       <c r="B172" s="24" t="n"/>
       <c r="C172" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D172" s="39" t="inlineStr">
@@ -13583,7 +13583,7 @@
       <c r="B173" s="24" t="n"/>
       <c r="C173" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D173" s="39" t="inlineStr">
@@ -13652,7 +13652,7 @@
       <c r="B174" s="24" t="n"/>
       <c r="C174" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D174" s="39" t="inlineStr">
@@ -13721,7 +13721,7 @@
       <c r="B175" s="24" t="n"/>
       <c r="C175" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D175" s="39" t="inlineStr">
@@ -13790,7 +13790,7 @@
       <c r="B176" s="24" t="n"/>
       <c r="C176" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D176" s="39" t="inlineStr">
@@ -13859,7 +13859,7 @@
       <c r="B177" s="24" t="n"/>
       <c r="C177" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D177" s="39" t="inlineStr">
@@ -13928,7 +13928,7 @@
       <c r="B178" s="24" t="n"/>
       <c r="C178" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D178" s="39" t="inlineStr">
@@ -13997,7 +13997,7 @@
       <c r="B179" s="24" t="n"/>
       <c r="C179" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D179" s="39" t="inlineStr">
@@ -14066,7 +14066,7 @@
       <c r="B180" s="24" t="n"/>
       <c r="C180" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D180" s="39" t="inlineStr">
@@ -14135,7 +14135,7 @@
       <c r="B181" s="24" t="n"/>
       <c r="C181" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="D181" s="39" t="inlineStr">
@@ -14205,7 +14205,7 @@
       <c r="B182" s="24" t="n"/>
       <c r="C182" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D182" s="39" t="inlineStr">
@@ -14279,7 +14279,7 @@
       <c r="B183" s="24" t="n"/>
       <c r="C183" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D183" s="39" t="inlineStr">
@@ -14348,7 +14348,7 @@
       <c r="B184" s="24" t="n"/>
       <c r="C184" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D184" s="39" t="inlineStr">
@@ -14417,7 +14417,7 @@
       <c r="B185" s="24" t="n"/>
       <c r="C185" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D185" s="39" t="inlineStr">
@@ -14486,7 +14486,7 @@
       <c r="B186" s="24" t="n"/>
       <c r="C186" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D186" s="39" t="inlineStr">
@@ -14560,7 +14560,7 @@
       <c r="B187" s="24" t="n"/>
       <c r="C187" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D187" s="39" t="inlineStr">
@@ -14628,7 +14628,7 @@
       <c r="B188" s="24" t="n"/>
       <c r="C188" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="D188" s="39" t="inlineStr">
@@ -14700,7 +14700,7 @@
       <c r="B189" s="24" t="n"/>
       <c r="C189" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="D189" s="39" t="inlineStr">
@@ -14772,7 +14772,7 @@
       <c r="B190" s="24" t="n"/>
       <c r="C190" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="D190" s="39" t="inlineStr">
@@ -14844,7 +14844,7 @@
       <c r="B191" s="24" t="n"/>
       <c r="C191" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Taiwan (Chinese Taipei)</t>
         </is>
       </c>
       <c r="D191" s="39" t="inlineStr">
@@ -14927,7 +14927,7 @@
       <c r="B192" s="24" t="n"/>
       <c r="C192" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D192" s="39" t="inlineStr">
@@ -14996,7 +14996,7 @@
       <c r="B193" s="24" t="n"/>
       <c r="C193" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D193" s="39" t="inlineStr">
@@ -15065,7 +15065,7 @@
       <c r="B194" s="24" t="n"/>
       <c r="C194" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D194" s="39" t="inlineStr">
@@ -15134,7 +15134,7 @@
       <c r="B195" s="24" t="n"/>
       <c r="C195" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D195" s="39" t="inlineStr">
@@ -15203,7 +15203,7 @@
       <c r="B196" s="24" t="n"/>
       <c r="C196" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D196" s="39" t="inlineStr">
@@ -15273,7 +15273,7 @@
       <c r="B197" s="24" t="n"/>
       <c r="C197" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D197" s="39" t="inlineStr">
@@ -15342,7 +15342,7 @@
       <c r="B198" s="24" t="n"/>
       <c r="C198" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D198" s="39" t="inlineStr">
@@ -15417,7 +15417,7 @@
       <c r="B199" s="24" t="n"/>
       <c r="C199" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D199" s="39" t="inlineStr">
@@ -15492,7 +15492,7 @@
       <c r="B200" s="24" t="n"/>
       <c r="C200" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D200" s="39" t="inlineStr">
@@ -15561,7 +15561,7 @@
       <c r="B201" s="24" t="n"/>
       <c r="C201" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D201" s="39" t="inlineStr">
@@ -15630,7 +15630,7 @@
       <c r="B202" s="24" t="n"/>
       <c r="C202" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D202" s="39" t="inlineStr">
@@ -15699,7 +15699,7 @@
       <c r="B203" s="24" t="n"/>
       <c r="C203" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D203" s="39" t="inlineStr">
@@ -15779,7 +15779,7 @@
       <c r="B204" s="24" t="n"/>
       <c r="C204" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D204" s="39" t="inlineStr">
@@ -15848,7 +15848,7 @@
       <c r="B205" s="24" t="n"/>
       <c r="C205" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D205" s="39" t="inlineStr">
@@ -15917,7 +15917,7 @@
       <c r="B206" s="24" t="n"/>
       <c r="C206" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D206" s="39" t="inlineStr">
@@ -15986,7 +15986,7 @@
       <c r="B207" s="24" t="n"/>
       <c r="C207" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D207" s="39" t="inlineStr">
@@ -16055,7 +16055,7 @@
       <c r="B208" s="24" t="n"/>
       <c r="C208" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D208" s="39" t="inlineStr">
@@ -16124,7 +16124,7 @@
       <c r="B209" s="24" t="n"/>
       <c r="C209" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D209" s="39" t="inlineStr">
@@ -16193,7 +16193,7 @@
       <c r="B210" s="24" t="n"/>
       <c r="C210" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D210" s="39" t="inlineStr">
@@ -16267,7 +16267,7 @@
       <c r="B211" s="24" t="n"/>
       <c r="C211" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D211" s="39" t="inlineStr">
@@ -16336,7 +16336,7 @@
       <c r="B212" s="24" t="n"/>
       <c r="C212" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D212" s="39" t="inlineStr">

--- a/Briefing/Briefing.xlsx
+++ b/Briefing/Briefing.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="825" yWindow="3285" windowWidth="20160" windowHeight="17100" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1065" yWindow="2805" windowWidth="20160" windowHeight="17100" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Ori Format" sheetId="1" state="visible" r:id="rId1"/>
